--- a/tame_output/ON/bt/strategyON_20240522.xlsx
+++ b/tame_output/ON/bt/strategyON_20240522.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.7%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.9%</t>
+          <t>69.8%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>17.3%</t>
+          <t>17.7%</t>
         </is>
       </c>
     </row>
@@ -921,12 +921,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.8%</t>
+          <t>111.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>92.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -982,37 +982,37 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.8%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.3%</t>
+          <t>-50.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-72.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>445.0%</t>
+          <t>445.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-601.7%</t>
+          <t>-595.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>3.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.9%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.7%</t>
+          <t>-37.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-3.1%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.9%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-279.4%</t>
+          <t>-276.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-22.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.0%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1318,37 +1318,37 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.1%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>46.8%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-213.6%</t>
+          <t>-139.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-216.2%</t>
+          <t>-210.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>63.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>42.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>43.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-168.4%</t>
+          <t>-164.8%</t>
         </is>
       </c>
     </row>
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.620092025845824</v>
+        <v>-5.838350069223328</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7214637543052151</v>
+        <v>0.6341605369542136</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7263910735463472</v>
+        <v>-0.9446491169238513</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.534022344829484</v>
+        <v>2.403067518802982</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.556456283611889</v>
+        <v>-5.774714326989393</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7516128522531065</v>
+        <v>0.6643096349021049</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.6627553313124127</v>
+        <v>-0.8810133746899168</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.576898591224162</v>
+        <v>2.44594376519766</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.463456242405991</v>
+        <v>-5.681714285783495</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7700071275192615</v>
+        <v>0.6827039101682599</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.6627553313124127</v>
+        <v>-0.8810133746899168</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.558092850007958</v>
+        <v>2.427138023981455</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.223025745601131</v>
+        <v>-5.441283788978635</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8679224028660828</v>
+        <v>0.7806191855150812</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4223248345075524</v>
+        <v>-0.6405828778850565</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.704094224715751</v>
+        <v>2.573139398689249</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.150783177429936</v>
+        <v>-5.36904122080744</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9007487439693809</v>
+        <v>0.8134455266183793</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4223248345075524</v>
+        <v>-0.6405828778850565</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.708023538550572</v>
+        <v>2.577068712524069</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.034843327804751</v>
+        <v>-5.253101371182255</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9478032677367949</v>
+        <v>0.8605000503857934</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3455031034914285</v>
+        <v>-0.5637611468689326</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.754795161077586</v>
+        <v>2.623840335051083</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.926038442325024</v>
+        <v>-5.144296485702528</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9883232931486794</v>
+        <v>0.9010200757976778</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3455031034914285</v>
+        <v>-0.5637611468689326</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.751793232297579</v>
+        <v>2.620838406271077</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.706017644288013</v>
+        <v>-4.924275687665517</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.077910649374098</v>
+        <v>0.9906074320230962</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2042832584234483</v>
+        <v>-0.4225413018009524</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.838104176348982</v>
+        <v>2.707149350322479</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.573149955224736</v>
+        <v>-4.79140799860224</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.146951907801232</v>
+        <v>1.05964869045023</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2042832584234483</v>
+        <v>-0.4225413018009524</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.853998359150805</v>
+        <v>2.723043533124303</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.413634851705366</v>
+        <v>-4.63189289508287</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.211903793649282</v>
+        <v>1.12460057629828</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.04476815490407837</v>
+        <v>-0.2630261982815825</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.950853265702729</v>
+        <v>2.819898439676226</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.268962706605628</v>
+        <v>-4.487220749983132</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.279860754250617</v>
+        <v>1.192557536899615</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.09990399019565904</v>
+        <v>-0.1183540531818451</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.047744655324011</v>
+        <v>2.916789829297509</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.328837533963321</v>
+        <v>-4.547095577340825</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.241948314708966</v>
+        <v>1.154645097357964</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.04002916283796693</v>
+        <v>-0.1782288805395372</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.997857250310822</v>
+        <v>2.866902424284319</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.242038036184312</v>
+        <v>-4.460296079561816</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.299068607143135</v>
+        <v>1.211765389792133</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.04002916283796693</v>
+        <v>-0.1782288805395372</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.020257743633388</v>
+        <v>2.889302917606885</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.244507742646118</v>
+        <v>-4.462765786023622</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.298153125931825</v>
+        <v>1.210849908580823</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.03755945637616076</v>
+        <v>-0.1806985870013433</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.018848321129716</v>
+        <v>2.887893495103214</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.312877928970128</v>
+        <v>-4.531135972347633</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.281811973876923</v>
+        <v>1.194508756525921</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.04683515541237571</v>
+        <v>-0.1714228879651284</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.035420663026147</v>
+        <v>2.904465836999645</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.421416109886262</v>
+        <v>-4.639674153263766</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.228833410142361</v>
+        <v>1.141530192791359</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.04683515541237571</v>
+        <v>-0.1714228879651284</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.025857371658038</v>
+        <v>2.894902545631536</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.452409269214967</v>
+        <v>-4.670667312592472</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.041145711451265</v>
+        <v>0.9538424941002634</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.04683515541237571</v>
+        <v>-0.1714228879651284</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.850566936698425</v>
+        <v>2.719612110671923</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.276935009422498</v>
+        <v>-4.495193052800003</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.115902647360041</v>
+        <v>1.028599430009039</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.04683515541237571</v>
+        <v>-0.1714228879651284</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.855134168690213</v>
+        <v>2.724179342663711</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.387871262063747</v>
+        <v>-4.606129305441252</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.047270175064748</v>
+        <v>0.9599669577137462</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.04683515541237571</v>
+        <v>-0.1714228879651284</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.83087619745142</v>
+        <v>2.699921371424918</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.59089783960698</v>
+        <v>-4.809155882984485</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9691909292673604</v>
+        <v>0.8818877119163586</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.3744494655083618</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.712191636145385</v>
+        <v>2.581236810118883</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.432972240671687</v>
+        <v>-4.651230284049192</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.04253355527361</v>
+        <v>0.9552303379226081</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.3744494655083618</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.722364022577518</v>
+        <v>2.591409196551016</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.34672877764531</v>
+        <v>-4.564986821022814</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.071977211058021</v>
+        <v>0.9846739937070195</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.3744494655083618</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.717310293151378</v>
+        <v>2.586355467124876</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.347911862296371</v>
+        <v>-4.566169905673876</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.063279752642122</v>
+        <v>0.9759765352911205</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1618344705973692</v>
+        <v>-0.3800925139748733</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.705700239515997</v>
+        <v>2.574745413489494</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.224784155302288</v>
+        <v>-4.443042198679793</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.113082708472857</v>
+        <v>1.025779491121855</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1618344705973692</v>
+        <v>-0.3800925139748733</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.706252112549099</v>
+        <v>2.575297286522596</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.131973673851428</v>
+        <v>-4.350231717228933</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.079479592944567</v>
+        <v>0.9921763755935649</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.06902398914650987</v>
+        <v>-0.287282032524014</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.691211093310979</v>
+        <v>2.560256267284477</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.083410621630398</v>
+        <v>-4.301668665007903</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.10077828975758</v>
+        <v>1.013475072406578</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.02046093692547968</v>
+        <v>-0.2387189803029838</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.722222400568199</v>
+        <v>2.591267574541696</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.970739403394148</v>
+        <v>-4.188997446771653</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.140922485563802</v>
+        <v>1.053619268212801</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.09221028131077053</v>
+        <v>-0.1260477620667336</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.784900840021672</v>
+        <v>2.653946013995169</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.858362402211476</v>
+        <v>-4.07662044558898</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.191364581867539</v>
+        <v>1.104061364516537</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.09221028131077053</v>
+        <v>-0.1260477620667336</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.790392135852339</v>
+        <v>2.659437309825837</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.056596971098206</v>
+        <v>-4.274855014475711</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.123567956081386</v>
+        <v>1.036264738730384</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1060242875759601</v>
+        <v>-0.3242823309534641</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.68294859628884</v>
+        <v>2.551993770262337</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.139598252123485</v>
+        <v>-4.35785629550099</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9287231636719273</v>
+        <v>0.8414199463209255</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1245951721031338</v>
+        <v>-0.3428532154806379</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.510161785573189</v>
+        <v>2.379206959546686</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.266665258430473</v>
+        <v>-4.484923301807978</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9980460218683378</v>
+        <v>0.9107428045173358</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1245951721031338</v>
+        <v>-0.3428532154806379</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.630311446292394</v>
+        <v>2.499356620265892</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.353263841411576</v>
+        <v>-4.571521884789081</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9779196147782196</v>
+        <v>0.8906163974272177</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1245951721031338</v>
+        <v>-0.3428532154806379</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.644824472394717</v>
+        <v>2.513869646368215</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.314880178853425</v>
+        <v>-4.53313822223093</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9906925211438486</v>
+        <v>0.9033893037928469</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.08621150954498263</v>
+        <v>-0.3044695529224867</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.665274111271977</v>
+        <v>2.534319285245474</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.137763848818259</v>
+        <v>-4.356021892195764</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.058268082003217</v>
+        <v>0.9709648646522151</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.08621150954498263</v>
+        <v>-0.3044695529224867</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.662003140117279</v>
+        <v>2.531048314090776</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.108061724841965</v>
+        <v>-4.32631976821947</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.070832323355648</v>
+        <v>0.9835291060046458</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.090681634760296</v>
+        <v>-0.3089396781378001</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.660004456750004</v>
+        <v>2.529049630723501</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.928686303603198</v>
+        <v>-4.146944346980702</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.136369467157569</v>
+        <v>1.049066249806567</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.06609512341042267</v>
+        <v>-0.1521629199670814</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.747857486958849</v>
+        <v>2.616902660932347</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.973700517123804</v>
+        <v>-4.191958560501309</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.099171237080916</v>
+        <v>1.011868019729914</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.03574622809581807</v>
+        <v>-0.182511815281686</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.710455605101676</v>
+        <v>2.579500779075174</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.240705027396239</v>
+        <v>-4.458963070773744</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9980609953108879</v>
+        <v>0.9107577779598861</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1586168099471305</v>
+        <v>-0.3768748533246346</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.599529344614853</v>
+        <v>2.46857451858835</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.529492247855154</v>
+        <v>-4.747750291232659</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8817500290238232</v>
+        <v>0.7944468116728214</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2597029300461309</v>
+        <v>-0.477960973423635</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.538081594451954</v>
+        <v>2.407126768425452</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.497016661684382</v>
+        <v>-4.715274705061887</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8923402250464489</v>
+        <v>0.8050370076954469</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2597029300461309</v>
+        <v>-0.477960973423635</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.535681556006271</v>
+        <v>2.404726729979768</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.477978533977085</v>
+        <v>-4.69623657735459</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8964801953376127</v>
+        <v>0.8091769779866107</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3178865413773254</v>
+        <v>-0.5361445847548295</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.497296108415799</v>
+        <v>2.366341282389297</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.509105165127703</v>
+        <v>-4.727363208505208</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.061611411816046</v>
+        <v>0.974308194465044</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3178865413773254</v>
+        <v>-0.5361445847548295</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.67487797735448</v>
+        <v>2.543923151327977</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.561425545728495</v>
+        <v>-4.779683589106</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.041516588561863</v>
+        <v>0.9542133712108609</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.2829396813684533</v>
+        <v>-0.5011977247459574</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.696679422345936</v>
+        <v>2.565724596319434</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.705748451653414</v>
+        <v>-4.924006495030919</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.989795956588821</v>
+        <v>0.9024927392378193</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.2829396813684533</v>
+        <v>-0.5011977247459574</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.702687952742862</v>
+        <v>2.57173312671636</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.558005481418411</v>
+        <v>-4.776263524795916</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.128045792474844</v>
+        <v>1.040742575123842</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1151323241335701</v>
+        <v>-0.3333903675110742</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.882525014875814</v>
+        <v>2.751570188849312</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.660020163949633</v>
+        <v>-4.878278207327138</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.090033540993836</v>
+        <v>1.002730323642835</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1151323241335701</v>
+        <v>-0.3333903675110742</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.885318636407295</v>
+        <v>2.754363810380793</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.52341081985554</v>
+        <v>-4.741668863233045</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.145339627023132</v>
+        <v>1.05803640967213</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.02147701996052237</v>
+        <v>-0.1967810234169817</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.967946591255409</v>
+        <v>2.836991765228906</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.66617615267819</v>
+        <v>-4.884434196055695</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.087313970634182</v>
+        <v>1.00001075328318</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.121288312862128</v>
+        <v>-0.3395463562396321</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.881367868301929</v>
+        <v>2.750413042275427</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.603878153902068</v>
+        <v>-4.822136197279573</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.178568723941452</v>
+        <v>1.09126550659045</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.121288312862128</v>
+        <v>-0.3395463562396321</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.94770342209875</v>
+        <v>2.816748596072247</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.454075798084077</v>
+        <v>3.45824391493612</v>
       </c>
       <c r="C1971" t="n">
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.401213498897135</v>
+        <v>-4.333903580743762</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9682154583328231</v>
+        <v>0.9951394255941723</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.07804310718714147</v>
+        <v>0.1391395362430771</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.775883146517709</v>
+        <v>2.812541003951271</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240522.xlsx
+++ b/tame_output/ON/bt/strategyON_20240522.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>61.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.3%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.8%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.4%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>51.5%</t>
         </is>
       </c>
     </row>
@@ -844,17 +844,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.8%</t>
+          <t>-78.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.0%</t>
+          <t>110.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.2%</t>
+          <t>128.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>92.7%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,42 +977,42 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-665.4%</t>
+          <t>-671.7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-8.8%</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-50.3%</t>
+          <t>-51.5%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.9%</t>
+          <t>-74.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>91.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>445.1%</t>
+          <t>449.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-595.0%</t>
+          <t>-606.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-266.5%</t>
+          <t>-269.1%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-9.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-37.9%</t>
+          <t>-38.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-26.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>49.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-276.7%</t>
+          <t>-281.3%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.2%</t>
+          <t>-21.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>68.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>69.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1318,37 +1318,37 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-14.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>56.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>48.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-139.6%</t>
+          <t>-213.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-210.1%</t>
+          <t>-209.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.8%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.1%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>42.3%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.2%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-15.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-164.8%</t>
+          <t>-164.3%</t>
         </is>
       </c>
     </row>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178241</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.371692658904851</v>
+        <v>-4.434725892533942</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.388705158687692</v>
+        <v>1.363491865236055</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.555734532842116</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.803498452054638</v>
+        <v>-4.86653168568373</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.202315728895181</v>
+        <v>1.177102435443545</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.692152029283383</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.038192446187191</v>
+        <v>-5.101225679816282</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.096722906244251</v>
+        <v>1.071509612792615</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.6858157620541279</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.373855093417643</v>
+        <v>-5.436888327046734</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9610384390080351</v>
+        <v>0.9358251455563988</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.6858157620541279</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.737481338317957</v>
+        <v>-5.800514571947048</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8220755012821512</v>
+        <v>0.796862207830515</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.7840373989212537</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.102608720956703</v>
+        <v>-6.165641954585794</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6752790632324839</v>
+        <v>0.6500657697808476</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.080348183220266</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.511197498137381</v>
+        <v>-6.574230731766473</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.510605096374972</v>
+        <v>0.4853918029233348</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.488936960400945</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.787773598453214</v>
+        <v>-6.850806832082306</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3951600887200994</v>
+        <v>0.3699467952684627</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.488936960400945</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.204165472740211</v>
+        <v>-7.267198706369303</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2265973896141777</v>
+        <v>0.201384096162541</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.488936960400945</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.580842483270056</v>
+        <v>-7.643875716899148</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.08618527607091897</v>
+        <v>0.06097198261928227</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.488936960400945</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.926717305254865</v>
+        <v>-7.989750538883957</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.05606508757730966</v>
+        <v>-0.08127838102894636</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.488936960400945</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.090297183439249</v>
+        <v>-8.153330417068341</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1230921187960621</v>
+        <v>-0.1483054122476992</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.488936960400945</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.386958525249447</v>
+        <v>-8.449991758878539</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2379776795909332</v>
+        <v>-0.2631909730425703</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.557680096134823</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.510202914464877</v>
+        <v>-8.573236148093969</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2913017398115083</v>
+        <v>-0.316515033263145</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297746</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.893204303207508</v>
+        <v>-8.9562375368366</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4446043966301447</v>
+        <v>-0.4698176900817814</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.050603183420629</v>
+        <v>-9.113636417049721</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.504992432743963</v>
+        <v>-0.5302057261955997</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.715078976347944</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.41013350592463</v>
+        <v>-9.473166739553722</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6434542584475134</v>
+        <v>-0.6686675518991501</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.715078976347944</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.460482569378852</v>
+        <v>-9.523515803007944</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6556778638720249</v>
+        <v>-0.6808911573236616</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.765428039802166</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776673</v>
+        <v>3.500446096776674</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.558101846800248</v>
+        <v>-9.62113508042934</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6916838242188144</v>
+        <v>-0.7168971176704511</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.863047317223563</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.554410921843838</v>
+        <v>-9.61744415547293</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.69020745423625</v>
+        <v>-0.7154207476878867</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.863047317223563</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.758669097173701</v>
+        <v>-9.821702330802793</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7663975272495529</v>
+        <v>-0.79161082070119</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.990686261837552</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.976706868804879</v>
+        <v>-10.03974010243397</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8491300814175879</v>
+        <v>-0.8743433748692246</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.165457029933451</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.90323703713743</v>
+        <v>-9.966270270766522</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8043704472571873</v>
+        <v>-0.829583740708824</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.091987198266002</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.07836145452397</v>
+        <v>-10.14139468815307</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8598649934642877</v>
+        <v>-0.8850782869159248</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.267111615652546</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.31281354853846</v>
+        <v>-10.37584678216755</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9608649959716797</v>
+        <v>-0.9860782894233169</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.267111615652546</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.6006173930757</v>
+        <v>-10.66365062670479</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.082658724560551</v>
+        <v>-1.107872018012188</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.554915460189784</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.65340354867603</v>
+        <v>-10.71643678230512</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.102657396962126</v>
+        <v>-1.127870690413762</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.650590946772181</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.88543246841229</v>
+        <v>-10.94846570204138</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.192775236227515</v>
+        <v>-1.217988529679153</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.712603643960604</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.83341695444348</v>
+        <v>-10.89645018807257</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.16797869495359</v>
+        <v>-1.193191988405227</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.712603643960604</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.9750887961676</v>
+        <v>-11.03812202979669</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.226122658541979</v>
+        <v>-1.251335951993616</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.712603643960604</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.92549795174276</v>
+        <v>-10.98853118537185</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.191232910607174</v>
+        <v>-1.216446204058811</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.663012799535771</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.72634584450566</v>
+        <v>-10.78937907813476</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.124623201359017</v>
+        <v>-1.149836494810654</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.497690273585957</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.50050069178625</v>
+        <v>-10.56353392541535</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.024706067235044</v>
+        <v>-1.049919360686681</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.455763597998794</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282097</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.37592203544866</v>
+        <v>-10.43895526907775</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9737354601439487</v>
+        <v>-0.998948753595585</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.455763597998794</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116211</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.42881732349295</v>
+        <v>-10.49185055712204</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9922598011995554</v>
+        <v>-1.017473094651193</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.450808251910348</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081562</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.1449085925642</v>
+        <v>-10.20794182619329</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8729626045894197</v>
+        <v>-0.8981758980410559</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.450808251910348</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425322</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.07354219995455</v>
+        <v>-10.13657543358364</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8541533099394254</v>
+        <v>-0.8793666033910625</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.379441859300699</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702406</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.809705332750482</v>
+        <v>-9.872738566379574</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7585020443707053</v>
+        <v>-0.783715337822342</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.379441859300699</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906222</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.542463531882085</v>
+        <v>-9.605496765511177</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6534398845227201</v>
+        <v>-0.6786531779743568</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.379441859300699</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781941</v>
+        <v>3.784680945781943</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.444556493205594</v>
+        <v>-9.507589726834686</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6145773840255848</v>
+        <v>-0.6397906774772215</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.311456109440143</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567235</v>
+        <v>3.800825778567237</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.420602952229636</v>
+        <v>-9.483636185858728</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6043274614897078</v>
+        <v>-0.6295407549413445</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.287502568464185</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487764</v>
+        <v>3.789307536487766</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.156543013906839</v>
+        <v>-9.219576247535931</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5119638023223412</v>
+        <v>-0.5371770957739779</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.023442630141389</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309719</v>
+        <v>3.833249172309721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.449463390402002</v>
+        <v>-8.512496624031094</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2319189865807072</v>
+        <v>-0.2571322800323439</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.023442630141389</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858722</v>
+        <v>3.839370871858724</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.409279092035812</v>
+        <v>-8.472312325664904</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2155016433463897</v>
+        <v>-0.2407149367980264</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.983258331775199</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096467</v>
+        <v>3.856158176096469</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.329209296498007</v>
+        <v>-8.392242530127099</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1841069039105108</v>
+        <v>-0.2093201973621479</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.903188536237395</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761805</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.095728074268408</v>
+        <v>-8.1587613078975</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.08278998618081879</v>
+        <v>-0.1080032796324555</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.669707314007796</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.946061683260893</v>
+        <v>-8.009094916889985</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.02581564009077209</v>
+        <v>-0.05102893354240923</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.57680382276526</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.813786209630006</v>
+        <v>-7.876819443259099</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.02246203610860986</v>
+        <v>-0.00275125734302728</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.444528349134373</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.623186534956853</v>
+        <v>-7.686219768585946</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1015169666655074</v>
+        <v>0.07630367321387022</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.253928674461221</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430985</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.374186736273272</v>
+        <v>-7.437219969902365</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2140232273625986</v>
+        <v>0.1888099339109615</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.253928674461221</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077641</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.479776726046377</v>
+        <v>-7.54280995967547</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.04381130185413795</v>
+        <v>0.01859800840250081</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.359518664234325</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457897</v>
+        <v>3.770419008457899</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.498511628164974</v>
+        <v>-7.561544861794067</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.08486168288378559</v>
+        <v>0.05964838943214845</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.359518664234325</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180806</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.350571586757375</v>
+        <v>-7.413604820386468</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.02415877675865774</v>
+        <v>-0.001054516692979401</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.339197748325767</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879199</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.326342950368402</v>
+        <v>-7.389376183997495</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.02513624506076884</v>
+        <v>-7.704839086830617e-05</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.314969111936795</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568104</v>
+        <v>3.729966140568106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.282794543597712</v>
+        <v>-7.345827777226805</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.03559499567395186</v>
+        <v>0.01038170222231471</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.314969111936795</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963416</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.040646150143854</v>
+        <v>-7.103679383772946</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1469167074366382</v>
+        <v>0.1217034139850011</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.314969111936795</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192814</v>
+        <v>3.828547911192816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.977416778375505</v>
+        <v>-7.040450012004598</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1667405766031722</v>
+        <v>0.1415272831515351</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.314969111936795</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262044</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.854125643558374</v>
+        <v>-6.917158877187467</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2135551245406018</v>
+        <v>0.1883418310889646</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.191677977119665</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.832976444654931</v>
+        <v>-6.896009678284024</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2297157823393041</v>
+        <v>0.204502488887667</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.170528778216221</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788091</v>
+        <v>3.748324832788093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.589211002671487</v>
+        <v>-6.65224423630058</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3230026674797326</v>
+        <v>0.2977893740280955</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.170528778216221</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527522</v>
+        <v>3.824307657527524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.442313974953617</v>
+        <v>-6.505347208582709</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3838857924868964</v>
+        <v>0.3586724990352597</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.122870536237633</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749179</v>
+        <v>3.826351398749181</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.192463581004542</v>
+        <v>-6.255496814633634</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4765680250502284</v>
+        <v>0.4513547315985917</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.122870536237633</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481492</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.01657148853711</v>
+        <v>-6.079604722166202</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5505239855578501</v>
+        <v>0.5253106921062134</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.122870536237633</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862981</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.845125025514647</v>
+        <v>-5.908158259143739</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6324300768213891</v>
+        <v>0.6072167833697524</v>
       </c>
       <c r="F1921" t="n">
         <v>-0.9514240732151701</v>
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102774</v>
+        <v>3.773761647102777</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.838350069223328</v>
+        <v>-5.683125259474916</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6341605369542136</v>
+        <v>0.6962504608535784</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.9446491169238513</v>
+        <v>-0.7263910735463472</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.403067518802982</v>
+        <v>2.534022344829484</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353066</v>
+        <v>3.764614304353069</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.774714326989393</v>
+        <v>-5.619489517240981</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6643096349021049</v>
+        <v>0.7263995588014698</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.8810133746899168</v>
+        <v>-0.6627553313124127</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.44594376519766</v>
+        <v>2.576898591224162</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544775</v>
+        <v>3.798811195544777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.681714285783495</v>
+        <v>-5.526489476035083</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6827039101682599</v>
+        <v>0.7447938340676243</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.8810133746899168</v>
+        <v>-0.6627553313124127</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.427138023981455</v>
+        <v>2.558092850007958</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712285</v>
+        <v>3.797691308712287</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.441283788978635</v>
+        <v>-5.286058979230223</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7806191855150812</v>
+        <v>0.8427091094144461</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.6405828778850565</v>
+        <v>-0.4223248345075524</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.573139398689249</v>
+        <v>2.704094224715751</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837675</v>
+        <v>3.821589933837677</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.36904122080744</v>
+        <v>-5.213816411059028</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8134455266183793</v>
+        <v>0.8755354505177442</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.6405828778850565</v>
+        <v>-0.4223248345075524</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.577068712524069</v>
+        <v>2.708023538550572</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349958</v>
+        <v>3.822323422349959</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.253101371182255</v>
+        <v>-5.097876561433843</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8605000503857934</v>
+        <v>0.9225899742851582</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.5637611468689326</v>
+        <v>-0.3455031034914285</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.623840335051083</v>
+        <v>2.754795161077586</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.144296485702528</v>
+        <v>-4.989071675954116</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9010200757976778</v>
+        <v>0.9631099996970425</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.5637611468689326</v>
+        <v>-0.3455031034914285</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.620838406271077</v>
+        <v>2.751793232297579</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.924275687665517</v>
+        <v>-4.769050877917105</v>
       </c>
       <c r="E1929" t="n">
-        <v>0.9906074320230962</v>
+        <v>1.052697355922461</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.4225413018009524</v>
+        <v>-0.2042832584234483</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.707149350322479</v>
+        <v>2.838104176348982</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.79140799860224</v>
+        <v>-4.636183188853828</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.05964869045023</v>
+        <v>1.121738614349595</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.4225413018009524</v>
+        <v>-0.2042832584234483</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.723043533124303</v>
+        <v>2.853998359150805</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.63189289508287</v>
+        <v>-4.476668085334458</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.12460057629828</v>
+        <v>1.186690500197645</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.2630261982815825</v>
+        <v>-0.04476815490407837</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.819898439676226</v>
+        <v>2.950853265702729</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.487220749983132</v>
+        <v>-4.33199594023472</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.192557536899615</v>
+        <v>1.25464746079898</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.1183540531818451</v>
+        <v>0.09990399019565904</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.916789829297509</v>
+        <v>3.047744655324011</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.547095577340825</v>
+        <v>-4.391870767592413</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.154645097357964</v>
+        <v>1.216735021257329</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.1782288805395372</v>
+        <v>0.04002916283796693</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.866902424284319</v>
+        <v>2.997857250310822</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.460296079561816</v>
+        <v>-4.305071269813403</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.211765389792133</v>
+        <v>1.273855313691499</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.1782288805395372</v>
+        <v>0.04002916283796693</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.889302917606885</v>
+        <v>3.020257743633388</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.462765786023622</v>
+        <v>-4.307540976275209</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.210849908580823</v>
+        <v>1.272939832480188</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1806985870013433</v>
+        <v>0.03755945637616076</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.887893495103214</v>
+        <v>3.018848321129716</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.531135972347633</v>
+        <v>-4.37591116259922</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.194508756525921</v>
+        <v>1.256598680425286</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.1714228879651284</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.904465836999645</v>
+        <v>3.035420663026147</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.639674153263766</v>
+        <v>-4.484449343515354</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.141530192791359</v>
+        <v>1.203620116690724</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.1714228879651284</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.894902545631536</v>
+        <v>3.025857371658038</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887697</v>
+        <v>3.710903155887696</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.670667312592472</v>
+        <v>-4.515442502844059</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9538424941002634</v>
+        <v>1.015932417999629</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.1714228879651284</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.719612110671923</v>
+        <v>2.850566936698425</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675892</v>
+        <v>3.746038950675891</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.495193052800003</v>
+        <v>-4.33996824305159</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.028599430009039</v>
+        <v>1.090689353908404</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.1714228879651284</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.724179342663711</v>
+        <v>2.855134168690213</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695438</v>
+        <v>3.765020747695437</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.606129305441252</v>
+        <v>-4.450904495692839</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9599669577137462</v>
+        <v>1.022056881613111</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.1714228879651284</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.699921371424918</v>
+        <v>2.83087619745142</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.809155882984485</v>
+        <v>-4.653931073236072</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8818877119163586</v>
+        <v>0.9439776358157237</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.3744494655083618</v>
+        <v>-0.1561914221308577</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.581236810118883</v>
+        <v>2.712191636145385</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.651230284049192</v>
+        <v>-4.496005474300779</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9552303379226081</v>
+        <v>1.017320261821973</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.3744494655083618</v>
+        <v>-0.1561914221308577</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.591409196551016</v>
+        <v>2.722364022577518</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.564986821022814</v>
+        <v>-4.409762011274402</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9846739937070195</v>
+        <v>1.046763917606385</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.3744494655083618</v>
+        <v>-0.1561914221308577</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.586355467124876</v>
+        <v>2.717310293151378</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.566169905673876</v>
+        <v>-4.410945095925463</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9759765352911205</v>
+        <v>1.038066459190486</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.3800925139748733</v>
+        <v>-0.1618344705973692</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.574745413489494</v>
+        <v>2.705700239515997</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.443042198679793</v>
+        <v>-4.28781738893138</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.025779491121855</v>
+        <v>1.08786941502122</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.3800925139748733</v>
+        <v>-0.1618344705973692</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.575297286522596</v>
+        <v>2.706252112549099</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.350231717228933</v>
+        <v>-4.19500690748052</v>
       </c>
       <c r="E1946" t="n">
-        <v>0.9921763755935649</v>
+        <v>1.05426629949293</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.287282032524014</v>
+        <v>-0.06902398914650987</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.560256267284477</v>
+        <v>2.691211093310979</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.301668665007903</v>
+        <v>-4.14644385525949</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.013475072406578</v>
+        <v>1.075564996305943</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.2387189803029838</v>
+        <v>-0.02046093692547968</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.591267574541696</v>
+        <v>2.722222400568199</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.188997446771653</v>
+        <v>-4.03377263702324</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.053619268212801</v>
+        <v>1.115709192112166</v>
       </c>
       <c r="F1948" t="n">
-        <v>-0.1260477620667336</v>
+        <v>0.09221028131077053</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.653946013995169</v>
+        <v>2.784900840021672</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.07662044558898</v>
+        <v>-3.921395635840568</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.104061364516537</v>
+        <v>1.166151288415902</v>
       </c>
       <c r="F1949" t="n">
-        <v>-0.1260477620667336</v>
+        <v>0.09221028131077053</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.659437309825837</v>
+        <v>2.790392135852339</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.274855014475711</v>
+        <v>-4.119630204727298</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.036264738730384</v>
+        <v>1.098354662629749</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.3242823309534641</v>
+        <v>-0.1060242875759601</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.551993770262337</v>
+        <v>2.68294859628884</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.35785629550099</v>
+        <v>-4.202631485752577</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8414199463209255</v>
+        <v>0.9035098702202906</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.3428532154806379</v>
+        <v>-0.1245951721031338</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.379206959546686</v>
+        <v>2.510161785573189</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.484923301807978</v>
+        <v>-4.329698492059565</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9107428045173358</v>
+        <v>0.9728327284167011</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.3428532154806379</v>
+        <v>-0.1245951721031338</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.499356620265892</v>
+        <v>2.630311446292394</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660762</v>
+        <v>3.733008865660763</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.571521884789081</v>
+        <v>-4.387049612219795</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.8906163974272177</v>
+        <v>0.9644053064549321</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.3428532154806379</v>
+        <v>-0.1245951721031338</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.513869646368215</v>
+        <v>2.644824472394717</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383417</v>
+        <v>3.741170494383418</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.53313822223093</v>
+        <v>-4.348665949661644</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9033893037928469</v>
+        <v>0.9771782128205611</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.3044695529224867</v>
+        <v>-0.08621150954498263</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.534319285245474</v>
+        <v>2.665274111271977</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.356021892195764</v>
+        <v>-4.171549619626478</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9709648646522151</v>
+        <v>1.044753773679929</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.3044695529224867</v>
+        <v>-0.08621150954498263</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.531048314090776</v>
+        <v>2.662003140117279</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.32631976821947</v>
+        <v>-4.141847495650184</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.9835291060046458</v>
+        <v>1.05731801503236</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.3089396781378001</v>
+        <v>-0.090681634760296</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.529049630723501</v>
+        <v>2.660004456750004</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.146944346980702</v>
+        <v>-3.962472074411417</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.049066249806567</v>
+        <v>1.122855158834281</v>
       </c>
       <c r="F1957" t="n">
-        <v>-0.1521629199670814</v>
+        <v>0.06609512341042267</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.616902660932347</v>
+        <v>2.747857486958849</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452223</v>
+        <v>3.716988143452222</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.191958560501309</v>
+        <v>-4.007486287932023</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.011868019729914</v>
+        <v>1.085656928757629</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.182511815281686</v>
+        <v>0.03574622809581807</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.579500779075174</v>
+        <v>2.710455605101676</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702303297953</v>
+        <v>3.737023032979529</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.458963070773744</v>
+        <v>-4.274490798204459</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9107577779598861</v>
+        <v>0.9845466869876003</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.3768748533246346</v>
+        <v>-0.1586168099471305</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.46857451858835</v>
+        <v>2.599529344614853</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230805</v>
+        <v>3.702305879230804</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.747750291232659</v>
+        <v>-4.563278018663374</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.7944468116728214</v>
+        <v>0.8682357207005356</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.477960973423635</v>
+        <v>-0.2597029300461309</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.407126768425452</v>
+        <v>2.538081594451954</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.70556808628545</v>
+        <v>3.705568086285449</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.715274705061887</v>
+        <v>-4.530802432492602</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8050370076954469</v>
+        <v>0.8788259167231613</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.477960973423635</v>
+        <v>-0.2597029300461309</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.404726729979768</v>
+        <v>2.535681556006271</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.69623657735459</v>
+        <v>-4.511764304785305</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8091769779866107</v>
+        <v>0.8829658870143251</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.5361445847548295</v>
+        <v>-0.3178865413773254</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.366341282389297</v>
+        <v>2.497296108415799</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106089760125</v>
+        <v>3.731060897601248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.727363208505208</v>
+        <v>-4.542890935935923</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.974308194465044</v>
+        <v>1.048097103492758</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.5361445847548295</v>
+        <v>-0.3178865413773254</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.543923151327977</v>
+        <v>2.67487797735448</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537861</v>
+        <v>3.722443786537859</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.779683589106</v>
+        <v>-4.595211316536715</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9542133712108609</v>
+        <v>1.028002280238575</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.5011977247459574</v>
+        <v>-0.2829396813684533</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.565724596319434</v>
+        <v>2.696679422345936</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259117</v>
+        <v>3.787422005259115</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.924006495030919</v>
+        <v>-4.739534222461634</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9024927392378193</v>
+        <v>0.9762816482655334</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.5011977247459574</v>
+        <v>-0.2829396813684533</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.57173312671636</v>
+        <v>2.702687952742862</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989902</v>
+        <v>3.781497674989899</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.776263524795916</v>
+        <v>-4.591791252226631</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.040742575123842</v>
+        <v>1.114531484151557</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3333903675110742</v>
+        <v>-0.1151323241335701</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.751570188849312</v>
+        <v>2.882525014875814</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651164</v>
+        <v>3.802242353651161</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.878278207327138</v>
+        <v>-4.693805934757853</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.002730323642835</v>
+        <v>1.076519232670549</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3333903675110742</v>
+        <v>-0.1151323241335701</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.754363810380793</v>
+        <v>2.885318636407295</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864723</v>
+        <v>3.805605409864721</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.741668863233045</v>
+        <v>-4.55719659066376</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.05803640967213</v>
+        <v>1.131825318699844</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1967810234169817</v>
+        <v>0.02147701996052237</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.836991765228906</v>
+        <v>2.967946591255409</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823621936061</v>
+        <v>3.798236219360607</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.884434196055695</v>
+        <v>-4.69996192348641</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.00001075328318</v>
+        <v>1.073799662310895</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3395463562396321</v>
+        <v>-0.121288312862128</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.750413042275427</v>
+        <v>2.881367868301929</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.86735906126842</v>
+        <v>3.867359061268418</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.822136197279573</v>
+        <v>-4.637663924710288</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.09126550659045</v>
+        <v>1.165054415618164</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3395463562396321</v>
+        <v>-0.121288312862128</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.816748596072247</v>
+        <v>2.94770342209875</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.45824391493612</v>
+        <v>3.796130164008313</v>
       </c>
       <c r="C1971" t="n">
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.333903580743762</v>
+        <v>-4.449892898349184</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9951394255941723</v>
+        <v>0.9487436985520041</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.1391395362430771</v>
+        <v>0.1477204746223392</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.812541003951271</v>
+        <v>2.817689566978828</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240522.xlsx
+++ b/tame_output/ON/bt/strategyON_20240522.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.9%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>68.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.2%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>19.4%</t>
         </is>
       </c>
     </row>
@@ -844,17 +844,17 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>40.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>27.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.1%</t>
+          <t>-78.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.0%</t>
+          <t>109.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.7%</t>
+          <t>128.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-671.7%</t>
+          <t>-665.4%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.5%</t>
+          <t>-52.1%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-74.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.2%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>449.2%</t>
+          <t>445.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-606.6%</t>
+          <t>-622.5%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-269.1%</t>
+          <t>-266.5%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.9%</t>
+          <t>-39.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-26.5%</t>
+          <t>-23.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>49.4%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-281.3%</t>
+          <t>-287.7%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-21.6%</t>
+          <t>-25.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>68.2%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-0.37</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>69.3%</t>
+          <t>66.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.7%</t>
+          <t>-30.0%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-14.3%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.7%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-213.6%</t>
+          <t>-208.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-209.2%</t>
+          <t>-236.9%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.4%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.0%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1461,17 +1461,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-25.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.7%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.0%</t>
+          <t>-14.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-164.3%</t>
+          <t>-180.8%</t>
         </is>
       </c>
     </row>
@@ -44279,16 +44279,16 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178241</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.434725892533942</v>
+        <v>-4.371692658904851</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.363491865236055</v>
+        <v>1.388705158687692</v>
       </c>
       <c r="F1858" t="n">
         <v>-0.555734532842116</v>
@@ -44308,10 +44308,10 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.86653168568373</v>
+        <v>-4.803498452054638</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.177102435443545</v>
+        <v>1.202315728895181</v>
       </c>
       <c r="F1859" t="n">
         <v>-0.692152029283383</v>
@@ -44325,16 +44325,16 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.101225679816282</v>
+        <v>-5.038192446187191</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.071509612792615</v>
+        <v>1.096722906244251</v>
       </c>
       <c r="F1860" t="n">
         <v>-0.6858157620541279</v>
@@ -44354,10 +44354,10 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.436888327046734</v>
+        <v>-5.373855093417643</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9358251455563988</v>
+        <v>0.9610384390080351</v>
       </c>
       <c r="F1861" t="n">
         <v>-0.6858157620541279</v>
@@ -44377,10 +44377,10 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.800514571947048</v>
+        <v>-5.737481338317957</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.796862207830515</v>
+        <v>0.8220755012821512</v>
       </c>
       <c r="F1862" t="n">
         <v>-0.7840373989212537</v>
@@ -44400,10 +44400,10 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.165641954585794</v>
+        <v>-6.102608720956703</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6500657697808476</v>
+        <v>0.6752790632324839</v>
       </c>
       <c r="F1863" t="n">
         <v>-1.080348183220266</v>
@@ -44423,10 +44423,10 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.574230731766473</v>
+        <v>-6.511197498137381</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4853918029233348</v>
+        <v>0.510605096374972</v>
       </c>
       <c r="F1864" t="n">
         <v>-1.488936960400945</v>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.850806832082306</v>
+        <v>-6.787773598453214</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3699467952684627</v>
+        <v>0.3951600887200994</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.488936960400945</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.267198706369303</v>
+        <v>-7.204165472740211</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.201384096162541</v>
+        <v>0.2265973896141777</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.488936960400945</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.643875716899148</v>
+        <v>-7.580842483270056</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.06097198261928227</v>
+        <v>0.08618527607091897</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.488936960400945</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.989750538883957</v>
+        <v>-7.926717305254865</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.08127838102894636</v>
+        <v>-0.05606508757730966</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.488936960400945</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.153330417068341</v>
+        <v>-8.090297183439249</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1483054122476992</v>
+        <v>-0.1230921187960621</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.488936960400945</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.449991758878539</v>
+        <v>-8.386958525249447</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2631909730425703</v>
+        <v>-0.2379776795909332</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.557680096134823</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.573236148093969</v>
+        <v>-8.510202914464877</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.316515033263145</v>
+        <v>-0.2913017398115083</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
@@ -44601,16 +44601,16 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297746</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.9562375368366</v>
+        <v>-8.893204303207508</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4698176900817814</v>
+        <v>-0.4446043966301447</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
@@ -44624,16 +44624,16 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.113636417049721</v>
+        <v>-9.050603183420629</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5302057261955997</v>
+        <v>-0.504992432743963</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.715078976347944</v>
@@ -44647,16 +44647,16 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.473166739553722</v>
+        <v>-9.41013350592463</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6686675518991501</v>
+        <v>-0.6434542584475134</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.715078976347944</v>
@@ -44670,16 +44670,16 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.523515803007944</v>
+        <v>-9.460482569378852</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6808911573236616</v>
+        <v>-0.6556778638720249</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.765428039802166</v>
@@ -44693,16 +44693,16 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776674</v>
+        <v>3.500446096776673</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.62113508042934</v>
+        <v>-9.558101846800248</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7168971176704511</v>
+        <v>-0.6916838242188144</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.863047317223563</v>
@@ -44716,16 +44716,16 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.61744415547293</v>
+        <v>-9.554410921843838</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7154207476878867</v>
+        <v>-0.69020745423625</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.863047317223563</v>
@@ -44739,16 +44739,16 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.821702330802793</v>
+        <v>-9.758669097173701</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.79161082070119</v>
+        <v>-0.7663975272495529</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.990686261837552</v>
@@ -44762,16 +44762,16 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.03974010243397</v>
+        <v>-9.976706868804879</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8743433748692246</v>
+        <v>-0.8491300814175879</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.165457029933451</v>
@@ -44785,16 +44785,16 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.966270270766522</v>
+        <v>-9.90323703713743</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.829583740708824</v>
+        <v>-0.8043704472571873</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.091987198266002</v>
@@ -44808,16 +44808,16 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.14139468815307</v>
+        <v>-10.07836145452397</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8850782869159248</v>
+        <v>-0.8598649934642877</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.267111615652546</v>
@@ -44831,16 +44831,16 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.37584678216755</v>
+        <v>-10.31281354853846</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9860782894233169</v>
+        <v>-0.9608649959716797</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.267111615652546</v>
@@ -44854,16 +44854,16 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.66365062670479</v>
+        <v>-10.6006173930757</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.107872018012188</v>
+        <v>-1.082658724560551</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.554915460189784</v>
@@ -44877,16 +44877,16 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.71643678230512</v>
+        <v>-10.65340354867603</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.127870690413762</v>
+        <v>-1.102657396962126</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.650590946772181</v>
@@ -44900,16 +44900,16 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.94846570204138</v>
+        <v>-10.88543246841229</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.217988529679153</v>
+        <v>-1.192775236227515</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.712603643960604</v>
@@ -44923,16 +44923,16 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.89645018807257</v>
+        <v>-10.83341695444348</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.193191988405227</v>
+        <v>-1.16797869495359</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.712603643960604</v>
@@ -44946,16 +44946,16 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.03812202979669</v>
+        <v>-10.9750887961676</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.251335951993616</v>
+        <v>-1.226122658541979</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.712603643960604</v>
@@ -44969,16 +44969,16 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.98853118537185</v>
+        <v>-10.92549795174276</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.216446204058811</v>
+        <v>-1.191232910607174</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.663012799535771</v>
@@ -44992,16 +44992,16 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.78937907813476</v>
+        <v>-10.72634584450566</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.149836494810654</v>
+        <v>-1.124623201359017</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.497690273585957</v>
@@ -45015,16 +45015,16 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.56353392541535</v>
+        <v>-10.50050069178625</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.049919360686681</v>
+        <v>-1.024706067235044</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.455763597998794</v>
@@ -45038,16 +45038,16 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282097</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.43895526907775</v>
+        <v>-10.37592203544866</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.998948753595585</v>
+        <v>-0.9737354601439487</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.455763597998794</v>
@@ -45061,16 +45061,16 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116211</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.49185055712204</v>
+        <v>-10.42881732349295</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.017473094651193</v>
+        <v>-0.9922598011995554</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.450808251910348</v>
@@ -45084,16 +45084,16 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081562</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.20794182619329</v>
+        <v>-10.1449085925642</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8981758980410559</v>
+        <v>-0.8729626045894197</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.450808251910348</v>
@@ -45107,16 +45107,16 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425322</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.13657543358364</v>
+        <v>-10.07354219995455</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8793666033910625</v>
+        <v>-0.8541533099394254</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.379441859300699</v>
@@ -45130,16 +45130,16 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702406</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.872738566379574</v>
+        <v>-9.809705332750482</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.783715337822342</v>
+        <v>-0.7585020443707053</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.379441859300699</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906222</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.605496765511177</v>
+        <v>-9.542463531882085</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6786531779743568</v>
+        <v>-0.6534398845227201</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.379441859300699</v>
@@ -45176,16 +45176,16 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781943</v>
+        <v>3.784680945781941</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.507589726834686</v>
+        <v>-9.444556493205594</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6397906774772215</v>
+        <v>-0.6145773840255848</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.311456109440143</v>
@@ -45199,16 +45199,16 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567237</v>
+        <v>3.800825778567235</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.483636185858728</v>
+        <v>-9.420602952229636</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6295407549413445</v>
+        <v>-0.6043274614897078</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.287502568464185</v>
@@ -45222,16 +45222,16 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487766</v>
+        <v>3.789307536487764</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.219576247535931</v>
+        <v>-9.156543013906839</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5371770957739779</v>
+        <v>-0.5119638023223412</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.023442630141389</v>
@@ -45245,16 +45245,16 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309721</v>
+        <v>3.833249172309719</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.512496624031094</v>
+        <v>-8.449463390402002</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2571322800323439</v>
+        <v>-0.2319189865807072</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.023442630141389</v>
@@ -45268,16 +45268,16 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858724</v>
+        <v>3.839370871858722</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.472312325664904</v>
+        <v>-8.409279092035812</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2407149367980264</v>
+        <v>-0.2155016433463897</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.983258331775199</v>
@@ -45291,16 +45291,16 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096469</v>
+        <v>3.856158176096467</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.392242530127099</v>
+        <v>-8.329209296498007</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2093201973621479</v>
+        <v>-0.1841069039105108</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.903188536237395</v>
@@ -45314,16 +45314,16 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.787326853761805</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.1587613078975</v>
+        <v>-8.095728074268408</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1080032796324555</v>
+        <v>-0.08278998618081879</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.669707314007796</v>
@@ -45337,16 +45337,16 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.009094916889985</v>
+        <v>-7.946061683260893</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.05102893354240923</v>
+        <v>-0.02581564009077209</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.57680382276526</v>
@@ -45360,16 +45360,16 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.876819443259099</v>
+        <v>-7.813786209630006</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.00275125734302728</v>
+        <v>0.02246203610860986</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.444528349134373</v>
@@ -45383,16 +45383,16 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575952</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.686219768585946</v>
+        <v>-7.623186534956853</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.07630367321387022</v>
+        <v>0.1015169666655074</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.253928674461221</v>
@@ -45406,16 +45406,16 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.437219969902365</v>
+        <v>-7.374186736273272</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1888099339109615</v>
+        <v>0.2140232273625986</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.253928674461221</v>
@@ -45429,16 +45429,16 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077641</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.54280995967547</v>
+        <v>-7.479776726046377</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.01859800840250081</v>
+        <v>0.04381130185413795</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.359518664234325</v>
@@ -45452,16 +45452,16 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457899</v>
+        <v>3.770419008457897</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.561544861794067</v>
+        <v>-7.498511628164974</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.05964838943214845</v>
+        <v>0.08486168288378559</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.359518664234325</v>
@@ -45475,16 +45475,16 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180806</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.413604820386468</v>
+        <v>-7.350571586757375</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.001054516692979401</v>
+        <v>0.02415877675865774</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.339197748325767</v>
@@ -45498,16 +45498,16 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879199</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.389376183997495</v>
+        <v>-7.326342950368402</v>
       </c>
       <c r="E1911" t="n">
-        <v>-7.704839086830617e-05</v>
+        <v>0.02513624506076884</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.314969111936795</v>
@@ -45521,16 +45521,16 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568106</v>
+        <v>3.729966140568104</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.345827777226805</v>
+        <v>-7.282794543597712</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.01038170222231471</v>
+        <v>0.03559499567395186</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.314969111936795</v>
@@ -45544,16 +45544,16 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963416</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.103679383772946</v>
+        <v>-7.040646150143854</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1217034139850011</v>
+        <v>0.1469167074366382</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.314969111936795</v>
@@ -45567,16 +45567,16 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192816</v>
+        <v>3.828547911192814</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.040450012004598</v>
+        <v>-6.977416778375505</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1415272831515351</v>
+        <v>0.1667405766031722</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.314969111936795</v>
@@ -45590,16 +45590,16 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262044</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.917158877187467</v>
+        <v>-6.854125643558374</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1883418310889646</v>
+        <v>0.2135551245406018</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.191677977119665</v>
@@ -45613,16 +45613,16 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389908</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.896009678284024</v>
+        <v>-6.832976444654931</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.204502488887667</v>
+        <v>0.2297157823393041</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.170528778216221</v>
@@ -45636,16 +45636,16 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788093</v>
+        <v>3.748324832788091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.65224423630058</v>
+        <v>-6.589211002671487</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2977893740280955</v>
+        <v>0.3230026674797326</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.170528778216221</v>
@@ -45659,16 +45659,16 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527524</v>
+        <v>3.824307657527522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.505347208582709</v>
+        <v>-6.442313974953617</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3586724990352597</v>
+        <v>0.3838857924868964</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.122870536237633</v>
@@ -45682,16 +45682,16 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749181</v>
+        <v>3.826351398749179</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.255496814633634</v>
+        <v>-6.192463581004542</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4513547315985917</v>
+        <v>0.4765680250502284</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.122870536237633</v>
@@ -45705,16 +45705,16 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481492</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.079604722166202</v>
+        <v>-6.01657148853711</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5253106921062134</v>
+        <v>0.5505239855578501</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.122870536237633</v>
@@ -45728,16 +45728,16 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862982</v>
+        <v>3.780930335862981</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.908158259143739</v>
+        <v>-5.845125025514647</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6072167833697524</v>
+        <v>0.6324300768213891</v>
       </c>
       <c r="F1921" t="n">
         <v>-0.9514240732151701</v>
@@ -45751,16 +45751,16 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102777</v>
+        <v>3.773761647102774</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.683125259474916</v>
+        <v>-5.620092025845824</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6962504608535784</v>
+        <v>0.7214637543052151</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.7263910735463472</v>
@@ -45774,16 +45774,16 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353069</v>
+        <v>3.764614304353066</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.619489517240981</v>
+        <v>-5.556456283611889</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7263995588014698</v>
+        <v>0.7516128522531065</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.6627553313124127</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.798811195544775</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.526489476035083</v>
+        <v>-5.463456242405991</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7447938340676243</v>
+        <v>0.7700071275192615</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.6627553313124127</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712287</v>
+        <v>3.797691308712285</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.286058979230223</v>
+        <v>-5.223025745601131</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8427091094144461</v>
+        <v>0.8679224028660828</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.4223248345075524</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837677</v>
+        <v>3.821589933837675</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.213816411059028</v>
+        <v>-5.150783177429936</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8755354505177442</v>
+        <v>0.9007487439693809</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.4223248345075524</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349959</v>
+        <v>3.822323422349958</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.097876561433843</v>
+        <v>-5.034843327804751</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9225899742851582</v>
+        <v>0.9478032677367949</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.3455031034914285</v>
@@ -45895,10 +45895,10 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.989071675954116</v>
+        <v>-4.926038442325024</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9631099996970425</v>
+        <v>0.9883232931486794</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.3455031034914285</v>
@@ -45918,10 +45918,10 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.769050877917105</v>
+        <v>-4.706017644288013</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.052697355922461</v>
+        <v>1.077910649374098</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.2042832584234483</v>
@@ -45941,10 +45941,10 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.636183188853828</v>
+        <v>-4.573149955224736</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.121738614349595</v>
+        <v>1.146951907801232</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.2042832584234483</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.476668085334458</v>
+        <v>-4.413634851705366</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.186690500197645</v>
+        <v>1.211903793649282</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.04476815490407837</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.33199594023472</v>
+        <v>-4.268962706605628</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.25464746079898</v>
+        <v>1.279860754250617</v>
       </c>
       <c r="F1932" t="n">
         <v>0.09990399019565904</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.391870767592413</v>
+        <v>-4.328837533963321</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.216735021257329</v>
+        <v>1.241948314708966</v>
       </c>
       <c r="F1933" t="n">
         <v>0.04002916283796693</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.305071269813403</v>
+        <v>-4.242038036184312</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.273855313691499</v>
+        <v>1.299068607143135</v>
       </c>
       <c r="F1934" t="n">
         <v>0.04002916283796693</v>
@@ -46056,10 +46056,10 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.307540976275209</v>
+        <v>-4.244507742646118</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.272939832480188</v>
+        <v>1.298153125931825</v>
       </c>
       <c r="F1935" t="n">
         <v>0.03755945637616076</v>
@@ -46079,10 +46079,10 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.37591116259922</v>
+        <v>-4.312877928970128</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.256598680425286</v>
+        <v>1.281811973876923</v>
       </c>
       <c r="F1936" t="n">
         <v>0.04683515541237571</v>
@@ -46102,10 +46102,10 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.484449343515354</v>
+        <v>-4.421416109886262</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.203620116690724</v>
+        <v>1.228833410142361</v>
       </c>
       <c r="F1937" t="n">
         <v>0.04683515541237571</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887696</v>
+        <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.515442502844059</v>
+        <v>-4.452409269214967</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.015932417999629</v>
+        <v>1.041145711451265</v>
       </c>
       <c r="F1938" t="n">
         <v>0.04683515541237571</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675891</v>
+        <v>3.746038950675892</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.33996824305159</v>
+        <v>-4.276935009422498</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.090689353908404</v>
+        <v>1.115902647360041</v>
       </c>
       <c r="F1939" t="n">
         <v>0.04683515541237571</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695437</v>
+        <v>3.765020747695438</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.450904495692839</v>
+        <v>-4.387871262063747</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.022056881613111</v>
+        <v>1.047270175064748</v>
       </c>
       <c r="F1940" t="n">
         <v>0.04683515541237571</v>
@@ -46194,10 +46194,10 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.653931073236072</v>
+        <v>-4.59089783960698</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9439776358157237</v>
+        <v>0.9691909292673604</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.1561914221308577</v>
@@ -46217,10 +46217,10 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.496005474300779</v>
+        <v>-4.432972240671687</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.017320261821973</v>
+        <v>1.04253355527361</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.1561914221308577</v>
@@ -46240,10 +46240,10 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.409762011274402</v>
+        <v>-4.34672877764531</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.046763917606385</v>
+        <v>1.071977211058021</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.1561914221308577</v>
@@ -46263,10 +46263,10 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.410945095925463</v>
+        <v>-4.347911862296371</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.038066459190486</v>
+        <v>1.063279752642122</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.1618344705973692</v>
@@ -46286,10 +46286,10 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.28781738893138</v>
+        <v>-4.224784155302288</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.08786941502122</v>
+        <v>1.113082708472857</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.1618344705973692</v>
@@ -46309,10 +46309,10 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.19500690748052</v>
+        <v>-4.131973673851428</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.05426629949293</v>
+        <v>1.079479592944567</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.06902398914650987</v>
@@ -46332,10 +46332,10 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.14644385525949</v>
+        <v>-4.083410621630398</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.075564996305943</v>
+        <v>1.10077828975758</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.02046093692547968</v>
@@ -46355,10 +46355,10 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.03377263702324</v>
+        <v>-3.970739403394148</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.115709192112166</v>
+        <v>1.140922485563802</v>
       </c>
       <c r="F1948" t="n">
         <v>0.09221028131077053</v>
@@ -46378,10 +46378,10 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.921395635840568</v>
+        <v>-3.858362402211476</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.166151288415902</v>
+        <v>1.191364581867539</v>
       </c>
       <c r="F1949" t="n">
         <v>0.09221028131077053</v>
@@ -46401,10 +46401,10 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.119630204727298</v>
+        <v>-4.056596971098206</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.098354662629749</v>
+        <v>1.123567956081386</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.1060242875759601</v>
@@ -46424,10 +46424,10 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.202631485752577</v>
+        <v>-4.139598252123485</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9035098702202906</v>
+        <v>0.9287231636719273</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.1245951721031338</v>
@@ -46447,10 +46447,10 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.329698492059565</v>
+        <v>-4.266665258430473</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9728327284167011</v>
+        <v>0.9980460218683378</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.1245951721031338</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660763</v>
+        <v>3.733008865660762</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.387049612219795</v>
+        <v>-4.353263841411576</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9644053064549321</v>
+        <v>0.9779196147782196</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.1245951721031338</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383418</v>
+        <v>3.741170494383417</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.348665949661644</v>
+        <v>-4.314880178853425</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9771782128205611</v>
+        <v>0.9906925211438486</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.08621150954498263</v>
@@ -46516,10 +46516,10 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.171549619626478</v>
+        <v>-4.137763848818259</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.044753773679929</v>
+        <v>1.058268082003217</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.08621150954498263</v>
@@ -46539,10 +46539,10 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.141847495650184</v>
+        <v>-4.108061724841965</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.05731801503236</v>
+        <v>1.070832323355648</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.090681634760296</v>
@@ -46562,10 +46562,10 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.962472074411417</v>
+        <v>-3.928686303603198</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.122855158834281</v>
+        <v>1.136369467157569</v>
       </c>
       <c r="F1957" t="n">
         <v>0.06609512341042267</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452222</v>
+        <v>3.716988143452223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.007486287932023</v>
+        <v>-3.973700517123804</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.085656928757629</v>
+        <v>1.099171237080916</v>
       </c>
       <c r="F1958" t="n">
         <v>0.03574622809581807</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979529</v>
+        <v>3.73702303297953</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.274490798204459</v>
+        <v>-4.240705027396239</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9845466869876003</v>
+        <v>0.9980609953108879</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.1586168099471305</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230804</v>
+        <v>3.702305879230805</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.563278018663374</v>
+        <v>-4.529492247855154</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8682357207005356</v>
+        <v>0.8817500290238232</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.2597029300461309</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285449</v>
+        <v>3.70556808628545</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.530802432492602</v>
+        <v>-4.497016661684382</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8788259167231613</v>
+        <v>0.8923402250464489</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.2597029300461309</v>
@@ -46677,10 +46677,10 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.511764304785305</v>
+        <v>-4.477978533977085</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8829658870143251</v>
+        <v>0.8964801953376127</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.3178865413773254</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601248</v>
+        <v>3.73106089760125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.542890935935923</v>
+        <v>-4.509105165127703</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.048097103492758</v>
+        <v>1.061611411816046</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.3178865413773254</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537859</v>
+        <v>3.722443786537861</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.595211316536715</v>
+        <v>-4.561425545728495</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.028002280238575</v>
+        <v>1.041516588561863</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.2829396813684533</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259115</v>
+        <v>3.787422005259117</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.739534222461634</v>
+        <v>-4.705748451653414</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9762816482655334</v>
+        <v>0.989795956588821</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.2829396813684533</v>
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989899</v>
+        <v>3.781497674989902</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.591791252226631</v>
+        <v>-4.76533442498297</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.114531484151557</v>
+        <v>1.045114215049021</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1151323241335701</v>
+        <v>-0.3206209495049898</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.882525014875814</v>
+        <v>2.759231839652962</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651161</v>
+        <v>3.802242353651164</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.693805934757853</v>
+        <v>-4.867349107514191</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.076519232670549</v>
+        <v>1.007101963568013</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1151323241335701</v>
+        <v>-0.3206209495049898</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.885318636407295</v>
+        <v>2.762025461184443</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864721</v>
+        <v>3.805605409864723</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.55719659066376</v>
+        <v>-4.730739763420098</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.131825318699844</v>
+        <v>1.062408049597309</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.02147701996052237</v>
+        <v>-0.1840116054108973</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.967946591255409</v>
+        <v>2.844653416032557</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798236219360607</v>
+        <v>3.79823621936061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.69996192348641</v>
+        <v>-4.873505096242749</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.073799662310895</v>
+        <v>1.004382393208359</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.121288312862128</v>
+        <v>-0.3267769382335478</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.881367868301929</v>
+        <v>2.758074693079077</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867359061268418</v>
+        <v>3.86735906126842</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.637663924710288</v>
+        <v>-4.811207097466626</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.165054415618164</v>
+        <v>1.095637146515628</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.121288312862128</v>
+        <v>-0.3267769382335478</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.94770342209875</v>
+        <v>2.824410246875898</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.796130164008313</v>
+        <v>3.474826600613507</v>
       </c>
       <c r="C1971" t="n">
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.449892898349184</v>
+        <v>-4.609416899801468</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9487436985520041</v>
+        <v>0.8849340979710898</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.1477204746223392</v>
+        <v>-0.1287587460643934</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.817689566978828</v>
+        <v>2.651802034566789</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240522.xlsx
+++ b/tame_output/ON/bt/strategyON_20240522.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>49.7%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>69.4%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.4%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.2%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>46.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,27 +839,27 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>27.4%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-38.7%</t>
+          <t>-47.1%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.6%</t>
+          <t>-78.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.8%</t>
+          <t>-75.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>445.2%</t>
+          <t>448.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-9.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-622.5%</t>
+          <t>-628.4%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-4.4%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.8%</t>
+          <t>-26.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-287.7%</t>
+          <t>-290.1%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.37</t>
+          <t>-0.38</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-19.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>39.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-208.6%</t>
+          <t>-114.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-236.9%</t>
+          <t>-242.7%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41.3%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-05-21</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>-25.2%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>43.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.6%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-180.8%</t>
+          <t>-182.2%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1971"/>
+  <dimension ref="A1:G1972"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310977</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.305849539006528</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.3047157169709</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.300815818330517</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191732</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108633</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097815</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923083</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.07354219995455</v>
+        <v>-10.13207055499297</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8541533099394254</v>
+        <v>-0.8775646519547937</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.379441859300699</v>
+        <v>-2.437970214339122</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.747954878775723</v>
+        <v>1.71283786575267</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.809705332750482</v>
+        <v>-9.868233687788903</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7585020443707053</v>
+        <v>-0.7819133863860737</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.379441859300699</v>
+        <v>-2.437970214339122</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.738071397462815</v>
+        <v>1.702954384439762</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.542463531882085</v>
+        <v>-9.600991886920506</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6534398845227201</v>
+        <v>-0.6768512265380884</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.379441859300699</v>
+        <v>-2.437970214339122</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.736236836963442</v>
+        <v>1.701119823940389</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.444556493205594</v>
+        <v>-9.503084848244015</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6145773840255848</v>
+        <v>-0.6379887260409531</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.311456109440143</v>
+        <v>-2.369984464478565</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.776727971906315</v>
+        <v>1.741610958883262</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.420602952229636</v>
+        <v>-9.479131307268057</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6043274614897078</v>
+        <v>-0.6277388035050762</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.287502568464185</v>
+        <v>-2.346030923502608</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.791768602637383</v>
+        <v>1.75665158961433</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.156543013906839</v>
+        <v>-9.21507136894526</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5119638023223412</v>
+        <v>-0.5353751443377095</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.023442630141389</v>
+        <v>-2.081970985179811</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.936944249469309</v>
+        <v>1.901827236446255</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.449463390402002</v>
+        <v>-8.507991745440423</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2319189865807072</v>
+        <v>-0.2553303285960755</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.023442630141389</v>
+        <v>-2.081970985179811</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.934157215809008</v>
+        <v>1.899040202785955</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.409279092035812</v>
+        <v>-8.467807447074232</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2155016433463897</v>
+        <v>-0.238912985361758</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.983258331775199</v>
+        <v>-2.04178668681362</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.958611418716564</v>
+        <v>1.923494405693511</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.329209296498007</v>
+        <v>-8.387737651536428</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1841069039105108</v>
+        <v>-0.2075182459258791</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.903188536237395</v>
+        <v>-1.961716891275816</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.006020117260003</v>
+        <v>1.97090310423695</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.095728074268408</v>
+        <v>-8.15425642930683</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.08278998618081879</v>
+        <v>-0.106201328196188</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.669707314007796</v>
+        <v>-1.728235669046218</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.154033279435614</v>
+        <v>2.118916266412561</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.946061683260893</v>
+        <v>-8.004590038299316</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.02581564009077209</v>
+        <v>-0.04922698210614085</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.57680382276526</v>
+        <v>-1.635332177803682</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.206883163868177</v>
+        <v>2.171766150845124</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.813786209630006</v>
+        <v>-7.87231456466843</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.02246203610860986</v>
+        <v>-0.0009493059067593457</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.444528349134373</v>
+        <v>-1.503056704172795</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.281615934793736</v>
+        <v>2.246498921770683</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.623186534956853</v>
+        <v>-7.681714889995277</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1015169666655074</v>
+        <v>0.07810562465013859</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.253928674461221</v>
+        <v>-1.312457029499642</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.398790800285264</v>
+        <v>2.363673787262211</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.374186736273272</v>
+        <v>-7.432715091311696</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2140232273625986</v>
+        <v>0.1906118853472294</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.253928674461221</v>
+        <v>-1.312457029499642</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.411697141508923</v>
+        <v>2.37658012848587</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.479776726046377</v>
+        <v>-7.5383050810848</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.04381130185413795</v>
+        <v>0.02039995983876919</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.359518664234325</v>
+        <v>-1.418047019272747</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.220367218045842</v>
+        <v>2.185250205022789</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.498511628164974</v>
+        <v>-7.557039983203397</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.08486168288378559</v>
+        <v>0.06145034086841683</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.359518664234325</v>
+        <v>-1.418047019272747</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.268911559922928</v>
+        <v>2.233794546899875</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.350571586757375</v>
+        <v>-7.409099941795798</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.02415877675865774</v>
+        <v>0.0007474347432889772</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.339197748325767</v>
+        <v>-1.397726103364189</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.161225186779895</v>
+        <v>2.126108173756842</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.326342950368402</v>
+        <v>-7.384871305406826</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.02513624506076884</v>
+        <v>0.001724903045399628</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.373497466975217</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.1670483823598</v>
+        <v>2.131931369336747</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.282794543597712</v>
+        <v>-7.341322898636135</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.03559499567395186</v>
+        <v>0.01218365365858265</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.373497466975217</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.160087770264707</v>
+        <v>2.124970757241654</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.040646150143854</v>
+        <v>-7.099174505182277</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1469167074366382</v>
+        <v>0.123505365421269</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.373497466975217</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.17455012464585</v>
+        <v>2.139433111622797</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.977416778375505</v>
+        <v>-7.035945133413929</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1667405766031722</v>
+        <v>0.1433292345878034</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.373497466975217</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.169082245105045</v>
+        <v>2.133965232081992</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.854125643558374</v>
+        <v>-6.912653998596798</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2135551245406018</v>
+        <v>0.1901437825252326</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.191677977119665</v>
+        <v>-1.250206332158086</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.2405550200059</v>
+        <v>2.205438006982847</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.832976444654931</v>
+        <v>-6.891504799693354</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2297157823393041</v>
+        <v>0.2063044403239349</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.170528778216221</v>
+        <v>-1.229057133254643</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.260945517585291</v>
+        <v>2.225828504562239</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.589211002671487</v>
+        <v>-6.64773935770991</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3230026674797326</v>
+        <v>0.2995913254643634</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.170528778216221</v>
+        <v>-1.229057133254643</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.256726225932342</v>
+        <v>2.221609212909289</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.442313974953617</v>
+        <v>-6.50084232999204</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3838857924868964</v>
+        <v>0.3604744504715276</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.122870536237633</v>
+        <v>-1.181398891276055</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.287445485039511</v>
+        <v>2.252328472016458</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.192463581004542</v>
+        <v>-6.250991936042966</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4765680250502284</v>
+        <v>0.4531566830348592</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.122870536237633</v>
+        <v>-1.181398891276055</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.280187560023213</v>
+        <v>2.24507054700016</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.01657148853711</v>
+        <v>-6.075099843575534</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5505239855578501</v>
+        <v>0.5271126435424809</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.122870536237633</v>
+        <v>-1.181398891276055</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.283786683543862</v>
+        <v>2.248669670520809</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.845125025514647</v>
+        <v>-5.90365338055307</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6324300768213891</v>
+        <v>0.6090187348060203</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9514240732151701</v>
+        <v>-1.009952428253592</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.399982067411893</v>
+        <v>2.36486505438884</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.620092025845824</v>
+        <v>-5.678620380884247</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7214637543052151</v>
+        <v>0.6980524122898464</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7263910735463472</v>
+        <v>-0.784919428584769</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.534022344829484</v>
+        <v>2.498905331806431</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353066</v>
+        <v>3.764614304353067</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.556456283611889</v>
+        <v>-5.614984638650313</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7516128522531065</v>
+        <v>0.7282015102377373</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.6627553313124127</v>
+        <v>-0.7212836863508345</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.576898591224162</v>
+        <v>2.541781578201109</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544775</v>
+        <v>3.798811195544776</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.463456242405991</v>
+        <v>-5.521984597444415</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7700071275192615</v>
+        <v>0.7465957855038923</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.6627553313124127</v>
+        <v>-0.7212836863508345</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.558092850007958</v>
+        <v>2.522975836984905</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.223025745601131</v>
+        <v>-5.281554100639554</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8679224028660828</v>
+        <v>0.8445110608507136</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4223248345075524</v>
+        <v>-0.4808531895459742</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.704094224715751</v>
+        <v>2.668977211692698</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.150783177429936</v>
+        <v>-5.20931153246836</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9007487439693809</v>
+        <v>0.8773374019540117</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4223248345075524</v>
+        <v>-0.4808531895459742</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.708023538550572</v>
+        <v>2.672906525527519</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.034843327804751</v>
+        <v>-5.093371682843174</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9478032677367949</v>
+        <v>0.9243919257214261</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3455031034914285</v>
+        <v>-0.4040314585298503</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.754795161077586</v>
+        <v>2.719678148054533</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972332</v>
+        <v>3.848613050972331</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.926038442325024</v>
+        <v>-4.984566797363447</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9883232931486794</v>
+        <v>0.9649119511333102</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3455031034914285</v>
+        <v>-0.4040314585298503</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.751793232297579</v>
+        <v>2.716676219274526</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145931</v>
+        <v>3.81866537614593</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.706017644288013</v>
+        <v>-4.764545999326437</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.077910649374098</v>
+        <v>1.054499307358729</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2042832584234483</v>
+        <v>-0.2628116134618701</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.838104176348982</v>
+        <v>2.802987163325929</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009943</v>
+        <v>3.843270952009942</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.573149955224736</v>
+        <v>-4.631678310263159</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.146951907801232</v>
+        <v>1.123540565785863</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2042832584234483</v>
+        <v>-0.2628116134618701</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.853998359150805</v>
+        <v>2.818881346127752</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966255</v>
+        <v>3.845043810966254</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.413634851705366</v>
+        <v>-4.472163206743789</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.211903793649282</v>
+        <v>1.188492451633913</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.04476815490407837</v>
+        <v>-0.1032965099425002</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.950853265702729</v>
+        <v>2.915736252679676</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046993</v>
+        <v>3.791269976046991</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.268962706605628</v>
+        <v>-4.327491061644052</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.279860754250617</v>
+        <v>1.256449412235248</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.09990399019565904</v>
+        <v>0.04137563515723724</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.047744655324011</v>
+        <v>3.012627642300958</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412102</v>
+        <v>3.7358356474121</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.328837533963321</v>
+        <v>-4.387365889001744</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.241948314708966</v>
+        <v>1.218536972693597</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.04002916283796693</v>
+        <v>-0.01849919220045487</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.997857250310822</v>
+        <v>2.962740237287769</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144513</v>
+        <v>3.762643902144512</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.242038036184312</v>
+        <v>-4.300566391222735</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.299068607143135</v>
+        <v>1.275657265127766</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.04002916283796693</v>
+        <v>-0.01849919220045487</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.020257743633388</v>
+        <v>2.985140730610335</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900691</v>
+        <v>3.729142822900689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.244507742646118</v>
+        <v>-4.303036097684541</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.298153125931825</v>
+        <v>1.274741783916456</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.03755945637616076</v>
+        <v>-0.02096889866226104</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.018848321129716</v>
+        <v>2.983731308106663</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473595</v>
+        <v>3.743216620473594</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.312877928970128</v>
+        <v>-4.371406284008551</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.281811973876923</v>
+        <v>1.258400631861554</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.04683515541237571</v>
+        <v>-0.01169319962604609</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.035420663026147</v>
+        <v>3.000303650003094</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978364</v>
+        <v>3.714175563978362</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.421416109886262</v>
+        <v>-4.479944464924685</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.228833410142361</v>
+        <v>1.205422068126992</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.04683515541237571</v>
+        <v>-0.01169319962604609</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.025857371658038</v>
+        <v>2.990740358634985</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887697</v>
+        <v>3.710903155887695</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.452409269214967</v>
+        <v>-4.510937624253391</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.041145711451265</v>
+        <v>1.017734369435896</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.04683515541237571</v>
+        <v>-0.01169319962604609</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.850566936698425</v>
+        <v>2.815449923675372</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746038950675892</v>
+        <v>3.74603895067589</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.276935009422498</v>
+        <v>-4.335463364460922</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.115902647360041</v>
+        <v>1.092491305344672</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.04683515541237571</v>
+        <v>-0.01169319962604609</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.855134168690213</v>
+        <v>2.82001715566716</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695438</v>
+        <v>3.765020747695436</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.387871262063747</v>
+        <v>-4.446399617102171</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.047270175064748</v>
+        <v>1.023858833049379</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.04683515541237571</v>
+        <v>-0.01169319962604609</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.83087619745142</v>
+        <v>2.795759184428367</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581287</v>
+        <v>3.773206721581285</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.59089783960698</v>
+        <v>-4.649426194645404</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9691909292673604</v>
+        <v>0.9457795872519914</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.2147197771692795</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.712191636145385</v>
+        <v>2.677074623122333</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734157</v>
+        <v>3.784340376734155</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.432972240671687</v>
+        <v>-4.491500595710111</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.04253355527361</v>
+        <v>1.019122213258241</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.2147197771692795</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.722364022577518</v>
+        <v>2.687247009554465</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212293</v>
+        <v>3.786946382212292</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.34672877764531</v>
+        <v>-4.405257132683733</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.071977211058021</v>
+        <v>1.048565869042652</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.2147197771692795</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.717310293151378</v>
+        <v>2.682193280128325</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786041</v>
+        <v>3.752023923786039</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.347911862296371</v>
+        <v>-4.406440217334795</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.063279752642122</v>
+        <v>1.039868410626753</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1618344705973692</v>
+        <v>-0.220362825635791</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.705700239515997</v>
+        <v>2.670583226492944</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273187</v>
+        <v>3.753567590273185</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.224784155302288</v>
+        <v>-4.283312510340711</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.113082708472857</v>
+        <v>1.089671366457488</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1618344705973692</v>
+        <v>-0.220362825635791</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.706252112549099</v>
+        <v>2.671135099526045</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279496</v>
+        <v>3.733387025279495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.131973673851428</v>
+        <v>-4.190502028889852</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.079479592944567</v>
+        <v>1.056068250929198</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.06902398914650987</v>
+        <v>-0.1275523441849317</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.691211093310979</v>
+        <v>2.656094080287926</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030424</v>
+        <v>3.748282241030422</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.083410621630398</v>
+        <v>-4.141938976668822</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.10077828975758</v>
+        <v>1.077366947742211</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.02046093692547968</v>
+        <v>-0.07898929196390148</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.722222400568199</v>
+        <v>2.687105387545146</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942736</v>
+        <v>3.721073619942734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.970739403394148</v>
+        <v>-4.029267758432572</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.140922485563802</v>
+        <v>1.117511143548434</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.09221028131077053</v>
+        <v>0.03368192627234873</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.784900840021672</v>
+        <v>2.749783826998619</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268534</v>
+        <v>3.743044028268532</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.858362402211476</v>
+        <v>-3.916890757249899</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.191364581867539</v>
+        <v>1.16795323985217</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.09221028131077053</v>
+        <v>0.03368192627234873</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.790392135852339</v>
+        <v>2.755275122829286</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968858</v>
+        <v>3.689594264968857</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.056596971098206</v>
+        <v>-4.11512532613663</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.123567956081386</v>
+        <v>1.100156614066017</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1060242875759601</v>
+        <v>-0.1645526426143818</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.68294859628884</v>
+        <v>2.647831583265787</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175318</v>
+        <v>3.643066046175317</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.139598252123485</v>
+        <v>-4.198126607161909</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9287231636719273</v>
+        <v>0.9053118216565583</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1245951721031338</v>
+        <v>-0.1831235271415556</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.510161785573189</v>
+        <v>2.475044772550136</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199263</v>
+        <v>3.682712735199261</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.266665258430473</v>
+        <v>-4.325193613468897</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9980460218683378</v>
+        <v>0.9746346798529688</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1245951721031338</v>
+        <v>-0.1831235271415556</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.630311446292394</v>
+        <v>2.595194433269342</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733008865660762</v>
+        <v>3.73300886566076</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.353263841411576</v>
+        <v>-4.41179219645</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9779196147782196</v>
+        <v>0.9545082727628507</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1245951721031338</v>
+        <v>-0.1831235271415556</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.644824472394717</v>
+        <v>2.609707459371664</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383417</v>
+        <v>3.741170494383415</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.314880178853425</v>
+        <v>-4.373408533891848</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9906925211438486</v>
+        <v>0.9672811791284797</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.08621150954498263</v>
+        <v>-0.1447398645834044</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.665274111271977</v>
+        <v>2.630157098248924</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002478</v>
+        <v>3.751143622002475</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.137763848818259</v>
+        <v>-4.196292203856682</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.058268082003217</v>
+        <v>1.034856739987848</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.08621150954498263</v>
+        <v>-0.1447398645834044</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.662003140117279</v>
+        <v>2.626886127094226</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263895</v>
+        <v>3.741324873263892</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.108061724841965</v>
+        <v>-4.166590079880389</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.070832323355648</v>
+        <v>1.047420981340279</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.090681634760296</v>
+        <v>-0.1492099897987178</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.660004456750004</v>
+        <v>2.62488744372695</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481227</v>
+        <v>3.750725801481225</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.928686303603198</v>
+        <v>-3.987214658641621</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.136369467157569</v>
+        <v>1.1129581251422</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.06609512341042267</v>
+        <v>0.007566768372000876</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.747857486958849</v>
+        <v>2.712740473935796</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452223</v>
+        <v>3.716988143452221</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.973700517123804</v>
+        <v>-4.032228872162228</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.099171237080916</v>
+        <v>1.075759895065547</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.03574622809581807</v>
+        <v>-0.02278212694260373</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.710455605101676</v>
+        <v>2.675338592078623</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702303297953</v>
+        <v>3.737023032979527</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.240705027396239</v>
+        <v>-4.299233382434663</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9980609953108879</v>
+        <v>0.9746496532955189</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1586168099471305</v>
+        <v>-0.2171451649855523</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.599529344614853</v>
+        <v>2.5644123315918</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230805</v>
+        <v>3.702305879230802</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.529492247855154</v>
+        <v>-4.588020602893578</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8817500290238232</v>
+        <v>0.8583386870084542</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2597029300461309</v>
+        <v>-0.3182312850845527</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.538081594451954</v>
+        <v>2.502964581428901</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.70556808628545</v>
+        <v>3.705568086285448</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.497016661684382</v>
+        <v>-4.555545016722806</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8923402250464489</v>
+        <v>0.8689288830310797</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2597029300461309</v>
+        <v>-0.3182312850845527</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.535681556006271</v>
+        <v>2.500564542983218</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848098</v>
+        <v>3.709506867848096</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.477978533977085</v>
+        <v>-4.536506889015508</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8964801953376127</v>
+        <v>0.8730688533222437</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3178865413773254</v>
+        <v>-0.3764148964157472</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.497296108415799</v>
+        <v>2.462179095392746</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.73106089760125</v>
+        <v>3.731060897601246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.509105165127703</v>
+        <v>-4.567633520166127</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.061611411816046</v>
+        <v>1.038200069800677</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3178865413773254</v>
+        <v>-0.3764148964157472</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.67487797735448</v>
+        <v>2.639760964331427</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537861</v>
+        <v>3.722443786537857</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.561425545728495</v>
+        <v>-4.619953900766919</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.041516588561863</v>
+        <v>1.018105246546494</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.2829396813684533</v>
+        <v>-0.3414680364068751</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.696679422345936</v>
+        <v>2.661562409322883</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259117</v>
+        <v>3.787422005259113</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.705748451653414</v>
+        <v>-4.764276806691838</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.989795956588821</v>
+        <v>0.966384614573452</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.2829396813684533</v>
+        <v>-0.3414680364068751</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.702687952742862</v>
+        <v>2.667570939719809</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989902</v>
+        <v>3.781497674989899</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.76533442498297</v>
+        <v>-4.823862780021393</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.045114215049021</v>
+        <v>1.021702873033652</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3206209495049898</v>
+        <v>-0.3791493045434116</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.759231839652962</v>
+        <v>2.724114826629909</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651164</v>
+        <v>3.80224235365116</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.867349107514191</v>
+        <v>-4.925877462552615</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.007101963568013</v>
+        <v>0.9836906215526442</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3206209495049898</v>
+        <v>-0.3791493045434116</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.762025461184443</v>
+        <v>2.72690844816139</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864723</v>
+        <v>3.80560540986472</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.730739763420098</v>
+        <v>-4.789268118458522</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.062408049597309</v>
+        <v>1.03899670758194</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.1840116054108973</v>
+        <v>-0.2425399604493191</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.844653416032557</v>
+        <v>2.809536403009504</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.79823621936061</v>
+        <v>3.798236219360606</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.873505096242749</v>
+        <v>-4.932033451281172</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.004382393208359</v>
+        <v>0.9809710511929897</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3267769382335478</v>
+        <v>-0.3853052932719696</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.758074693079077</v>
+        <v>2.722957680056024</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.86735906126842</v>
+        <v>3.867359061268417</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.811207097466626</v>
+        <v>-4.86973545250505</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.095637146515628</v>
+        <v>1.07222580450026</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3267769382335478</v>
+        <v>-0.3853052932719696</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.824410246875898</v>
+        <v>2.789293233852845</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,45 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.474826600613507</v>
+        <v>3.848725564462185</v>
       </c>
       <c r="C1971" t="n">
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.609416899801468</v>
+        <v>-4.667945254839892</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8849340979710898</v>
+        <v>0.8615227559557208</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1287587460643934</v>
+        <v>-0.1872871011028152</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.651802034566789</v>
+        <v>2.616685021543736</v>
+      </c>
+    </row>
+    <row r="1972">
+      <c r="A1972" s="2" t="n">
+        <v>45434</v>
+      </c>
+      <c r="B1972" t="n">
+        <v>3.747608600760003</v>
+      </c>
+      <c r="C1972" t="n">
+        <v>2.645105971078365</v>
+      </c>
+      <c r="D1972" t="n">
+        <v>-4.667945254839892</v>
+      </c>
+      <c r="E1972" t="n">
+        <v>0.8615227559557208</v>
+      </c>
+      <c r="F1972" t="n">
+        <v>-0.1872871011028152</v>
+      </c>
+      <c r="G1972" t="n">
+        <v>2.638169768064733</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240522.xlsx
+++ b/tame_output/ON/bt/strategyON_20240522.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>47.9%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-47.1%</t>
+          <t>-38.9%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.8%</t>
+          <t>-77.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.6%</t>
+          <t>109.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.4%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-52.1%</t>
+          <t>-51.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.1%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.9%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.6%</t>
+          <t>448.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.2%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-628.4%</t>
+          <t>-601.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>2.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.3%</t>
+          <t>-38.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-26.4%</t>
+          <t>-24.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-290.1%</t>
+          <t>-279.3%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-22.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.38</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>68.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.2%</t>
+          <t>10.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-30.0%</t>
+          <t>-31.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-19.6%</t>
+          <t>-15.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-114.9%</t>
+          <t>-213.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-242.7%</t>
+          <t>-216.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>43.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.2%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.4%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-14.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-182.2%</t>
+          <t>-174.0%</t>
         </is>
       </c>
     </row>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310977</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006528</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.3047157169709</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330517</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.13207055499297</v>
+        <v>-10.07354219995455</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8775646519547937</v>
+        <v>-0.8541533099394254</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.437970214339122</v>
+        <v>-2.379441859300699</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.71283786575267</v>
+        <v>1.747954878775723</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.868233687788903</v>
+        <v>-9.809705332750482</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7819133863860737</v>
+        <v>-0.7585020443707053</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.437970214339122</v>
+        <v>-2.379441859300699</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.702954384439762</v>
+        <v>1.738071397462815</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.600991886920506</v>
+        <v>-9.542463531882085</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6768512265380884</v>
+        <v>-0.6534398845227201</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.437970214339122</v>
+        <v>-2.379441859300699</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.701119823940389</v>
+        <v>1.736236836963442</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.503084848244015</v>
+        <v>-9.444556493205594</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6379887260409531</v>
+        <v>-0.6145773840255848</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.369984464478565</v>
+        <v>-2.311456109440143</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.741610958883262</v>
+        <v>1.776727971906315</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.479131307268057</v>
+        <v>-9.420602952229636</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6277388035050762</v>
+        <v>-0.6043274614897078</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.346030923502608</v>
+        <v>-2.287502568464185</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.75665158961433</v>
+        <v>1.791768602637383</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.21507136894526</v>
+        <v>-9.156543013906839</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5353751443377095</v>
+        <v>-0.5119638023223412</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.081970985179811</v>
+        <v>-2.023442630141389</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.901827236446255</v>
+        <v>1.936944249469309</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.507991745440423</v>
+        <v>-8.449463390402002</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2553303285960755</v>
+        <v>-0.2319189865807072</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.081970985179811</v>
+        <v>-2.023442630141389</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.899040202785955</v>
+        <v>1.934157215809008</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.467807447074232</v>
+        <v>-8.409279092035812</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.238912985361758</v>
+        <v>-0.2155016433463897</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.04178668681362</v>
+        <v>-1.983258331775199</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.923494405693511</v>
+        <v>1.958611418716564</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.387737651536428</v>
+        <v>-8.329209296498007</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2075182459258791</v>
+        <v>-0.1841069039105108</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.961716891275816</v>
+        <v>-1.903188536237395</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.97090310423695</v>
+        <v>2.006020117260003</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.15425642930683</v>
+        <v>-8.095728074268408</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.106201328196188</v>
+        <v>-0.08278998618081879</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.728235669046218</v>
+        <v>-1.669707314007796</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.118916266412561</v>
+        <v>2.154033279435614</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.004590038299316</v>
+        <v>-7.946061683260893</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.04922698210614085</v>
+        <v>-0.02581564009077209</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.635332177803682</v>
+        <v>-1.57680382276526</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.171766150845124</v>
+        <v>2.206883163868177</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.87231456466843</v>
+        <v>-7.813786209630006</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.0009493059067593457</v>
+        <v>0.02246203610860986</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.503056704172795</v>
+        <v>-1.444528349134373</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.246498921770683</v>
+        <v>2.281615934793736</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.681714889995277</v>
+        <v>-7.623186534956853</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.07810562465013859</v>
+        <v>0.1015169666655074</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.312457029499642</v>
+        <v>-1.253928674461221</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.363673787262211</v>
+        <v>2.398790800285264</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.432715091311696</v>
+        <v>-7.374186736273272</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1906118853472294</v>
+        <v>0.2140232273625986</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.312457029499642</v>
+        <v>-1.253928674461221</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.37658012848587</v>
+        <v>2.411697141508923</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.5383050810848</v>
+        <v>-7.479776726046377</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.02039995983876919</v>
+        <v>0.04381130185413795</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.418047019272747</v>
+        <v>-1.359518664234325</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.185250205022789</v>
+        <v>2.220367218045842</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.557039983203397</v>
+        <v>-7.498511628164974</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.06145034086841683</v>
+        <v>0.08486168288378559</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.418047019272747</v>
+        <v>-1.359518664234325</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.233794546899875</v>
+        <v>2.268911559922928</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.409099941795798</v>
+        <v>-7.350571586757375</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.0007474347432889772</v>
+        <v>0.02415877675865774</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.397726103364189</v>
+        <v>-1.339197748325767</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.126108173756842</v>
+        <v>2.161225186779895</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.384871305406826</v>
+        <v>-7.326342950368402</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.001724903045399628</v>
+        <v>0.02513624506076884</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.373497466975217</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.131931369336747</v>
+        <v>2.1670483823598</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.341322898636135</v>
+        <v>-7.282794543597712</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.01218365365858265</v>
+        <v>0.03559499567395186</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.373497466975217</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.124970757241654</v>
+        <v>2.160087770264707</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.099174505182277</v>
+        <v>-7.040646150143854</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.123505365421269</v>
+        <v>0.1469167074366382</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.373497466975217</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.139433111622797</v>
+        <v>2.17455012464585</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.035945133413929</v>
+        <v>-6.977416778375505</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1433292345878034</v>
+        <v>0.1667405766031722</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.373497466975217</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.133965232081992</v>
+        <v>2.169082245105045</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.912653998596798</v>
+        <v>-6.854125643558374</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1901437825252326</v>
+        <v>0.2135551245406018</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.250206332158086</v>
+        <v>-1.191677977119665</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.205438006982847</v>
+        <v>2.2405550200059</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.891504799693354</v>
+        <v>-6.832976444654931</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2063044403239349</v>
+        <v>0.2297157823393041</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.229057133254643</v>
+        <v>-1.170528778216221</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.225828504562239</v>
+        <v>2.260945517585291</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.64773935770991</v>
+        <v>-6.589211002671487</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2995913254643634</v>
+        <v>0.3230026674797326</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.229057133254643</v>
+        <v>-1.170528778216221</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.221609212909289</v>
+        <v>2.256726225932342</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.50084232999204</v>
+        <v>-6.442313974953617</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3604744504715276</v>
+        <v>0.3838857924868964</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.181398891276055</v>
+        <v>-1.122870536237633</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.252328472016458</v>
+        <v>2.287445485039511</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.250991936042966</v>
+        <v>-6.192463581004542</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4531566830348592</v>
+        <v>0.4765680250502284</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.181398891276055</v>
+        <v>-1.122870536237633</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.24507054700016</v>
+        <v>2.280187560023213</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.075099843575534</v>
+        <v>-6.01657148853711</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5271126435424809</v>
+        <v>0.5505239855578501</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.181398891276055</v>
+        <v>-1.122870536237633</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.248669670520809</v>
+        <v>2.283786683543862</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.90365338055307</v>
+        <v>-5.845125025514647</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6090187348060203</v>
+        <v>0.6324300768213891</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.009952428253592</v>
+        <v>-0.9514240732151701</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.36486505438884</v>
+        <v>2.399982067411893</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.678620380884247</v>
+        <v>-5.620092025845824</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6980524122898464</v>
+        <v>0.7214637543052151</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.784919428584769</v>
+        <v>-0.7263910735463472</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.498905331806431</v>
+        <v>2.534022344829484</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.614984638650313</v>
+        <v>-5.556456283611889</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7282015102377373</v>
+        <v>0.7516128522531065</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.7212836863508345</v>
+        <v>-0.6627553313124127</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.541781578201109</v>
+        <v>2.576898591224162</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.521984597444415</v>
+        <v>-5.463456242405991</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7465957855038923</v>
+        <v>0.7700071275192615</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.7212836863508345</v>
+        <v>-0.6627553313124127</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.522975836984905</v>
+        <v>2.558092850007958</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.281554100639554</v>
+        <v>-5.223025745601131</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8445110608507136</v>
+        <v>0.8679224028660828</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4808531895459742</v>
+        <v>-0.4223248345075524</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.668977211692698</v>
+        <v>2.704094224715751</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.20931153246836</v>
+        <v>-5.150783177429936</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8773374019540117</v>
+        <v>0.9007487439693809</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4808531895459742</v>
+        <v>-0.4223248345075524</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.672906525527519</v>
+        <v>2.708023538550572</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.093371682843174</v>
+        <v>-5.034843327804751</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9243919257214261</v>
+        <v>0.9478032677367949</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.4040314585298503</v>
+        <v>-0.3455031034914285</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.719678148054533</v>
+        <v>2.754795161077586</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.984566797363447</v>
+        <v>-4.926038442325024</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9649119511333102</v>
+        <v>0.9883232931486794</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.4040314585298503</v>
+        <v>-0.3455031034914285</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.716676219274526</v>
+        <v>2.751793232297579</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.764545999326437</v>
+        <v>-4.706017644288013</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.054499307358729</v>
+        <v>1.077910649374098</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2628116134618701</v>
+        <v>-0.2042832584234483</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.802987163325929</v>
+        <v>2.838104176348982</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.631678310263159</v>
+        <v>-4.573149955224736</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.123540565785863</v>
+        <v>1.146951907801232</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2628116134618701</v>
+        <v>-0.2042832584234483</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.818881346127752</v>
+        <v>2.853998359150805</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.472163206743789</v>
+        <v>-4.413634851705366</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.188492451633913</v>
+        <v>1.211903793649282</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.1032965099425002</v>
+        <v>-0.04476815490407837</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.915736252679676</v>
+        <v>2.950853265702729</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.327491061644052</v>
+        <v>-4.268962706605628</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.256449412235248</v>
+        <v>1.279860754250617</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.04137563515723724</v>
+        <v>0.09990399019565904</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.012627642300958</v>
+        <v>3.047744655324011</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.387365889001744</v>
+        <v>-4.328837533963321</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.218536972693597</v>
+        <v>1.241948314708966</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.01849919220045487</v>
+        <v>0.04002916283796693</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.962740237287769</v>
+        <v>2.997857250310822</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.300566391222735</v>
+        <v>-4.242038036184312</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.275657265127766</v>
+        <v>1.299068607143135</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.01849919220045487</v>
+        <v>0.04002916283796693</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.985140730610335</v>
+        <v>3.020257743633388</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.303036097684541</v>
+        <v>-4.244507742646118</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.274741783916456</v>
+        <v>1.298153125931825</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.02096889866226104</v>
+        <v>0.03755945637616076</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.983731308106663</v>
+        <v>3.018848321129716</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.371406284008551</v>
+        <v>-4.312877928970128</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.258400631861554</v>
+        <v>1.281811973876923</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.01169319962604609</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.000303650003094</v>
+        <v>3.035420663026147</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.479944464924685</v>
+        <v>-4.421416109886262</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.205422068126992</v>
+        <v>1.228833410142361</v>
       </c>
       <c r="F1937" t="n">
-        <v>-0.01169319962604609</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.990740358634985</v>
+        <v>3.025857371658038</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.510937624253391</v>
+        <v>-4.448144298067664</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.017734369435896</v>
+        <v>1.042851699910187</v>
       </c>
       <c r="F1938" t="n">
-        <v>-0.01169319962604609</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.815449923675372</v>
+        <v>2.850566936698425</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.335463364460922</v>
+        <v>-4.272670038275194</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.092491305344672</v>
+        <v>1.117608635818962</v>
       </c>
       <c r="F1939" t="n">
-        <v>-0.01169319962604609</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.82001715566716</v>
+        <v>2.855134168690213</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.446399617102171</v>
+        <v>-4.383606290916443</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.023858833049379</v>
+        <v>1.04897616352367</v>
       </c>
       <c r="F1940" t="n">
-        <v>-0.01169319962604609</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.795759184428367</v>
+        <v>2.83087619745142</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.649426194645404</v>
+        <v>-4.586632868459676</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9457795872519914</v>
+        <v>0.9708969177262821</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.2147197771692795</v>
+        <v>-0.1561914221308577</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.677074623122333</v>
+        <v>2.712191636145385</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.491500595710111</v>
+        <v>-4.428707269524383</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.019122213258241</v>
+        <v>1.044239543732532</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.2147197771692795</v>
+        <v>-0.1561914221308577</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.687247009554465</v>
+        <v>2.722364022577518</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.405257132683733</v>
+        <v>-4.342463806498006</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.048565869042652</v>
+        <v>1.073683199516943</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.2147197771692795</v>
+        <v>-0.1561914221308577</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.682193280128325</v>
+        <v>2.717310293151378</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.406440217334795</v>
+        <v>-4.343646891149067</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.039868410626753</v>
+        <v>1.064985741101044</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.220362825635791</v>
+        <v>-0.1618344705973692</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.670583226492944</v>
+        <v>2.705700239515997</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.283312510340711</v>
+        <v>-4.220519184154984</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.089671366457488</v>
+        <v>1.114788696931779</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.220362825635791</v>
+        <v>-0.1618344705973692</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.671135099526045</v>
+        <v>2.706252112549099</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.190502028889852</v>
+        <v>-4.127708702704124</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.056068250929198</v>
+        <v>1.081185581403488</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.1275523441849317</v>
+        <v>-0.06902398914650987</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.656094080287926</v>
+        <v>2.691211093310979</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.141938976668822</v>
+        <v>-4.079145650483095</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.077366947742211</v>
+        <v>1.102484278216501</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.07898929196390148</v>
+        <v>-0.02046093692547968</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.687105387545146</v>
+        <v>2.722222400568199</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.029267758432572</v>
+        <v>-3.966474432246844</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.117511143548434</v>
+        <v>1.142628474022724</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.03368192627234873</v>
+        <v>0.09221028131077053</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.749783826998619</v>
+        <v>2.784900840021672</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.916890757249899</v>
+        <v>-3.854097431064172</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.16795323985217</v>
+        <v>1.19307057032646</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.03368192627234873</v>
+        <v>0.09221028131077053</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.755275122829286</v>
+        <v>2.790392135852339</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.11512532613663</v>
+        <v>-4.052331999950902</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.100156614066017</v>
+        <v>1.125273944540307</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1645526426143818</v>
+        <v>-0.1060242875759601</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.647831583265787</v>
+        <v>2.68294859628884</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.198126607161909</v>
+        <v>-4.135333280976181</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9053118216565583</v>
+        <v>0.930429152130849</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1831235271415556</v>
+        <v>-0.1245951721031338</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.475044772550136</v>
+        <v>2.510161785573189</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.325193613468897</v>
+        <v>-4.262400287283169</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9746346798529688</v>
+        <v>0.9997520103272595</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1831235271415556</v>
+        <v>-0.1245951721031338</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.595194433269342</v>
+        <v>2.630311446292394</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.41179219645</v>
+        <v>-4.348998870264272</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9545082727628507</v>
+        <v>0.9796256032371411</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1831235271415556</v>
+        <v>-0.1245951721031338</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.609707459371664</v>
+        <v>2.644824472394717</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383415</v>
+        <v>3.741170494383416</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.373408533891848</v>
+        <v>-4.310615207706121</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9672811791284797</v>
+        <v>0.9923985096027703</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1447398645834044</v>
+        <v>-0.08621150954498263</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.630157098248924</v>
+        <v>2.665274111271977</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002475</v>
+        <v>3.751143622002476</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.196292203856682</v>
+        <v>-4.133498877670955</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.034856739987848</v>
+        <v>1.059974070462139</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1447398645834044</v>
+        <v>-0.08621150954498263</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.626886127094226</v>
+        <v>2.662003140117279</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263892</v>
+        <v>3.741324873263893</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.166590079880389</v>
+        <v>-4.103796753694661</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.047420981340279</v>
+        <v>1.072538311814569</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1492099897987178</v>
+        <v>-0.090681634760296</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.62488744372695</v>
+        <v>2.660004456750004</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.987214658641621</v>
+        <v>-3.924421332455894</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.1129581251422</v>
+        <v>1.138075455616491</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.007566768372000876</v>
+        <v>0.06609512341042267</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.712740473935796</v>
+        <v>2.747857486958849</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.032228872162228</v>
+        <v>-3.9694355459765</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.075759895065547</v>
+        <v>1.100877225539838</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.02278212694260373</v>
+        <v>0.03574622809581807</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.675338592078623</v>
+        <v>2.710455605101676</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.299233382434663</v>
+        <v>-4.236440056248935</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9746496532955189</v>
+        <v>0.9997669837698095</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2171451649855523</v>
+        <v>-0.1586168099471305</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.5644123315918</v>
+        <v>2.599529344614853</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.588020602893578</v>
+        <v>-4.525227276707851</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8583386870084542</v>
+        <v>0.8834560174827448</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3182312850845527</v>
+        <v>-0.2597029300461309</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.502964581428901</v>
+        <v>2.538081594451954</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.555545016722806</v>
+        <v>-4.492751690537078</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8689288830310797</v>
+        <v>0.8940462135053704</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3182312850845527</v>
+        <v>-0.2597029300461309</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.500564542983218</v>
+        <v>2.535681556006271</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.536506889015508</v>
+        <v>-4.473713562829781</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8730688533222437</v>
+        <v>0.8981861837965344</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3764148964157472</v>
+        <v>-0.3178865413773254</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.462179095392746</v>
+        <v>2.497296108415799</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.567633520166127</v>
+        <v>-4.504840193980399</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.038200069800677</v>
+        <v>1.063317400274967</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3764148964157472</v>
+        <v>-0.3178865413773254</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.639760964331427</v>
+        <v>2.67487797735448</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.619953900766919</v>
+        <v>-4.557160574581191</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.018105246546494</v>
+        <v>1.043222577020784</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3414680364068751</v>
+        <v>-0.2829396813684533</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.661562409322883</v>
+        <v>2.696679422345936</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.764276806691838</v>
+        <v>-4.70148348050611</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.966384614573452</v>
+        <v>0.9915019450477427</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3414680364068751</v>
+        <v>-0.2829396813684533</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.667570939719809</v>
+        <v>2.702687952742862</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.823862780021393</v>
+        <v>-4.553740510271107</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.021702873033652</v>
+        <v>1.129751780933766</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.3791493045434116</v>
+        <v>-0.1151323241335701</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.724114826629909</v>
+        <v>2.882525014875814</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.925877462552615</v>
+        <v>-4.655755192802329</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9836906215526442</v>
+        <v>1.091739529452758</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.3791493045434116</v>
+        <v>-0.1151323241335701</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.72690844816139</v>
+        <v>2.885318636407295</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.789268118458522</v>
+        <v>-4.519145848708236</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.03899670758194</v>
+        <v>1.147045615482054</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.2425399604493191</v>
+        <v>0.02147701996052237</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.809536403009504</v>
+        <v>2.967946591255409</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.932033451281172</v>
+        <v>-4.661911181530886</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9809710511929897</v>
+        <v>1.089019959093104</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.3853052932719696</v>
+        <v>-0.121288312862128</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.722957680056024</v>
+        <v>2.881367868301929</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.86973545250505</v>
+        <v>-4.599613182754764</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.07222580450026</v>
+        <v>1.180274712400374</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.3853052932719696</v>
+        <v>-0.121288312862128</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.789293233852845</v>
+        <v>2.94770342209875</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848725564462185</v>
+        <v>3.848725564462184</v>
       </c>
       <c r="C1971" t="n">
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.667945254839892</v>
+        <v>-4.397822985089606</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8615227559557208</v>
+        <v>0.9695716638558347</v>
       </c>
       <c r="F1971" t="n">
-        <v>-0.1872871011028152</v>
+        <v>0.07672987930702635</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.616685021543736</v>
+        <v>2.775095209789641</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.747608600760003</v>
+        <v>3.759644785935425</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.645105971078365</v>
+        <v>2.727252143662181</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.667945254839892</v>
+        <v>-4.397822985089606</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8615227559557208</v>
+        <v>0.9695716638558347</v>
       </c>
       <c r="F1972" t="n">
-        <v>-0.1872871011028152</v>
+        <v>0.07672987930702635</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.638169768064733</v>
+        <v>2.720315940648549</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240522.xlsx
+++ b/tame_output/ON/bt/strategyON_20240522.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>60.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>48.1%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>40.9%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.9%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-01</t>
+          <t>2024-05-22</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-5.9%</t>
+          <t>-9.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.5%</t>
+          <t>-6.1%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-3.2%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-38.9%</t>
+          <t>-46.6%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.8%</t>
+          <t>-78.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.8%</t>
+          <t>109.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.9%</t>
+          <t>-74.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>91.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.8%</t>
+          <t>448.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-9.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-601.4%</t>
+          <t>-606.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>1.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-24.1%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-279.3%</t>
+          <t>-281.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>40.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-4.2%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-25.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.6%</t>
+          <t>-14.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-174.0%</t>
+          <t>-181.7%</t>
         </is>
       </c>
     </row>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191732</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108633</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097815</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.419979433923083</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297745</v>
+        <v>3.458100091297746</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317613</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737167</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.50317028234131</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776673</v>
+        <v>3.500446096776674</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199887</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.49996816391063</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078597</v>
+        <v>3.490055666078598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587501888027</v>
+        <v>3.485875018880271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234395</v>
+        <v>3.480688917234396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860584</v>
+        <v>3.493712438860585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767398</v>
+        <v>3.492098065767399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792542</v>
+        <v>3.573670449792543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003468962892</v>
+        <v>3.600034689628921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282097</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116211</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081562</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425322</v>
+        <v>3.728574354425324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702406</v>
+        <v>3.747699084702408</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906222</v>
+        <v>3.766313503906224</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781941</v>
+        <v>3.784680945781943</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567235</v>
+        <v>3.800825778567237</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487764</v>
+        <v>3.789307536487766</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309719</v>
+        <v>3.833249172309721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858722</v>
+        <v>3.839370871858724</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096467</v>
+        <v>3.856158176096469</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761805</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860425</v>
+        <v>3.763178672860427</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575951</v>
+        <v>3.784715218575952</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430985</v>
+        <v>3.753878996430987</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077641</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457897</v>
+        <v>3.770419008457899</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180806</v>
+        <v>3.760330111180807</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879199</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568104</v>
+        <v>3.729966140568106</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963416</v>
+        <v>3.782918957963417</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192814</v>
+        <v>3.828547911192816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262044</v>
+        <v>3.828049353262045</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389907</v>
+        <v>3.812450103389908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788091</v>
+        <v>3.748324832788093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527522</v>
+        <v>3.824307657527524</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749179</v>
+        <v>3.826351398749181</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481492</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862981</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102774</v>
+        <v>3.773761647102776</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353067</v>
+        <v>3.764614304353068</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
@@ -45797,16 +45797,16 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544776</v>
+        <v>3.798811195544777</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.463456242405991</v>
+        <v>-5.513327994744332</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7700071275192615</v>
+        <v>0.7500584265839252</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.6627553313124127</v>
@@ -45820,16 +45820,16 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712285</v>
+        <v>3.797691308712287</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.223025745601131</v>
+        <v>-5.272897497939471</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8679224028660828</v>
+        <v>0.8479737019307465</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.4223248345075524</v>
@@ -45843,16 +45843,16 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837675</v>
+        <v>3.821589933837677</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.150783177429936</v>
+        <v>-5.200654929768277</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9007487439693809</v>
+        <v>0.8808000430340446</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.4223248345075524</v>
@@ -45866,16 +45866,16 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349958</v>
+        <v>3.822323422349959</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.034843327804751</v>
+        <v>-5.084715080143091</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9478032677367949</v>
+        <v>0.9278545668014586</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.3455031034914285</v>
@@ -45889,16 +45889,16 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972331</v>
+        <v>3.848613050972332</v>
       </c>
       <c r="C1928" t="n">
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.926038442325024</v>
+        <v>-4.975910194663364</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9883232931486794</v>
+        <v>0.9683745922133431</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.3455031034914285</v>
@@ -45912,16 +45912,16 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866537614593</v>
+        <v>3.818665376145931</v>
       </c>
       <c r="C1929" t="n">
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.706017644288013</v>
+        <v>-4.755889396626354</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.077910649374098</v>
+        <v>1.057961948438761</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.2042832584234483</v>
@@ -45935,16 +45935,16 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009942</v>
+        <v>3.843270952009943</v>
       </c>
       <c r="C1930" t="n">
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.573149955224736</v>
+        <v>-4.623021707563076</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.146951907801232</v>
+        <v>1.127003206865896</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.2042832584234483</v>
@@ -45958,16 +45958,16 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966254</v>
+        <v>3.845043810966255</v>
       </c>
       <c r="C1931" t="n">
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.413634851705366</v>
+        <v>-4.463506604043706</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.211903793649282</v>
+        <v>1.191955092713946</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.04476815490407837</v>
@@ -45981,16 +45981,16 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046991</v>
+        <v>3.791269976046993</v>
       </c>
       <c r="C1932" t="n">
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.268962706605628</v>
+        <v>-4.318834458943969</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.279860754250617</v>
+        <v>1.259912053315281</v>
       </c>
       <c r="F1932" t="n">
         <v>0.09990399019565904</v>
@@ -46004,16 +46004,16 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.7358356474121</v>
+        <v>3.735835647412102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.328837533963321</v>
+        <v>-4.378709286301661</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.241948314708966</v>
+        <v>1.221999613773629</v>
       </c>
       <c r="F1933" t="n">
         <v>0.04002916283796693</v>
@@ -46027,16 +46027,16 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144512</v>
+        <v>3.762643902144513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.242038036184312</v>
+        <v>-4.291909788522652</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.299068607143135</v>
+        <v>1.279119906207799</v>
       </c>
       <c r="F1934" t="n">
         <v>0.04002916283796693</v>
@@ -46050,16 +46050,16 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900689</v>
+        <v>3.729142822900691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.244507742646118</v>
+        <v>-4.294379494984458</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.298153125931825</v>
+        <v>1.278204424996489</v>
       </c>
       <c r="F1935" t="n">
         <v>0.03755945637616076</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743216620473594</v>
+        <v>3.743216620473595</v>
       </c>
       <c r="C1936" t="n">
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.312877928970128</v>
+        <v>-4.362749681308468</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.281811973876923</v>
+        <v>1.261863272941587</v>
       </c>
       <c r="F1936" t="n">
         <v>0.04683515541237571</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714175563978362</v>
+        <v>3.714175563978364</v>
       </c>
       <c r="C1937" t="n">
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.421416109886262</v>
+        <v>-4.471287862224602</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.228833410142361</v>
+        <v>1.208884709207025</v>
       </c>
       <c r="F1937" t="n">
         <v>0.04683515541237571</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710903155887695</v>
+        <v>3.710903155887697</v>
       </c>
       <c r="C1938" t="n">
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.448144298067664</v>
+        <v>-4.498016050406004</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.042851699910187</v>
+        <v>1.02290299897485</v>
       </c>
       <c r="F1938" t="n">
         <v>0.04683515541237571</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.74603895067589</v>
+        <v>3.746038950675892</v>
       </c>
       <c r="C1939" t="n">
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.272670038275194</v>
+        <v>-4.322541790613535</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.117608635818962</v>
+        <v>1.097659934883626</v>
       </c>
       <c r="F1939" t="n">
         <v>0.04683515541237571</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765020747695436</v>
+        <v>3.765020747695438</v>
       </c>
       <c r="C1940" t="n">
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.383606290916443</v>
+        <v>-4.433478043254784</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.04897616352367</v>
+        <v>1.029027462588334</v>
       </c>
       <c r="F1940" t="n">
         <v>0.04683515541237571</v>
@@ -46188,16 +46188,16 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773206721581285</v>
+        <v>3.773206721581287</v>
       </c>
       <c r="C1941" t="n">
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.586632868459676</v>
+        <v>-4.636504620798017</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9708969177262821</v>
+        <v>0.9509482167909458</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.1561914221308577</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784340376734155</v>
+        <v>3.784340376734157</v>
       </c>
       <c r="C1942" t="n">
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.428707269524383</v>
+        <v>-4.478579021862724</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.044239543732532</v>
+        <v>1.024290842797195</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.1561914221308577</v>
@@ -46234,16 +46234,16 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786946382212292</v>
+        <v>3.786946382212293</v>
       </c>
       <c r="C1943" t="n">
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.342463806498006</v>
+        <v>-4.392335558836346</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.073683199516943</v>
+        <v>1.053734498581607</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.1561914221308577</v>
@@ -46257,16 +46257,16 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752023923786039</v>
+        <v>3.752023923786041</v>
       </c>
       <c r="C1944" t="n">
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.343646891149067</v>
+        <v>-4.393518643487408</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.064985741101044</v>
+        <v>1.045037040165708</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.1618344705973692</v>
@@ -46280,16 +46280,16 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753567590273185</v>
+        <v>3.753567590273187</v>
       </c>
       <c r="C1945" t="n">
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.220519184154984</v>
+        <v>-4.270390936493325</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.114788696931779</v>
+        <v>1.094839995996443</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.1618344705973692</v>
@@ -46303,16 +46303,16 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733387025279495</v>
+        <v>3.733387025279496</v>
       </c>
       <c r="C1946" t="n">
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.127708702704124</v>
+        <v>-4.177580455042465</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.081185581403488</v>
+        <v>1.061236880468152</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.06902398914650987</v>
@@ -46326,16 +46326,16 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748282241030422</v>
+        <v>3.748282241030424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.079145650483095</v>
+        <v>-4.129017402821435</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.102484278216501</v>
+        <v>1.082535577281165</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.02046093692547968</v>
@@ -46349,16 +46349,16 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721073619942734</v>
+        <v>3.721073619942736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.966474432246844</v>
+        <v>-4.016346184585185</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.142628474022724</v>
+        <v>1.122679773087388</v>
       </c>
       <c r="F1948" t="n">
         <v>0.09221028131077053</v>
@@ -46372,16 +46372,16 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743044028268532</v>
+        <v>3.743044028268534</v>
       </c>
       <c r="C1949" t="n">
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.854097431064172</v>
+        <v>-3.903969183402512</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.19307057032646</v>
+        <v>1.173121869391124</v>
       </c>
       <c r="F1949" t="n">
         <v>0.09221028131077053</v>
@@ -46395,16 +46395,16 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689594264968857</v>
+        <v>3.689594264968858</v>
       </c>
       <c r="C1950" t="n">
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.052331999950902</v>
+        <v>-4.102203752289243</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.125273944540307</v>
+        <v>1.105325243604971</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.1060242875759601</v>
@@ -46418,16 +46418,16 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643066046175317</v>
+        <v>3.643066046175318</v>
       </c>
       <c r="C1951" t="n">
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.135333280976181</v>
+        <v>-4.185205033314522</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.930429152130849</v>
+        <v>0.9104804511955127</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.1245951721031338</v>
@@ -46441,16 +46441,16 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682712735199261</v>
+        <v>3.682712735199263</v>
       </c>
       <c r="C1952" t="n">
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.262400287283169</v>
+        <v>-4.31227203962151</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9997520103272595</v>
+        <v>0.9798033093919232</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.1245951721031338</v>
@@ -46464,16 +46464,16 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.73300886566076</v>
+        <v>3.733008865660762</v>
       </c>
       <c r="C1953" t="n">
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.348998870264272</v>
+        <v>-4.398870622602613</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9796256032371411</v>
+        <v>0.959676902301805</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.1245951721031338</v>
@@ -46487,16 +46487,16 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741170494383416</v>
+        <v>3.741170494383417</v>
       </c>
       <c r="C1954" t="n">
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.310615207706121</v>
+        <v>-4.360486960044462</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9923985096027703</v>
+        <v>0.972449808667434</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.08621150954498263</v>
@@ -46510,16 +46510,16 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002476</v>
+        <v>3.751143622002477</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.133498877670955</v>
+        <v>-4.183370630009295</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.059974070462139</v>
+        <v>1.040025369526802</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.08621150954498263</v>
@@ -46533,16 +46533,16 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263893</v>
+        <v>3.741324873263894</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.103796753694661</v>
+        <v>-4.153668506033002</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.072538311814569</v>
+        <v>1.052589610879233</v>
       </c>
       <c r="F1956" t="n">
         <v>-0.090681634760296</v>
@@ -46556,16 +46556,16 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481225</v>
+        <v>3.750725801481227</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.924421332455894</v>
+        <v>-3.974293084794234</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.138075455616491</v>
+        <v>1.118126754681154</v>
       </c>
       <c r="F1957" t="n">
         <v>0.06609512341042267</v>
@@ -46579,16 +46579,16 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452221</v>
+        <v>3.716988143452222</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.9694355459765</v>
+        <v>-4.019307298314841</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.100877225539838</v>
+        <v>1.080928524604502</v>
       </c>
       <c r="F1958" t="n">
         <v>0.03574622809581807</v>
@@ -46602,16 +46602,16 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979527</v>
+        <v>3.737023032979529</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.236440056248935</v>
+        <v>-4.286311808587276</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9997669837698095</v>
+        <v>0.9798182828344733</v>
       </c>
       <c r="F1959" t="n">
         <v>-0.1586168099471305</v>
@@ -46625,16 +46625,16 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230802</v>
+        <v>3.702305879230804</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.525227276707851</v>
+        <v>-4.575099029046191</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8834560174827448</v>
+        <v>0.8635073165474085</v>
       </c>
       <c r="F1960" t="n">
         <v>-0.2597029300461309</v>
@@ -46648,16 +46648,16 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285448</v>
+        <v>3.705568086285449</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.492751690537078</v>
+        <v>-4.542623442875419</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8940462135053704</v>
+        <v>0.8740975125700343</v>
       </c>
       <c r="F1961" t="n">
         <v>-0.2597029300461309</v>
@@ -46671,16 +46671,16 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848096</v>
+        <v>3.709506867848098</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.473713562829781</v>
+        <v>-4.523585315168122</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8981861837965344</v>
+        <v>0.8782374828611981</v>
       </c>
       <c r="F1962" t="n">
         <v>-0.3178865413773254</v>
@@ -46694,16 +46694,16 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601246</v>
+        <v>3.731060897601248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.504840193980399</v>
+        <v>-4.55471194631874</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.063317400274967</v>
+        <v>1.043368699339631</v>
       </c>
       <c r="F1963" t="n">
         <v>-0.3178865413773254</v>
@@ -46717,16 +46717,16 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537857</v>
+        <v>3.722443786537859</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.557160574581191</v>
+        <v>-4.607032326919532</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.043222577020784</v>
+        <v>1.023273876085448</v>
       </c>
       <c r="F1964" t="n">
         <v>-0.2829396813684533</v>
@@ -46740,16 +46740,16 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259113</v>
+        <v>3.787422005259115</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.70148348050611</v>
+        <v>-4.751355232844451</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9915019450477427</v>
+        <v>0.9715532441124064</v>
       </c>
       <c r="F1965" t="n">
         <v>-0.2829396813684533</v>
@@ -46763,16 +46763,16 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781497674989899</v>
+        <v>3.7814976749899</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.553740510271107</v>
+        <v>-4.603612262609448</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.129751780933766</v>
+        <v>1.10980307999843</v>
       </c>
       <c r="F1966" t="n">
         <v>-0.1151323241335701</v>
@@ -46786,16 +46786,16 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224235365116</v>
+        <v>3.802242353651162</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.655755192802329</v>
+        <v>-4.705626945140669</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.091739529452758</v>
+        <v>1.071790828517422</v>
       </c>
       <c r="F1967" t="n">
         <v>-0.1151323241335701</v>
@@ -46809,16 +46809,16 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560540986472</v>
+        <v>3.805605409864722</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.519145848708236</v>
+        <v>-4.569017601046577</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.147045615482054</v>
+        <v>1.127096914546717</v>
       </c>
       <c r="F1968" t="n">
         <v>0.02147701996052237</v>
@@ -46832,16 +46832,16 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798236219360606</v>
+        <v>3.798236219360608</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.661911181530886</v>
+        <v>-4.711782933869227</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.089019959093104</v>
+        <v>1.069071258157767</v>
       </c>
       <c r="F1969" t="n">
         <v>-0.121288312862128</v>
@@ -46855,16 +46855,16 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867359061268417</v>
+        <v>3.867359061268418</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.599613182754764</v>
+        <v>-4.649484935093104</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.180274712400374</v>
+        <v>1.160326011465037</v>
       </c>
       <c r="F1970" t="n">
         <v>-0.121288312862128</v>
@@ -46884,10 +46884,10 @@
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.397822985089606</v>
+        <v>-4.447694737427947</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9695716638558347</v>
+        <v>0.9496229629204986</v>
       </c>
       <c r="F1971" t="n">
         <v>0.07672987930702635</v>
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.759644785935425</v>
+        <v>3.762046590962948</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.727252143662181</v>
+        <v>2.650322586146471</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.397822985089606</v>
+        <v>-4.447694737427947</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9695716638558347</v>
+        <v>0.9496229629204986</v>
       </c>
       <c r="F1972" t="n">
         <v>0.07672987930702635</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.720315940648549</v>
+        <v>2.643386383132839</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240522.xlsx
+++ b/tame_output/ON/bt/strategyON_20240522.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.4%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>54.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.59</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.9%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>48.9%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,11 +811,11 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-05-22</t>
+          <t>2024-05-01</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,12 +824,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-9.0%</t>
+          <t>-5.9%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-6.1%</t>
+          <t>-5.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>28.3%</t>
+          <t>28.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>1.4</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.2%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-46.6%</t>
+          <t>-38.5%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.0%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.7%</t>
+          <t>109.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.2%</t>
+          <t>127.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.8%</t>
+          <t>88.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>24.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.3%</t>
+          <t>-51.2%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.1%</t>
+          <t>-74.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.0%</t>
+          <t>90.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.7%</t>
+          <t>448.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.7%</t>
+          <t>-10.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-606.3%</t>
+          <t>-620.2%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.6%</t>
+          <t>0.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.7%</t>
+          <t>-38.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-23.7%</t>
+          <t>-41.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-281.3%</t>
+          <t>-286.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.4%</t>
+          <t>-22.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.33</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.7%</t>
+          <t>-31.9%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.7%</t>
+          <t>-16.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-213.6%</t>
+          <t>-265.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-216.3%</t>
+          <t>-218.3%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.2%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.4%</t>
+          <t>-27.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.3%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-181.7%</t>
+          <t>-173.6%</t>
         </is>
       </c>
     </row>
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.102608720956703</v>
+        <v>-6.066344719820509</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6752790632324839</v>
+        <v>0.6897846636869618</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.080348183220266</v>
+        <v>-1.100425479901013</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.468470065996753</v>
+        <v>2.456423687988305</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.511197498137381</v>
+        <v>-6.474933497001187</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.510605096374972</v>
+        <v>0.5251106968294494</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.509014257081692</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.222078343703105</v>
+        <v>2.210031965694657</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.787773598453214</v>
+        <v>-6.751509597317019</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3951600887200994</v>
+        <v>0.4096656891745774</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.509014257081692</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.217263776174566</v>
+        <v>2.205217398166118</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.204165472740211</v>
+        <v>-7.167901471604017</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2265973896141777</v>
+        <v>0.2411029900686557</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.509014257081692</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.215257826783443</v>
+        <v>2.203211448774995</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.580842483270056</v>
+        <v>-7.544578482133861</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.08618527607091897</v>
+        <v>0.1006908765253969</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.509014257081692</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.225516517452122</v>
+        <v>2.213470139443674</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.926717305254865</v>
+        <v>-7.890453304118671</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.05606508757730966</v>
+        <v>-0.04155948712283175</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.509014257081692</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.221616082597818</v>
+        <v>2.209569704589369</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.090297183439249</v>
+        <v>-8.054033182303055</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1230921187960621</v>
+        <v>-0.1085865183415846</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.488936960400945</v>
+        <v>-1.509014257081692</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.220021002652818</v>
+        <v>2.20797462464437</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.386958525249447</v>
+        <v>-8.350694524113253</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2379776795909332</v>
+        <v>-0.2234720791364557</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.557680096134823</v>
+        <v>-1.57775739281557</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.182554097141699</v>
+        <v>2.170507719133251</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.510202914464877</v>
+        <v>-8.473938913328682</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2913017398115083</v>
+        <v>-0.2767961393570304</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.557680096134823</v>
+        <v>-1.57775739281557</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.178527792607296</v>
+        <v>2.166481414598848</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.893204303207508</v>
+        <v>-8.856940302071314</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4446043966301447</v>
+        <v>-0.4300987961756668</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.557680096134823</v>
+        <v>-1.57775739281557</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.178425691285712</v>
+        <v>2.166379313277264</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.050603183420629</v>
+        <v>-9.014339182284434</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.504992432743963</v>
+        <v>-0.4904868322894851</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.715078976347944</v>
+        <v>-1.735156273028691</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.08655787912927</v>
+        <v>2.074511501120821</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.41013350592463</v>
+        <v>-9.373869504788436</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6434542584475134</v>
+        <v>-0.6289486579930355</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.715078976347944</v>
+        <v>-1.735156273028691</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.09190818242732</v>
+        <v>2.079861804418872</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.460482569378852</v>
+        <v>-9.424218568242658</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6556778638720249</v>
+        <v>-0.641172263417547</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.765428039802166</v>
+        <v>-1.785505336482913</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.069614764311964</v>
+        <v>2.057568386303516</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.558101846800248</v>
+        <v>-9.521837845664054</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6916838242188144</v>
+        <v>-0.6771782237643365</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.863047317223563</v>
+        <v>-1.88312461390431</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.014084948480895</v>
+        <v>2.002038570472447</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.554410921843838</v>
+        <v>-9.518146920707643</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.69020745423625</v>
+        <v>-0.6757018537817721</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.863047317223563</v>
+        <v>-1.88312461390431</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.014084948480895</v>
+        <v>2.002038570472447</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.758669097173701</v>
+        <v>-9.722405096037507</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7663975272495529</v>
+        <v>-0.7518919267950754</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.990686261837552</v>
+        <v>-2.010763558518299</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.943014778831144</v>
+        <v>1.930968400822696</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.976706868804879</v>
+        <v>-9.940442867668684</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8491300814175879</v>
+        <v>-0.8346244809631105</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.165457029933451</v>
+        <v>-2.185534326614198</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.842634872458041</v>
+        <v>1.830588494449592</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.90323703713743</v>
+        <v>-9.866973036001236</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8043704472571873</v>
+        <v>-0.7898648468027094</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.091987198266002</v>
+        <v>-2.11206449494675</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.902088472951931</v>
+        <v>1.890042094943483</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.07836145452397</v>
+        <v>-10.04209745338778</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8598649934642877</v>
+        <v>-0.8453593930098098</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.267111615652546</v>
+        <v>-2.287188912333293</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.811569043267521</v>
+        <v>1.799522665259073</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.31281354853846</v>
+        <v>-10.27654954740227</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9608649959716797</v>
+        <v>-0.9463593955172018</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.267111615652546</v>
+        <v>-2.287188912333293</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.804349878365925</v>
+        <v>1.792303500357477</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.6006173930757</v>
+        <v>-10.56435339193951</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.082658724560551</v>
+        <v>-1.068153124106074</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.554915460189784</v>
+        <v>-2.574992756870532</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.624995380869606</v>
+        <v>1.612949002861158</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.65340354867603</v>
+        <v>-10.61713954753983</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.102657396962126</v>
+        <v>-1.088151796507648</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.650590946772181</v>
+        <v>-2.670668243452929</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.568705878758724</v>
+        <v>1.556659500750276</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.88543246841229</v>
+        <v>-10.8491684672761</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.192775236227515</v>
+        <v>-1.178269635773038</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.712603643960604</v>
+        <v>-2.732680940641352</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.534191989074785</v>
+        <v>1.522145611066337</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.83341695444348</v>
+        <v>-10.79715295330728</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.16797869495359</v>
+        <v>-1.153473094499112</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.712603643960604</v>
+        <v>-2.732680940641352</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.538182324761186</v>
+        <v>1.526135946752738</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.9750887961676</v>
+        <v>-10.9388247950314</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.226122658541979</v>
+        <v>-1.211617058087501</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.712603643960604</v>
+        <v>-2.732680940641352</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.536707097862444</v>
+        <v>1.524660719853996</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.92549795174276</v>
+        <v>-10.88923395060657</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.191232910607174</v>
+        <v>-1.176727310152696</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.663012799535771</v>
+        <v>-2.683090096216518</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.581515014682217</v>
+        <v>1.569468636673769</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.72634584450566</v>
+        <v>-10.69008184336947</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.124623201359017</v>
+        <v>-1.110117600904539</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.497690273585957</v>
+        <v>-2.517767570266705</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.667657396605422</v>
+        <v>1.655611018596973</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.50050069178625</v>
+        <v>-10.46423669065006</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.024706067235044</v>
+        <v>-1.010200466780566</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.455763597998794</v>
+        <v>-2.475840894679541</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.702392474993929</v>
+        <v>1.69034609698548</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.37592203544866</v>
+        <v>-10.33965803431247</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9737354601439487</v>
+        <v>-0.9592298596894699</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.455763597998794</v>
+        <v>-2.475840894679541</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.703531619549988</v>
+        <v>1.691485241541539</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.42881732349295</v>
+        <v>-10.39255332235675</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9922598011995554</v>
+        <v>-0.9777542007450775</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.450808251910348</v>
+        <v>-2.470885548591095</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.709138601365163</v>
+        <v>1.697092223356715</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.1449085925642</v>
+        <v>-10.108644591428</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8729626045894197</v>
+        <v>-0.8584570041349409</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.450808251910348</v>
+        <v>-2.470885548591095</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.7148723056038</v>
+        <v>1.702825927595351</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.07354219995455</v>
+        <v>-10.03727819881836</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8541533099394254</v>
+        <v>-0.8396477094849475</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.379441859300699</v>
+        <v>-2.399519155981447</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.747954878775723</v>
+        <v>1.735908500767275</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.809705332750482</v>
+        <v>-9.773441331614286</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7585020443707053</v>
+        <v>-0.743996443916227</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.379441859300699</v>
+        <v>-2.399519155981447</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.738071397462815</v>
+        <v>1.726025019454367</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.542463531882085</v>
+        <v>-9.726869358587766</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6534398845227201</v>
+        <v>-0.7272022152049926</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.379441859300699</v>
+        <v>-2.399519155981447</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.736236836963442</v>
+        <v>1.724190458954993</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.444556493205594</v>
+        <v>-9.628962319911276</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6145773840255848</v>
+        <v>-0.6883397147078574</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.311456109440143</v>
+        <v>-2.33153340612089</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.776727971906315</v>
+        <v>1.764681593897867</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.420602952229636</v>
+        <v>-9.605008778935318</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6043274614897078</v>
+        <v>-0.6780897921719804</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.287502568464185</v>
+        <v>-2.307579865144933</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.791768602637383</v>
+        <v>1.779722224628935</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.156543013906839</v>
+        <v>-9.340948840612521</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5119638023223412</v>
+        <v>-0.5857261330046137</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.023442630141389</v>
+        <v>-2.043519926822137</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.936944249469309</v>
+        <v>1.92489787146086</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.449463390402002</v>
+        <v>-8.633869217107684</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2319189865807072</v>
+        <v>-0.3056813172629798</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.023442630141389</v>
+        <v>-2.043519926822137</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.934157215809008</v>
+        <v>1.92211083780056</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.409279092035812</v>
+        <v>-8.593684918741493</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2155016433463897</v>
+        <v>-0.2892639740286622</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.983258331775199</v>
+        <v>-2.003335628455946</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.958611418716564</v>
+        <v>1.946565040708115</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.329209296498007</v>
+        <v>-8.513615123203689</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.1841069039105108</v>
+        <v>-0.2578692345927838</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.903188536237395</v>
+        <v>-1.923265832918142</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.006020117260003</v>
+        <v>1.993973739251555</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.095728074268408</v>
+        <v>-8.280133900974089</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.08278998618081879</v>
+        <v>-0.1565523168630913</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.669707314007796</v>
+        <v>-1.689784610688543</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.154033279435614</v>
+        <v>2.141986901427166</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.946061683260893</v>
+        <v>-8.130467509966575</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.02581564009077209</v>
+        <v>-0.09957797077304509</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.57680382276526</v>
+        <v>-1.596881119446007</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.206883163868177</v>
+        <v>2.194836785859728</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.813786209630006</v>
+        <v>-7.998192036335689</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.02246203610860986</v>
+        <v>-0.05130029457366314</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.444528349134373</v>
+        <v>-1.464605645815121</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.281615934793736</v>
+        <v>2.269569556785287</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.623186534956853</v>
+        <v>-7.807592361662536</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.1015169666655074</v>
+        <v>0.02775463598323435</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.253928674461221</v>
+        <v>-1.274005971141968</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.398790800285264</v>
+        <v>2.386744422276816</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.374186736273272</v>
+        <v>-7.558592562978955</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.2140232273625986</v>
+        <v>0.1402608966803256</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.253928674461221</v>
+        <v>-1.274005971141968</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.411697141508923</v>
+        <v>2.399650763500475</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.479776726046377</v>
+        <v>-7.66418255275206</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.04381130185413795</v>
+        <v>-0.02995102882813505</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.359518664234325</v>
+        <v>-1.379595960915072</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.220367218045842</v>
+        <v>2.208320840037393</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.498511628164974</v>
+        <v>-7.682917454870656</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.08486168288378559</v>
+        <v>0.01109935220151259</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.359518664234325</v>
+        <v>-1.379595960915072</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.268911559922928</v>
+        <v>2.25686518191448</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.350571586757375</v>
+        <v>-7.534977413463057</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.02415877675865774</v>
+        <v>-0.04960355392361526</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.339197748325767</v>
+        <v>-1.359275045006515</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.161225186779895</v>
+        <v>2.149178808771447</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.326342950368402</v>
+        <v>-7.510748777074085</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.02513624506076884</v>
+        <v>-0.04862608562150417</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.335046408617542</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.1670483823598</v>
+        <v>2.155002004351352</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.282794543597712</v>
+        <v>-7.467200370303394</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.03559499567395186</v>
+        <v>-0.03816733500832115</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.335046408617542</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.160087770264707</v>
+        <v>2.148041392256259</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.040646150143854</v>
+        <v>-7.225051976849536</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1469167074366382</v>
+        <v>0.0731543767543652</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.335046408617542</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.17455012464585</v>
+        <v>2.162503746637402</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.977416778375505</v>
+        <v>-7.161822605081188</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1667405766031722</v>
+        <v>0.09297824592089921</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.314969111936795</v>
+        <v>-1.335046408617542</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.169082245105045</v>
+        <v>2.157035867096597</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.854125643558374</v>
+        <v>-7.038531470264057</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.2135551245406018</v>
+        <v>0.1397927938583288</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.191677977119665</v>
+        <v>-1.211755273800412</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.2405550200059</v>
+        <v>2.228508641997452</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.832976444654931</v>
+        <v>-7.017382271360614</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.2297157823393041</v>
+        <v>0.1559534516570311</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.170528778216221</v>
+        <v>-1.190606074896968</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.260945517585291</v>
+        <v>2.248899139576843</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.589211002671487</v>
+        <v>-6.773616829377169</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.3230026674797326</v>
+        <v>0.2492403367974596</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.170528778216221</v>
+        <v>-1.190606074896968</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.256726225932342</v>
+        <v>2.244679847923894</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.442313974953617</v>
+        <v>-6.626719801659299</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3838857924868964</v>
+        <v>0.3101234618046238</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.122870536237633</v>
+        <v>-1.14294783291838</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.287445485039511</v>
+        <v>2.275399107031062</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.192463581004542</v>
+        <v>-6.376869407710224</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4765680250502284</v>
+        <v>0.4028056943679559</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.122870536237633</v>
+        <v>-1.14294783291838</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.280187560023213</v>
+        <v>2.268141182014765</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.01657148853711</v>
+        <v>-6.200977315242792</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5505239855578501</v>
+        <v>0.4767616548755775</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.122870536237633</v>
+        <v>-1.14294783291838</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.283786683543862</v>
+        <v>2.271740305535413</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.845125025514647</v>
+        <v>-6.029530852220328</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6324300768213891</v>
+        <v>0.5586677461391165</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9514240732151701</v>
+        <v>-0.9715013698959173</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.399982067411893</v>
+        <v>2.387935689403445</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.620092025845824</v>
+        <v>-5.804497852551505</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.7214637543052151</v>
+        <v>0.6477014236229426</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7263910735463472</v>
+        <v>-0.7464683702270944</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.534022344829484</v>
+        <v>2.521975966821036</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.556456283611889</v>
+        <v>-5.740862110317571</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7516128522531065</v>
+        <v>0.6778505215708339</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.6627553313124127</v>
+        <v>-0.6828326279931599</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.576898591224162</v>
+        <v>2.564852213215714</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.513327994744332</v>
+        <v>-5.647862069111673</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7500584265839252</v>
+        <v>0.6962447968369885</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.6627553313124127</v>
+        <v>-0.6828326279931599</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.558092850007958</v>
+        <v>2.546046471999509</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.272897497939471</v>
+        <v>-5.407431572306812</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8479737019307465</v>
+        <v>0.7941600721838102</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4223248345075524</v>
+        <v>-0.4424021311882996</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.704094224715751</v>
+        <v>2.692047846707303</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.200654929768277</v>
+        <v>-5.335189004135618</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8808000430340446</v>
+        <v>0.8269864132871083</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4223248345075524</v>
+        <v>-0.4424021311882996</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.708023538550572</v>
+        <v>2.695977160542123</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.084715080143091</v>
+        <v>-5.219249154510432</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9278545668014586</v>
+        <v>0.8740409370545223</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3455031034914285</v>
+        <v>-0.3655804001721757</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.754795161077586</v>
+        <v>2.742748783069137</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.975910194663364</v>
+        <v>-5.110444269030705</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9683745922133431</v>
+        <v>0.9145609624664068</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3455031034914285</v>
+        <v>-0.3655804001721757</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.751793232297579</v>
+        <v>2.739746854289131</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.755889396626354</v>
+        <v>-4.890423470993695</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.057961948438761</v>
+        <v>1.004148318691825</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2042832584234483</v>
+        <v>-0.2243605551041955</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.838104176348982</v>
+        <v>2.826057798340533</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.623021707563076</v>
+        <v>-4.757555781930417</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.127003206865896</v>
+        <v>1.073189577118959</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2042832584234483</v>
+        <v>-0.2243605551041955</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.853998359150805</v>
+        <v>2.841951981142357</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.463506604043706</v>
+        <v>-4.598040678411047</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.191955092713946</v>
+        <v>1.138141462967009</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.04476815490407837</v>
+        <v>-0.06484545158482558</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.950853265702729</v>
+        <v>2.93880688769428</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.318834458943969</v>
+        <v>-4.45336853331131</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.259912053315281</v>
+        <v>1.206098423568344</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.09990399019565904</v>
+        <v>0.07982669351491184</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.047744655324011</v>
+        <v>3.035698277315563</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.378709286301661</v>
+        <v>-4.513243360669002</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.221999613773629</v>
+        <v>1.168185984026693</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.04002916283796693</v>
+        <v>0.01995186615721972</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.997857250310822</v>
+        <v>2.985810872302373</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.291909788522652</v>
+        <v>-4.426443862889993</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.279119906207799</v>
+        <v>1.225306276460863</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.04002916283796693</v>
+        <v>0.01995186615721972</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.020257743633388</v>
+        <v>3.008211365624939</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.294379494984458</v>
+        <v>-4.428913569351799</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.278204424996489</v>
+        <v>1.224390795249553</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.03755945637616076</v>
+        <v>0.01748215969541356</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.018848321129716</v>
+        <v>3.006801943121268</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.362749681308468</v>
+        <v>-4.497283755675809</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.261863272941587</v>
+        <v>1.20804964319465</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.04683515541237571</v>
+        <v>0.0267578587316285</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.035420663026147</v>
+        <v>3.023374285017699</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.471287862224602</v>
+        <v>-4.605821936591943</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.208884709207025</v>
+        <v>1.155071079460088</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.04683515541237571</v>
+        <v>0.0267578587316285</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.025857371658038</v>
+        <v>3.01381099364959</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.498016050406004</v>
+        <v>-4.636815095920649</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.02290299897485</v>
+        <v>0.9673833807689927</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.04683515541237571</v>
+        <v>0.0267578587316285</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.850566936698425</v>
+        <v>2.838520558689977</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.322541790613535</v>
+        <v>-4.46134083612818</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.097659934883626</v>
+        <v>1.042140316677768</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.04683515541237571</v>
+        <v>0.0267578587316285</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.855134168690213</v>
+        <v>2.843087790681765</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.433478043254784</v>
+        <v>-4.572277088769429</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.029027462588334</v>
+        <v>0.9735078443824756</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.04683515541237571</v>
+        <v>0.0267578587316285</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.83087619745142</v>
+        <v>2.818829819442972</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.636504620798017</v>
+        <v>-4.775303666312662</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9509482167909458</v>
+        <v>0.8954285985850878</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.1762687188116049</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.712191636145385</v>
+        <v>2.700145258136937</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.478579021862724</v>
+        <v>-4.617378067377369</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.024290842797195</v>
+        <v>0.9687712245913374</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.1762687188116049</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.722364022577518</v>
+        <v>2.71031764456907</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.392335558836346</v>
+        <v>-4.531134604350991</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.053734498581607</v>
+        <v>0.9982148803757487</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1561914221308577</v>
+        <v>-0.1762687188116049</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.717310293151378</v>
+        <v>2.70526391514293</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.393518643487408</v>
+        <v>-4.532317689002053</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.045037040165708</v>
+        <v>0.9895174219598497</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1618344705973692</v>
+        <v>-0.1819117672781164</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.705700239515997</v>
+        <v>2.693653861507549</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.270390936493325</v>
+        <v>-4.40918998200797</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.094839995996443</v>
+        <v>1.039320377790585</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1618344705973692</v>
+        <v>-0.1819117672781164</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.706252112549099</v>
+        <v>2.69420573454065</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.177580455042465</v>
+        <v>-4.31637950055711</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.061236880468152</v>
+        <v>1.005717262262294</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.06902398914650987</v>
+        <v>-0.08910128582725707</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.691211093310979</v>
+        <v>2.679164715302531</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.129017402821435</v>
+        <v>-4.26781644833608</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.082535577281165</v>
+        <v>1.027015959075307</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.02046093692547968</v>
+        <v>-0.04053823360622688</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.722222400568199</v>
+        <v>2.71017602255975</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.016346184585185</v>
+        <v>-4.15514523009983</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.122679773087388</v>
+        <v>1.06716015488153</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.09221028131077053</v>
+        <v>0.07213298463002332</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.784900840021672</v>
+        <v>2.772854462013223</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.903969183402512</v>
+        <v>-4.042768228917157</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.173121869391124</v>
+        <v>1.117602251185266</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.09221028131077053</v>
+        <v>0.07213298463002332</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.790392135852339</v>
+        <v>2.778345757843891</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.102203752289243</v>
+        <v>-4.241002797803888</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.105325243604971</v>
+        <v>1.049805625399113</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1060242875759601</v>
+        <v>-0.1261015842567073</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.68294859628884</v>
+        <v>2.670902218280391</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.185205033314522</v>
+        <v>-4.324004078829167</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9104804511955127</v>
+        <v>0.8549608329896548</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.1245951721031338</v>
+        <v>-0.144672468783881</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.510161785573189</v>
+        <v>2.49811540756474</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.31227203962151</v>
+        <v>-4.451071085136155</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9798033093919232</v>
+        <v>0.9242836911860652</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.1245951721031338</v>
+        <v>-0.144672468783881</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.630311446292394</v>
+        <v>2.618265068283946</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.398870622602613</v>
+        <v>-4.537669668117258</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.959676902301805</v>
+        <v>0.9041572840959469</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.1245951721031338</v>
+        <v>-0.144672468783881</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.644824472394717</v>
+        <v>2.632778094386269</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.360486960044462</v>
+        <v>-4.499286005559107</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.972449808667434</v>
+        <v>0.9169301904615761</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.08621150954498263</v>
+        <v>-0.1062888062257298</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.665274111271977</v>
+        <v>2.653227733263528</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751143622002477</v>
+        <v>3.751143622002478</v>
       </c>
       <c r="C1955" t="n">
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.183370630009295</v>
+        <v>-4.32216967552394</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.040025369526802</v>
+        <v>0.9845057513209445</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.08621150954498263</v>
+        <v>-0.1062888062257298</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.662003140117279</v>
+        <v>2.64995676210883</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263894</v>
+        <v>3.741324873263895</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.153668506033002</v>
+        <v>-4.292467551547647</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.052589610879233</v>
+        <v>0.997069992673375</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.090681634760296</v>
+        <v>-0.1107589314410432</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.660004456750004</v>
+        <v>2.647958078741556</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.974293084794234</v>
+        <v>-4.113092130308879</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.118126754681154</v>
+        <v>1.062607136475296</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.06609512341042267</v>
+        <v>0.04601782672967547</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.747857486958849</v>
+        <v>2.735811108950401</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.019307298314841</v>
+        <v>-4.158106343829486</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.080928524604502</v>
+        <v>1.025408906398644</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.03574622809581807</v>
+        <v>0.01566893141507086</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.710455605101676</v>
+        <v>2.698409227093228</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.286311808587276</v>
+        <v>-4.425110854101921</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9798182828344733</v>
+        <v>0.9242986646286153</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1586168099471305</v>
+        <v>-0.1786941066278777</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.599529344614853</v>
+        <v>2.587482966606404</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.575099029046191</v>
+        <v>-4.713898074560836</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8635073165474085</v>
+        <v>0.8079876983415506</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2597029300461309</v>
+        <v>-0.2797802267268781</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.538081594451954</v>
+        <v>2.526035216443506</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.542623442875419</v>
+        <v>-4.681422488390064</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8740975125700343</v>
+        <v>0.8185778943641762</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2597029300461309</v>
+        <v>-0.2797802267268781</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.535681556006271</v>
+        <v>2.523635177997822</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.523585315168122</v>
+        <v>-4.662384360682767</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8782374828611981</v>
+        <v>0.8227178646553401</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3178865413773254</v>
+        <v>-0.3379638380580726</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.497296108415799</v>
+        <v>2.485249730407351</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.55471194631874</v>
+        <v>-4.693510991833385</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.043368699339631</v>
+        <v>0.9878490811337732</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3178865413773254</v>
+        <v>-0.3379638380580726</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.67487797735448</v>
+        <v>2.662831599346031</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.607032326919532</v>
+        <v>-4.745831372434177</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.023273876085448</v>
+        <v>0.9677542578795901</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.2829396813684533</v>
+        <v>-0.3030169780492005</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.696679422345936</v>
+        <v>2.684633044337488</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.751355232844451</v>
+        <v>-4.890154278359096</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9715532441124064</v>
+        <v>0.9160336259065485</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.2829396813684533</v>
+        <v>-0.3030169780492005</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.702687952742862</v>
+        <v>2.690641574734414</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.603612262609448</v>
+        <v>-4.742411308124093</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.10980307999843</v>
+        <v>1.054283461792571</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1151323241335701</v>
+        <v>-0.1352096208143173</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.882525014875814</v>
+        <v>2.870478636867366</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.705626945140669</v>
+        <v>-4.844425990655314</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.071790828517422</v>
+        <v>1.016271210311564</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1151323241335701</v>
+        <v>-0.1352096208143173</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.885318636407295</v>
+        <v>2.873272258398847</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.569017601046577</v>
+        <v>-4.707816646561222</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.127096914546717</v>
+        <v>1.071577296340859</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.02147701996052237</v>
+        <v>0.001399723279775167</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.967946591255409</v>
+        <v>2.955900213246961</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.711782933869227</v>
+        <v>-4.850581979383872</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.069071258157767</v>
+        <v>1.01355163995191</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.121288312862128</v>
+        <v>-0.1413656095428752</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.881367868301929</v>
+        <v>2.869321490293481</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.649484935093104</v>
+        <v>-4.78828398060775</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.160326011465037</v>
+        <v>1.104806393259179</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.121288312862128</v>
+        <v>-0.1413656095428752</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.94770342209875</v>
+        <v>2.935657044090302</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.447694737427947</v>
+        <v>-4.586493782942592</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9496229629204986</v>
+        <v>0.8941033447146405</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.07672987930702635</v>
+        <v>0.05665258262627915</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.775095209789641</v>
+        <v>2.763048831781192</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.762046590962948</v>
+        <v>3.827742005147805</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.650322586146471</v>
+        <v>2.731145585719104</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.447694737427947</v>
+        <v>-4.586493782942592</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9496229629204986</v>
+        <v>0.8941033447146405</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.07672987930702635</v>
+        <v>0.05665258262627915</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.643386383132839</v>
+        <v>2.724209382705472</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240522.xlsx
+++ b/tame_output/ON/bt/strategyON_20240522.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>61.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>41.5%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.3%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>-38.4%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-78.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.0%</t>
+          <t>110.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>127.8%</t>
+          <t>128.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>88.6%</t>
+          <t>89.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.3%</t>
+          <t>24.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.2%</t>
+          <t>-51.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.4%</t>
+          <t>-74.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.4%</t>
+          <t>91.4%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.5%</t>
+          <t>448.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-10.0%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-620.2%</t>
+          <t>-613.9%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>1.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-38.6%</t>
+          <t>-39.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-41.3%</t>
+          <t>-27.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-286.8%</t>
+          <t>-283.9%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.8%</t>
+          <t>-22.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.33</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-31.9%</t>
+          <t>-31.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-16.0%</t>
+          <t>-15.8%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.5%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>37.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-265.8%</t>
+          <t>-212.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-218.3%</t>
+          <t>-217.5%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-27.5%</t>
+          <t>-27.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.8</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.2%</t>
+          <t>-14.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-173.6%</t>
+          <t>-168.9%</t>
         </is>
       </c>
     </row>
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.066344719820509</v>
+        <v>-6.102608720956703</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6897846636869618</v>
+        <v>0.6752790632324839</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.100425479901013</v>
+        <v>-1.080348183220266</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.456423687988305</v>
+        <v>2.468470065996753</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.474933497001187</v>
+        <v>-6.511197498137381</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5251106968294494</v>
+        <v>0.510605096374972</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.509014257081692</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.210031965694657</v>
+        <v>2.222078343703105</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.751509597317019</v>
+        <v>-6.865130375788477</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.4096656891745774</v>
+        <v>0.3642173777859945</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.509014257081692</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.205217398166118</v>
+        <v>2.217263776174566</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.167901471604017</v>
+        <v>-7.281522250075474</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.2411029900686557</v>
+        <v>0.1956546786800728</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.509014257081692</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.203211448774995</v>
+        <v>2.215257826783443</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.544578482133861</v>
+        <v>-7.658199260605318</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.1006908765253969</v>
+        <v>0.05524256513681403</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.509014257081692</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.213470139443674</v>
+        <v>2.225516517452122</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.890453304118671</v>
+        <v>-8.004074082590128</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.04155948712283175</v>
+        <v>-0.0870077985114146</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.509014257081692</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.209569704589369</v>
+        <v>2.221616082597818</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.054033182303055</v>
+        <v>-8.167653960774512</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1085865183415846</v>
+        <v>-0.1540348297301675</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.509014257081692</v>
+        <v>-1.488936960400945</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.20797462464437</v>
+        <v>2.220021002652818</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.350694524113253</v>
+        <v>-8.46431530258471</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2234720791364557</v>
+        <v>-0.2689203905250386</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.57775739281557</v>
+        <v>-1.557680096134823</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.170507719133251</v>
+        <v>2.182554097141699</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.473938913328682</v>
+        <v>-8.58755969180014</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.2767961393570304</v>
+        <v>-0.3222444507456133</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.57775739281557</v>
+        <v>-1.557680096134823</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.166481414598848</v>
+        <v>2.178527792607296</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297746</v>
+        <v>3.458100091297745</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.856940302071314</v>
+        <v>-8.970561080542771</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4300987961756668</v>
+        <v>-0.4755471075642497</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.57775739281557</v>
+        <v>-1.557680096134823</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.166379313277264</v>
+        <v>2.178425691285712</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317613</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.014339182284434</v>
+        <v>-9.127959960755891</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.4904868322894851</v>
+        <v>-0.5359351436780679</v>
       </c>
       <c r="F1873" t="n">
-        <v>-1.735156273028691</v>
+        <v>-1.715078976347944</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.074511501120821</v>
+        <v>2.08655787912927</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737167</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.373869504788436</v>
+        <v>-9.487490283259893</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6289486579930355</v>
+        <v>-0.6743969693816183</v>
       </c>
       <c r="F1874" t="n">
-        <v>-1.735156273028691</v>
+        <v>-1.715078976347944</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.079861804418872</v>
+        <v>2.09190818242732</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.50317028234131</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.424218568242658</v>
+        <v>-9.537839346714115</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.641172263417547</v>
+        <v>-0.6866205748061298</v>
       </c>
       <c r="F1875" t="n">
-        <v>-1.785505336482913</v>
+        <v>-1.765428039802166</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.057568386303516</v>
+        <v>2.069614764311964</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776674</v>
+        <v>3.500446096776673</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.521837845664054</v>
+        <v>-9.635458624135511</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.6771782237643365</v>
+        <v>-0.7226265351529193</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.88312461390431</v>
+        <v>-1.863047317223563</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.002038570472447</v>
+        <v>2.014084948480895</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.518146920707643</v>
+        <v>-9.6317676991791</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.6757018537817721</v>
+        <v>-0.7211501651703549</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.88312461390431</v>
+        <v>-1.863047317223563</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.002038570472447</v>
+        <v>2.014084948480895</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.722405096037507</v>
+        <v>-9.836025874508964</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7518919267950754</v>
+        <v>-0.7973402381836583</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.010763558518299</v>
+        <v>-1.990686261837552</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.930968400822696</v>
+        <v>1.943014778831144</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199887</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-9.940442867668684</v>
+        <v>-10.05406364614014</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8346244809631105</v>
+        <v>-0.8800727923516933</v>
       </c>
       <c r="F1879" t="n">
-        <v>-2.185534326614198</v>
+        <v>-2.165457029933451</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.830588494449592</v>
+        <v>1.842634872458041</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.49996816391063</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.866973036001236</v>
+        <v>-9.980593814472693</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.7898648468027094</v>
+        <v>-0.8353131581912923</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.11206449494675</v>
+        <v>-2.091987198266002</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.890042094943483</v>
+        <v>1.902088472951931</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078598</v>
+        <v>3.490055666078597</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.04209745338778</v>
+        <v>-10.15571823185924</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8453593930098098</v>
+        <v>-0.8908077043983926</v>
       </c>
       <c r="F1881" t="n">
-        <v>-2.287188912333293</v>
+        <v>-2.267111615652546</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.799522665259073</v>
+        <v>1.811569043267521</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880271</v>
+        <v>3.48587501888027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.27654954740227</v>
+        <v>-10.39017032587373</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9463593955172018</v>
+        <v>-0.9918077069057847</v>
       </c>
       <c r="F1882" t="n">
-        <v>-2.287188912333293</v>
+        <v>-2.267111615652546</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.792303500357477</v>
+        <v>1.804349878365925</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234396</v>
+        <v>3.480688917234395</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.56435339193951</v>
+        <v>-10.67797417041096</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.068153124106074</v>
+        <v>-1.113601435494657</v>
       </c>
       <c r="F1883" t="n">
-        <v>-2.574992756870532</v>
+        <v>-2.554915460189784</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.612949002861158</v>
+        <v>1.624995380869606</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860585</v>
+        <v>3.493712438860584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.61713954753983</v>
+        <v>-10.73076032601129</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.088151796507648</v>
+        <v>-1.133600107896231</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.670668243452929</v>
+        <v>-2.650590946772181</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.556659500750276</v>
+        <v>1.568705878758724</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767399</v>
+        <v>3.492098065767398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.8491684672761</v>
+        <v>-10.96278924574755</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.178269635773038</v>
+        <v>-1.223717947161621</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.732680940641352</v>
+        <v>-2.712603643960604</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.522145611066337</v>
+        <v>1.534191989074785</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792543</v>
+        <v>3.573670449792542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.79715295330728</v>
+        <v>-10.91077373177874</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.153473094499112</v>
+        <v>-1.198921405887694</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.732680940641352</v>
+        <v>-2.712603643960604</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.526135946752738</v>
+        <v>1.538182324761186</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628921</v>
+        <v>3.60003468962892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-10.9388247950314</v>
+        <v>-11.05244557350286</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.211617058087501</v>
+        <v>-1.257065369476084</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.732680940641352</v>
+        <v>-2.712603643960604</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.524660719853996</v>
+        <v>1.536707097862444</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410717</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-10.88923395060657</v>
+        <v>-11.00285472907803</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.176727310152696</v>
+        <v>-1.222175621541278</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.683090096216518</v>
+        <v>-2.663012799535771</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.569468636673769</v>
+        <v>1.581515014682217</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.69008184336947</v>
+        <v>-10.80370262184093</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.110117600904539</v>
+        <v>-1.155565912293122</v>
       </c>
       <c r="F1889" t="n">
-        <v>-2.517767570266705</v>
+        <v>-2.497690273585957</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.655611018596973</v>
+        <v>1.667657396605422</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.46423669065006</v>
+        <v>-10.57785746912151</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.010200466780566</v>
+        <v>-1.055648778169149</v>
       </c>
       <c r="F1890" t="n">
-        <v>-2.475840894679541</v>
+        <v>-2.455763597998794</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.69034609698548</v>
+        <v>1.702392474993929</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.684840248282097</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.33965803431247</v>
+        <v>-10.45327881278392</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.9592298596894699</v>
+        <v>-1.004678171078053</v>
       </c>
       <c r="F1891" t="n">
-        <v>-2.475840894679541</v>
+        <v>-2.455763597998794</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.691485241541539</v>
+        <v>1.703531619549988</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116211</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.39255332235675</v>
+        <v>-10.50617410082821</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.9777542007450775</v>
+        <v>-1.02320251213366</v>
       </c>
       <c r="F1892" t="n">
-        <v>-2.470885548591095</v>
+        <v>-2.450808251910348</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.697092223356715</v>
+        <v>1.709138601365163</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081562</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.108644591428</v>
+        <v>-10.22226536989946</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.8584570041349409</v>
+        <v>-0.9039053155235237</v>
       </c>
       <c r="F1893" t="n">
-        <v>-2.470885548591095</v>
+        <v>-2.450808251910348</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.702825927595351</v>
+        <v>1.7148723056038</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425322</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.03727819881836</v>
+        <v>-10.15089897728981</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8396477094849475</v>
+        <v>-0.8850960208735303</v>
       </c>
       <c r="F1894" t="n">
-        <v>-2.399519155981447</v>
+        <v>-2.379441859300699</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.735908500767275</v>
+        <v>1.747954878775723</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702406</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.773441331614286</v>
+        <v>-9.887062110085743</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.743996443916227</v>
+        <v>-0.7894447553048098</v>
       </c>
       <c r="F1895" t="n">
-        <v>-2.399519155981447</v>
+        <v>-2.379441859300699</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.726025019454367</v>
+        <v>1.738071397462815</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906222</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.726869358587766</v>
+        <v>-9.619820309217346</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.7272022152049926</v>
+        <v>-0.6843825954568246</v>
       </c>
       <c r="F1896" t="n">
-        <v>-2.399519155981447</v>
+        <v>-2.379441859300699</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.724190458954993</v>
+        <v>1.736236836963442</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781943</v>
+        <v>3.784680945781941</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.628962319911276</v>
+        <v>-9.521913270540855</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6883397147078574</v>
+        <v>-0.6455200949596889</v>
       </c>
       <c r="F1897" t="n">
-        <v>-2.33153340612089</v>
+        <v>-2.311456109440143</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.764681593897867</v>
+        <v>1.776727971906315</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567237</v>
+        <v>3.800825778567235</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.605008778935318</v>
+        <v>-9.497959729564897</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6780897921719804</v>
+        <v>-0.6352701724238123</v>
       </c>
       <c r="F1898" t="n">
-        <v>-2.307579865144933</v>
+        <v>-2.287502568464185</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.779722224628935</v>
+        <v>1.791768602637383</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487766</v>
+        <v>3.789307536487764</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.340948840612521</v>
+        <v>-9.2338997912421</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5857261330046137</v>
+        <v>-0.5429065132564457</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.043519926822137</v>
+        <v>-2.023442630141389</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.92489787146086</v>
+        <v>1.936944249469309</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309721</v>
+        <v>3.833249172309719</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.633869217107684</v>
+        <v>-8.526820167737263</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.3056813172629798</v>
+        <v>-0.2628616975148117</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.043519926822137</v>
+        <v>-2.023442630141389</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.92211083780056</v>
+        <v>1.934157215809008</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858724</v>
+        <v>3.839370871858722</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.593684918741493</v>
+        <v>-8.486635869371073</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2892639740286622</v>
+        <v>-0.2464443542804942</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.003335628455946</v>
+        <v>-1.983258331775199</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.946565040708115</v>
+        <v>1.958611418716564</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096469</v>
+        <v>3.856158176096467</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.513615123203689</v>
+        <v>-8.406566073833268</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2578692345927838</v>
+        <v>-0.2150496148446153</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.923265832918142</v>
+        <v>-1.903188536237395</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.993973739251555</v>
+        <v>2.006020117260003</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761807</v>
+        <v>3.787326853761805</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.280133900974089</v>
+        <v>-8.173084851603669</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1565523168630913</v>
+        <v>-0.1137326971149233</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.689784610688543</v>
+        <v>-1.669707314007796</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.141986901427166</v>
+        <v>2.154033279435614</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255785</v>
+        <v>3.801633547255783</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.130467509966575</v>
+        <v>-8.023418460596154</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.09957797077304509</v>
+        <v>-0.05675835102487659</v>
       </c>
       <c r="F1904" t="n">
-        <v>-1.596881119446007</v>
+        <v>-1.57680382276526</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.194836785859728</v>
+        <v>2.206883163868177</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860427</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.998192036335689</v>
+        <v>-7.891142986965268</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.05130029457366314</v>
+        <v>-0.008480674825495083</v>
       </c>
       <c r="F1905" t="n">
-        <v>-1.464605645815121</v>
+        <v>-1.444528349134373</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.269569556785287</v>
+        <v>2.281615934793736</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575952</v>
+        <v>3.784715218575951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.807592361662536</v>
+        <v>-7.700543312292115</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.02775463598323435</v>
+        <v>0.07057425573140286</v>
       </c>
       <c r="F1906" t="n">
-        <v>-1.274005971141968</v>
+        <v>-1.253928674461221</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.386744422276816</v>
+        <v>2.398790800285264</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430987</v>
+        <v>3.753878996430985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.558592562978955</v>
+        <v>-7.451543513608534</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1402608966803256</v>
+        <v>0.1830805164284937</v>
       </c>
       <c r="F1907" t="n">
-        <v>-1.274005971141968</v>
+        <v>-1.253928674461221</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.399650763500475</v>
+        <v>2.411697141508923</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077641</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.66418255275206</v>
+        <v>-7.557133503381639</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.02995102882813505</v>
+        <v>0.01286859092003345</v>
       </c>
       <c r="F1908" t="n">
-        <v>-1.379595960915072</v>
+        <v>-1.359518664234325</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.208320840037393</v>
+        <v>2.220367218045842</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457899</v>
+        <v>3.770419008457897</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.682917454870656</v>
+        <v>-7.575868405500236</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.01109935220151259</v>
+        <v>0.05391897194968109</v>
       </c>
       <c r="F1909" t="n">
-        <v>-1.379595960915072</v>
+        <v>-1.359518664234325</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.25686518191448</v>
+        <v>2.268911559922928</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180806</v>
       </c>
       <c r="C1910" t="n">
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.534977413463057</v>
+        <v>-7.427928364092637</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.04960355392361526</v>
+        <v>-0.00678393417544676</v>
       </c>
       <c r="F1910" t="n">
-        <v>-1.359275045006515</v>
+        <v>-1.339197748325767</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.149178808771447</v>
+        <v>2.161225186779895</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879201</v>
+        <v>3.723562653879199</v>
       </c>
       <c r="C1911" t="n">
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.510748777074085</v>
+        <v>-7.403699727703664</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.04862608562150417</v>
+        <v>-0.005806465873336109</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.335046408617542</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.155002004351352</v>
+        <v>2.1670483823598</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568106</v>
+        <v>3.729966140568104</v>
       </c>
       <c r="C1912" t="n">
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.467200370303394</v>
+        <v>-7.360151320932974</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.03816733500832115</v>
+        <v>0.004652284739846912</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.335046408617542</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.148041392256259</v>
+        <v>2.160087770264707</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963417</v>
+        <v>3.782918957963416</v>
       </c>
       <c r="C1913" t="n">
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.225051976849536</v>
+        <v>-7.118002927479115</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.0731543767543652</v>
+        <v>0.1159739965025333</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.335046408617542</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.162503746637402</v>
+        <v>2.17455012464585</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828547911192816</v>
+        <v>3.828547911192814</v>
       </c>
       <c r="C1914" t="n">
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.161822605081188</v>
+        <v>-7.054773555710767</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.09297824592089921</v>
+        <v>0.1357978656690677</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.335046408617542</v>
+        <v>-1.314969111936795</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.157035867096597</v>
+        <v>2.169082245105045</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828049353262045</v>
+        <v>3.828049353262044</v>
       </c>
       <c r="C1915" t="n">
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.038531470264057</v>
+        <v>-6.931482420893636</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1397927938583288</v>
+        <v>0.1826124136064968</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.211755273800412</v>
+        <v>-1.191677977119665</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.228508641997452</v>
+        <v>2.2405550200059</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389908</v>
+        <v>3.812450103389907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.017382271360614</v>
+        <v>-6.910333221990193</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1559534516570311</v>
+        <v>0.1987730714051992</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.190606074896968</v>
+        <v>-1.170528778216221</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.248899139576843</v>
+        <v>2.260945517585291</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788093</v>
+        <v>3.748324832788091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.773616829377169</v>
+        <v>-6.666567780006749</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2492403367974596</v>
+        <v>0.2920599565456277</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.190606074896968</v>
+        <v>-1.170528778216221</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.244679847923894</v>
+        <v>2.256726225932342</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824307657527524</v>
+        <v>3.824307657527522</v>
       </c>
       <c r="C1918" t="n">
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.626719801659299</v>
+        <v>-6.519670752288878</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3101234618046238</v>
+        <v>0.3529430815527919</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.14294783291838</v>
+        <v>-1.122870536237633</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.275399107031062</v>
+        <v>2.287445485039511</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749181</v>
+        <v>3.826351398749179</v>
       </c>
       <c r="C1919" t="n">
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.376869407710224</v>
+        <v>-6.269820358339803</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4028056943679559</v>
+        <v>0.4456253141161239</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.14294783291838</v>
+        <v>-1.122870536237633</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.268141182014765</v>
+        <v>2.280187560023213</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481493</v>
+        <v>3.835954411481492</v>
       </c>
       <c r="C1920" t="n">
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.200977315242792</v>
+        <v>-6.093928265872371</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4767616548755775</v>
+        <v>0.5195812746237456</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.14294783291838</v>
+        <v>-1.122870536237633</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.271740305535413</v>
+        <v>2.283786683543862</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862982</v>
+        <v>3.780930335862981</v>
       </c>
       <c r="C1921" t="n">
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.029530852220328</v>
+        <v>-5.922481802849908</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5586677461391165</v>
+        <v>0.6014873658872846</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.9715013698959173</v>
+        <v>-0.9514240732151701</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.387935689403445</v>
+        <v>2.399982067411893</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102776</v>
+        <v>3.773761647102774</v>
       </c>
       <c r="C1922" t="n">
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.804497852551505</v>
+        <v>-5.697448803181085</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6477014236229426</v>
+        <v>0.6905210433711111</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.7464683702270944</v>
+        <v>-0.7263910735463472</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.521975966821036</v>
+        <v>2.534022344829484</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353068</v>
+        <v>3.764614304353066</v>
       </c>
       <c r="C1923" t="n">
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.740862110317571</v>
+        <v>-5.63381306094715</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6778505215708339</v>
+        <v>0.720670141319002</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.6828326279931599</v>
+        <v>-0.6627553313124127</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.564852213215714</v>
+        <v>2.576898591224162</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.798811195544775</v>
       </c>
       <c r="C1924" t="n">
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.647862069111673</v>
+        <v>-5.540813019741252</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6962447968369885</v>
+        <v>0.739064416585157</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.6828326279931599</v>
+        <v>-0.6627553313124127</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.546046471999509</v>
+        <v>2.558092850007958</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712287</v>
+        <v>3.797691308712285</v>
       </c>
       <c r="C1925" t="n">
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.407431572306812</v>
+        <v>-5.300382522936392</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7941600721838102</v>
+        <v>0.8369796919319783</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.4424021311882996</v>
+        <v>-0.4223248345075524</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.692047846707303</v>
+        <v>2.704094224715751</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837677</v>
+        <v>3.821589933837675</v>
       </c>
       <c r="C1926" t="n">
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.335189004135618</v>
+        <v>-5.228139954765197</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8269864132871083</v>
+        <v>0.8698060330352764</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.4424021311882996</v>
+        <v>-0.4223248345075524</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.695977160542123</v>
+        <v>2.708023538550572</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349959</v>
+        <v>3.822323422349958</v>
       </c>
       <c r="C1927" t="n">
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.219249154510432</v>
+        <v>-5.112200105140012</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.8740409370545223</v>
+        <v>0.9168605568026904</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.3655804001721757</v>
+        <v>-0.3455031034914285</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.742748783069137</v>
+        <v>2.754795161077586</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.110444269030705</v>
+        <v>-5.003395219660285</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9145609624664068</v>
+        <v>0.9573805822145749</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.3655804001721757</v>
+        <v>-0.3455031034914285</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.739746854289131</v>
+        <v>2.751793232297579</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.890423470993695</v>
+        <v>-4.783374421623274</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.004148318691825</v>
+        <v>1.046967938439993</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.2243605551041955</v>
+        <v>-0.2042832584234483</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.826057798340533</v>
+        <v>2.838104176348982</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.757555781930417</v>
+        <v>-4.650506732559997</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.073189577118959</v>
+        <v>1.116009196867128</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.2243605551041955</v>
+        <v>-0.2042832584234483</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.841951981142357</v>
+        <v>2.853998359150805</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.598040678411047</v>
+        <v>-4.490991629040627</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.138141462967009</v>
+        <v>1.180961082715177</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.06484545158482558</v>
+        <v>-0.04476815490407837</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.93880688769428</v>
+        <v>2.950853265702729</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.45336853331131</v>
+        <v>-4.346319483940889</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.206098423568344</v>
+        <v>1.248918043316512</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.07982669351491184</v>
+        <v>0.09990399019565904</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.035698277315563</v>
+        <v>3.047744655324011</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.513243360669002</v>
+        <v>-4.406194311298582</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.168185984026693</v>
+        <v>1.211005603774861</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.01995186615721972</v>
+        <v>0.04002916283796693</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.985810872302373</v>
+        <v>2.997857250310822</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.426443862889993</v>
+        <v>-4.319394813519573</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.225306276460863</v>
+        <v>1.268125896209031</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.01995186615721972</v>
+        <v>0.04002916283796693</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.008211365624939</v>
+        <v>3.020257743633388</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.428913569351799</v>
+        <v>-4.321864519981379</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.224390795249553</v>
+        <v>1.267210414997721</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.01748215969541356</v>
+        <v>0.03755945637616076</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.006801943121268</v>
+        <v>3.018848321129716</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.497283755675809</v>
+        <v>-4.390234706305389</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.20804964319465</v>
+        <v>1.250869262942819</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.0267578587316285</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.023374285017699</v>
+        <v>3.035420663026147</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.605821936591943</v>
+        <v>-4.498772887221523</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.155071079460088</v>
+        <v>1.197890699208256</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.0267578587316285</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.01381099364959</v>
+        <v>3.025857371658038</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.636815095920649</v>
+        <v>-4.529766046550228</v>
       </c>
       <c r="E1938" t="n">
-        <v>0.9673833807689927</v>
+        <v>1.010203000517161</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.0267578587316285</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.838520558689977</v>
+        <v>2.850566936698425</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.46134083612818</v>
+        <v>-4.354291786757759</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.042140316677768</v>
+        <v>1.084959936425936</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.0267578587316285</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.843087790681765</v>
+        <v>2.855134168690213</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.572277088769429</v>
+        <v>-4.465228039399008</v>
       </c>
       <c r="E1940" t="n">
-        <v>0.9735078443824756</v>
+        <v>1.016327464130644</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.0267578587316285</v>
+        <v>0.04683515541237571</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.818829819442972</v>
+        <v>2.83087619745142</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.775303666312662</v>
+        <v>-4.668254616942241</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.8954285985850878</v>
+        <v>0.9382482183332561</v>
       </c>
       <c r="F1941" t="n">
-        <v>-0.1762687188116049</v>
+        <v>-0.1561914221308577</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.700145258136937</v>
+        <v>2.712191636145385</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.617378067377369</v>
+        <v>-4.510329018006948</v>
       </c>
       <c r="E1942" t="n">
-        <v>0.9687712245913374</v>
+        <v>1.011590844339506</v>
       </c>
       <c r="F1942" t="n">
-        <v>-0.1762687188116049</v>
+        <v>-0.1561914221308577</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.71031764456907</v>
+        <v>2.722364022577518</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.531134604350991</v>
+        <v>-4.424085554980571</v>
       </c>
       <c r="E1943" t="n">
-        <v>0.9982148803757487</v>
+        <v>1.041034500123917</v>
       </c>
       <c r="F1943" t="n">
-        <v>-0.1762687188116049</v>
+        <v>-0.1561914221308577</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.70526391514293</v>
+        <v>2.717310293151378</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.532317689002053</v>
+        <v>-4.425268639631632</v>
       </c>
       <c r="E1944" t="n">
-        <v>0.9895174219598497</v>
+        <v>1.032337041708018</v>
       </c>
       <c r="F1944" t="n">
-        <v>-0.1819117672781164</v>
+        <v>-0.1618344705973692</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.693653861507549</v>
+        <v>2.705700239515997</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.40918998200797</v>
+        <v>-4.302140932637549</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.039320377790585</v>
+        <v>1.082139997538753</v>
       </c>
       <c r="F1945" t="n">
-        <v>-0.1819117672781164</v>
+        <v>-0.1618344705973692</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.69420573454065</v>
+        <v>2.706252112549099</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.31637950055711</v>
+        <v>-4.209330451186689</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.005717262262294</v>
+        <v>1.048536882010462</v>
       </c>
       <c r="F1946" t="n">
-        <v>-0.08910128582725707</v>
+        <v>-0.06902398914650987</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.679164715302531</v>
+        <v>2.691211093310979</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.26781644833608</v>
+        <v>-4.16076739896566</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.027015959075307</v>
+        <v>1.069835578823475</v>
       </c>
       <c r="F1947" t="n">
-        <v>-0.04053823360622688</v>
+        <v>-0.02046093692547968</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.71017602255975</v>
+        <v>2.722222400568199</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.15514523009983</v>
+        <v>-4.048096180729409</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.06716015488153</v>
+        <v>1.109979774629698</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.07213298463002332</v>
+        <v>0.09221028131077053</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.772854462013223</v>
+        <v>2.784900840021672</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-4.042768228917157</v>
+        <v>-3.935719179546737</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.117602251185266</v>
+        <v>1.160421870933434</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.07213298463002332</v>
+        <v>0.09221028131077053</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.778345757843891</v>
+        <v>2.790392135852339</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.241002797803888</v>
+        <v>-4.133953748433467</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.049805625399113</v>
+        <v>1.092625245147281</v>
       </c>
       <c r="F1950" t="n">
-        <v>-0.1261015842567073</v>
+        <v>-0.1060242875759601</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.670902218280391</v>
+        <v>2.68294859628884</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.324004078829167</v>
+        <v>-4.216955029458746</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8549608329896548</v>
+        <v>0.897780452737823</v>
       </c>
       <c r="F1951" t="n">
-        <v>-0.144672468783881</v>
+        <v>-0.1245951721031338</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.49811540756474</v>
+        <v>2.510161785573189</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.451071085136155</v>
+        <v>-4.344022035765734</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9242836911860652</v>
+        <v>0.9671033109342333</v>
       </c>
       <c r="F1952" t="n">
-        <v>-0.144672468783881</v>
+        <v>-0.1245951721031338</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.618265068283946</v>
+        <v>2.630311446292394</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.537669668117258</v>
+        <v>-4.430620618746837</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9041572840959469</v>
+        <v>0.9469769038441151</v>
       </c>
       <c r="F1953" t="n">
-        <v>-0.144672468783881</v>
+        <v>-0.1245951721031338</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.632778094386269</v>
+        <v>2.644824472394717</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.499286005559107</v>
+        <v>-4.392236956188686</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9169301904615761</v>
+        <v>0.9597498102097444</v>
       </c>
       <c r="F1954" t="n">
-        <v>-0.1062888062257298</v>
+        <v>-0.08621150954498263</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.653227733263528</v>
+        <v>2.665274111271977</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.32216967552394</v>
+        <v>-4.21512062615352</v>
       </c>
       <c r="E1955" t="n">
-        <v>0.9845057513209445</v>
+        <v>1.027325371069113</v>
       </c>
       <c r="F1955" t="n">
-        <v>-0.1062888062257298</v>
+        <v>-0.08621150954498263</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.64995676210883</v>
+        <v>2.662003140117279</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.292467551547647</v>
+        <v>-4.269526293330919</v>
       </c>
       <c r="E1956" t="n">
-        <v>0.997069992673375</v>
+        <v>1.006246495960066</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1107589314410432</v>
+        <v>-0.1430088562630189</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.647958078741556</v>
+        <v>2.62860812384837</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.113092130308879</v>
+        <v>-4.090150872092152</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.062607136475296</v>
+        <v>1.071783639761987</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.04601782672967547</v>
+        <v>0.01376790190769978</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.735811108950401</v>
+        <v>2.716461154057216</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452222</v>
+        <v>3.716988143452223</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.158106343829486</v>
+        <v>-4.135165085612758</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.025408906398644</v>
+        <v>1.034585409685334</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.01566893141507086</v>
+        <v>-0.01658099340690483</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.698409227093228</v>
+        <v>2.679059272200043</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737023032979529</v>
+        <v>3.73702303297953</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.425110854101921</v>
+        <v>-4.402169595885193</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9242986646286153</v>
+        <v>0.9334751679153062</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.1786941066278777</v>
+        <v>-0.2109440314498534</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.587482966606404</v>
+        <v>2.568133011713219</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702305879230804</v>
+        <v>3.702305879230805</v>
       </c>
       <c r="C1960" t="n">
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.713898074560836</v>
+        <v>-4.690956816344109</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8079876983415506</v>
+        <v>0.8171642016282417</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.2797802267268781</v>
+        <v>-0.3120301515488538</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.526035216443506</v>
+        <v>2.50668526155032</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705568086285449</v>
+        <v>3.70556808628545</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.681422488390064</v>
+        <v>-4.658481230173336</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8185778943641762</v>
+        <v>0.8277543976508672</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.2797802267268781</v>
+        <v>-0.3120301515488538</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.523635177997822</v>
+        <v>2.504285223104637</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.662384360682767</v>
+        <v>-4.639443102466039</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.8227178646553401</v>
+        <v>0.831894367942031</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3379638380580726</v>
+        <v>-0.3702137628800483</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.485249730407351</v>
+        <v>2.465899775514165</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731060897601248</v>
+        <v>3.73106089760125</v>
       </c>
       <c r="C1963" t="n">
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.693510991833385</v>
+        <v>-4.670569733616658</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9878490811337732</v>
+        <v>0.9970255844204643</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3379638380580726</v>
+        <v>-0.3702137628800483</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.662831599346031</v>
+        <v>2.643481644452846</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722443786537859</v>
+        <v>3.722443786537861</v>
       </c>
       <c r="C1964" t="n">
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.745831372434177</v>
+        <v>-4.722890114217449</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.9677542578795901</v>
+        <v>0.976930761166281</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3030169780492005</v>
+        <v>-0.3352669028711762</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.684633044337488</v>
+        <v>2.665283089444303</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787422005259115</v>
+        <v>3.787422005259117</v>
       </c>
       <c r="C1965" t="n">
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.890154278359096</v>
+        <v>-4.867213020142368</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9160336259065485</v>
+        <v>0.9252101291932395</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3030169780492005</v>
+        <v>-0.3352669028711762</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.690641574734414</v>
+        <v>2.671291619841229</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.7814976749899</v>
+        <v>3.781497674989902</v>
       </c>
       <c r="C1966" t="n">
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.742411308124093</v>
+        <v>-4.719470049907366</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.054283461792571</v>
+        <v>1.063459965079262</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.1352096208143173</v>
+        <v>-0.167459545636293</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.870478636867366</v>
+        <v>2.85112868197418</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802242353651162</v>
+        <v>3.802242353651164</v>
       </c>
       <c r="C1967" t="n">
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.844425990655314</v>
+        <v>-4.821484732438587</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.016271210311564</v>
+        <v>1.025447713598255</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.1352096208143173</v>
+        <v>-0.167459545636293</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.873272258398847</v>
+        <v>2.853922303505661</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805605409864722</v>
+        <v>3.805605409864723</v>
       </c>
       <c r="C1968" t="n">
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.707816646561222</v>
+        <v>-4.684875388344494</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.071577296340859</v>
+        <v>1.08075379962755</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.001399723279775167</v>
+        <v>-0.03085020154220053</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.955900213246961</v>
+        <v>2.936550258353775</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798236219360608</v>
+        <v>3.79823621936061</v>
       </c>
       <c r="C1969" t="n">
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.850581979383872</v>
+        <v>-4.827640721167144</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.01355163995191</v>
+        <v>1.0227281432386</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1413656095428752</v>
+        <v>-0.1736155343648509</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.869321490293481</v>
+        <v>2.849971535400295</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867359061268418</v>
+        <v>3.86735906126842</v>
       </c>
       <c r="C1970" t="n">
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.78828398060775</v>
+        <v>-4.765342722391022</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.104806393259179</v>
+        <v>1.11398289654587</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.1413656095428752</v>
+        <v>-0.1736155343648509</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.935657044090302</v>
+        <v>2.916307089197116</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848725564462184</v>
+        <v>3.848725564462185</v>
       </c>
       <c r="C1971" t="n">
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.586493782942592</v>
+        <v>-4.563552524725864</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.8941033447146405</v>
+        <v>0.9032798480013315</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.05665258262627915</v>
+        <v>0.02440265780430345</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.763048831781192</v>
+        <v>2.743698876888007</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.827742005147805</v>
+        <v>3.781247022321528</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.731145585719104</v>
+        <v>2.732351656133147</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.586493782942592</v>
+        <v>-4.522983447524596</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.8941033447146405</v>
+        <v>0.9228018528095616</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.05665258262627915</v>
+        <v>0.06497173500557157</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.724209382705472</v>
+        <v>2.771334697136491</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240522.xlsx
+++ b/tame_output/ON/bt/strategyON_20240522.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.4%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>54.4%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>41.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-4.3%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>38.7%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.5%</t>
+          <t>-77.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>110.2%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>128.9%</t>
+          <t>127.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>89.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.9%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-51.8%</t>
+          <t>-51.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.6%</t>
+          <t>-73.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>91.4%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>448.9%</t>
+          <t>448.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-10.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-613.9%</t>
+          <t>-607.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.0%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.03</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-39.1%</t>
+          <t>-38.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-27.1%</t>
+          <t>-22.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-283.9%</t>
+          <t>-281.3%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-22.6%</t>
+          <t>-22.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-15.8%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>37.9%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-212.9%</t>
+          <t>-226.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-217.5%</t>
+          <t>-215.6%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.8%</t>
+          <t>-15.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>33.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-168.9%</t>
+          <t>-167.7%</t>
         </is>
       </c>
     </row>
@@ -44446,10 +44446,10 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.865130375788477</v>
+        <v>-6.787773598453214</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3642173777859945</v>
+        <v>0.3951600887200994</v>
       </c>
       <c r="F1865" t="n">
         <v>-1.488936960400945</v>
@@ -44469,10 +44469,10 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.281522250075474</v>
+        <v>-7.204165472740211</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1956546786800728</v>
+        <v>0.2265973896141777</v>
       </c>
       <c r="F1866" t="n">
         <v>-1.488936960400945</v>
@@ -44492,10 +44492,10 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.658199260605318</v>
+        <v>-7.508500860725634</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.05524256513681403</v>
+        <v>0.1151219250886877</v>
       </c>
       <c r="F1867" t="n">
         <v>-1.488936960400945</v>
@@ -44515,10 +44515,10 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.004074082590128</v>
+        <v>-7.854375682710442</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.0870077985114146</v>
+        <v>-0.0271284385595405</v>
       </c>
       <c r="F1868" t="n">
         <v>-1.488936960400945</v>
@@ -44538,10 +44538,10 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.167653960774512</v>
+        <v>-8.017955560894826</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.1540348297301675</v>
+        <v>-0.09415546977829292</v>
       </c>
       <c r="F1869" t="n">
         <v>-1.488936960400945</v>
@@ -44561,10 +44561,10 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.46431530258471</v>
+        <v>-8.314616902705025</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.2689203905250386</v>
+        <v>-0.209041030573164</v>
       </c>
       <c r="F1870" t="n">
         <v>-1.557680096134823</v>
@@ -44584,10 +44584,10 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-8.58755969180014</v>
+        <v>-8.437861291920454</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.3222444507456133</v>
+        <v>-0.2623650907937392</v>
       </c>
       <c r="F1871" t="n">
         <v>-1.557680096134823</v>
@@ -44607,10 +44607,10 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-8.970561080542771</v>
+        <v>-8.820862680663085</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.4755471075642497</v>
+        <v>-0.4156677476123756</v>
       </c>
       <c r="F1872" t="n">
         <v>-1.557680096134823</v>
@@ -44630,10 +44630,10 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.127959960755891</v>
+        <v>-8.978261560876206</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.5359351436780679</v>
+        <v>-0.4760557837261938</v>
       </c>
       <c r="F1873" t="n">
         <v>-1.715078976347944</v>
@@ -44653,10 +44653,10 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-9.487490283259893</v>
+        <v>-9.337791883380207</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.6743969693816183</v>
+        <v>-0.6145176094297442</v>
       </c>
       <c r="F1874" t="n">
         <v>-1.715078976347944</v>
@@ -44676,10 +44676,10 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-9.537839346714115</v>
+        <v>-9.388140946834429</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.6866205748061298</v>
+        <v>-0.6267412148542557</v>
       </c>
       <c r="F1875" t="n">
         <v>-1.765428039802166</v>
@@ -44699,10 +44699,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-9.635458624135511</v>
+        <v>-9.485760224255825</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.7226265351529193</v>
+        <v>-0.6627471752010452</v>
       </c>
       <c r="F1876" t="n">
         <v>-1.863047317223563</v>
@@ -44722,10 +44722,10 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-9.6317676991791</v>
+        <v>-9.482069299299415</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.7211501651703549</v>
+        <v>-0.6612708052184808</v>
       </c>
       <c r="F1877" t="n">
         <v>-1.863047317223563</v>
@@ -44745,10 +44745,10 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-9.836025874508964</v>
+        <v>-9.686327474629278</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.7973402381836583</v>
+        <v>-0.7374608782317837</v>
       </c>
       <c r="F1878" t="n">
         <v>-1.990686261837552</v>
@@ -44768,10 +44768,10 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-10.05406364614014</v>
+        <v>-9.904365246260456</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.8800727923516933</v>
+        <v>-0.8201934323998188</v>
       </c>
       <c r="F1879" t="n">
         <v>-2.165457029933451</v>
@@ -44791,10 +44791,10 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-9.980593814472693</v>
+        <v>-9.830895414593007</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.8353131581912923</v>
+        <v>-0.7754337982394182</v>
       </c>
       <c r="F1880" t="n">
         <v>-2.091987198266002</v>
@@ -44814,10 +44814,10 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-10.15571823185924</v>
+        <v>-10.00601983197955</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.8908077043983926</v>
+        <v>-0.8309283444465185</v>
       </c>
       <c r="F1881" t="n">
         <v>-2.267111615652546</v>
@@ -44837,10 +44837,10 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-10.39017032587373</v>
+        <v>-10.24047192599404</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.9918077069057847</v>
+        <v>-0.9319283469539106</v>
       </c>
       <c r="F1882" t="n">
         <v>-2.267111615652546</v>
@@ -44860,10 +44860,10 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-10.67797417041096</v>
+        <v>-10.52827577053128</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.113601435494657</v>
+        <v>-1.053722075542782</v>
       </c>
       <c r="F1883" t="n">
         <v>-2.554915460189784</v>
@@ -44883,10 +44883,10 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-10.73076032601129</v>
+        <v>-10.58106192613161</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.133600107896231</v>
+        <v>-1.073720747944357</v>
       </c>
       <c r="F1884" t="n">
         <v>-2.650590946772181</v>
@@ -44906,10 +44906,10 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-10.96278924574755</v>
+        <v>-10.81309084586787</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.223717947161621</v>
+        <v>-1.163838587209746</v>
       </c>
       <c r="F1885" t="n">
         <v>-2.712603643960604</v>
@@ -44929,10 +44929,10 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-10.91077373177874</v>
+        <v>-10.76107533189905</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.198921405887694</v>
+        <v>-1.13904204593582</v>
       </c>
       <c r="F1886" t="n">
         <v>-2.712603643960604</v>
@@ -44952,10 +44952,10 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-11.05244557350286</v>
+        <v>-10.90274717362317</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.257065369476084</v>
+        <v>-1.19718600952421</v>
       </c>
       <c r="F1887" t="n">
         <v>-2.712603643960604</v>
@@ -44975,10 +44975,10 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-11.00285472907803</v>
+        <v>-10.85315632919834</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.222175621541278</v>
+        <v>-1.162296261589404</v>
       </c>
       <c r="F1888" t="n">
         <v>-2.663012799535771</v>
@@ -44998,10 +44998,10 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-10.80370262184093</v>
+        <v>-10.65400422196124</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.155565912293122</v>
+        <v>-1.095686552341248</v>
       </c>
       <c r="F1889" t="n">
         <v>-2.497690273585957</v>
@@ -45021,10 +45021,10 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-10.57785746912151</v>
+        <v>-10.42815906924183</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.055648778169149</v>
+        <v>-0.9957694182172747</v>
       </c>
       <c r="F1890" t="n">
         <v>-2.455763597998794</v>
@@ -45044,10 +45044,10 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-10.45327881278392</v>
+        <v>-10.30358041290424</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.004678171078053</v>
+        <v>-0.9447988111261787</v>
       </c>
       <c r="F1891" t="n">
         <v>-2.455763597998794</v>
@@ -45067,10 +45067,10 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-10.50617410082821</v>
+        <v>-10.35647570094852</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.02320251213366</v>
+        <v>-0.9633231521817853</v>
       </c>
       <c r="F1892" t="n">
         <v>-2.450808251910348</v>
@@ -45090,10 +45090,10 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-10.22226536989946</v>
+        <v>-10.07256697001977</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.9039053155235237</v>
+        <v>-0.8440259555716496</v>
       </c>
       <c r="F1893" t="n">
         <v>-2.450808251910348</v>
@@ -45113,10 +45113,10 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-10.15089897728981</v>
+        <v>-10.00120057741013</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.8850960208735303</v>
+        <v>-0.8252166609216558</v>
       </c>
       <c r="F1894" t="n">
         <v>-2.379441859300699</v>
@@ -45136,10 +45136,10 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-9.887062110085743</v>
+        <v>-9.737363710206058</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.7894447553048098</v>
+        <v>-0.7295653953529357</v>
       </c>
       <c r="F1895" t="n">
         <v>-2.379441859300699</v>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-9.619820309217346</v>
+        <v>-9.47012190933766</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.6843825954568246</v>
+        <v>-0.62450323550495</v>
       </c>
       <c r="F1896" t="n">
         <v>-2.379441859300699</v>
@@ -45182,10 +45182,10 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-9.521913270540855</v>
+        <v>-9.372214870661169</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.6455200949596889</v>
+        <v>-0.5856407350078148</v>
       </c>
       <c r="F1897" t="n">
         <v>-2.311456109440143</v>
@@ -45205,10 +45205,10 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-9.497959729564897</v>
+        <v>-9.348261329685212</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.6352701724238123</v>
+        <v>-0.5753908124719378</v>
       </c>
       <c r="F1898" t="n">
         <v>-2.287502568464185</v>
@@ -45228,10 +45228,10 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-9.2338997912421</v>
+        <v>-9.084201391362415</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.5429065132564457</v>
+        <v>-0.4830271533045716</v>
       </c>
       <c r="F1899" t="n">
         <v>-2.023442630141389</v>
@@ -45251,10 +45251,10 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-8.526820167737263</v>
+        <v>-8.377121767857577</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.2628616975148117</v>
+        <v>-0.2029823375629372</v>
       </c>
       <c r="F1900" t="n">
         <v>-2.023442630141389</v>
@@ -45274,10 +45274,10 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-8.486635869371073</v>
+        <v>-8.336937469491387</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.2464443542804942</v>
+        <v>-0.1865649943286196</v>
       </c>
       <c r="F1901" t="n">
         <v>-1.983258331775199</v>
@@ -45297,10 +45297,10 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-8.406566073833268</v>
+        <v>-8.256867673953582</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.2150496148446153</v>
+        <v>-0.1551702548927412</v>
       </c>
       <c r="F1902" t="n">
         <v>-1.903188536237395</v>
@@ -45320,10 +45320,10 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-8.173084851603669</v>
+        <v>-8.023386451723983</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.1137326971149233</v>
+        <v>-0.05385333716304874</v>
       </c>
       <c r="F1903" t="n">
         <v>-1.669707314007796</v>
@@ -45343,10 +45343,10 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.023418460596154</v>
+        <v>-7.873720060716468</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.05675835102487659</v>
+        <v>0.003121008926997959</v>
       </c>
       <c r="F1904" t="n">
         <v>-1.57680382276526</v>
@@ -45366,10 +45366,10 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-7.891142986965268</v>
+        <v>-7.741444587085581</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.008480674825495083</v>
+        <v>0.05139868512637946</v>
       </c>
       <c r="F1905" t="n">
         <v>-1.444528349134373</v>
@@ -45389,10 +45389,10 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-7.700543312292115</v>
+        <v>-7.550844912412429</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.07057425573140286</v>
+        <v>0.1304536156832774</v>
       </c>
       <c r="F1906" t="n">
         <v>-1.253928674461221</v>
@@ -45412,10 +45412,10 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-7.451543513608534</v>
+        <v>-7.301845113728848</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.1830805164284937</v>
+        <v>0.2429598763803686</v>
       </c>
       <c r="F1907" t="n">
         <v>-1.253928674461221</v>
@@ -45435,10 +45435,10 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-7.557133503381639</v>
+        <v>-7.407435103501952</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.01286859092003345</v>
+        <v>0.072747950871908</v>
       </c>
       <c r="F1908" t="n">
         <v>-1.359518664234325</v>
@@ -45458,10 +45458,10 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-7.575868405500236</v>
+        <v>-7.426170005620549</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.05391897194968109</v>
+        <v>0.1137983319015556</v>
       </c>
       <c r="F1909" t="n">
         <v>-1.359518664234325</v>
@@ -45481,10 +45481,10 @@
         <v>2.964743835775355</v>
       </c>
       <c r="D1910" t="n">
-        <v>-7.427928364092637</v>
+        <v>-7.27822996421295</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.00678393417544676</v>
+        <v>0.05309542577642778</v>
       </c>
       <c r="F1910" t="n">
         <v>-1.339197748325767</v>
@@ -45504,10 +45504,10 @@
         <v>2.956029849521877</v>
       </c>
       <c r="D1911" t="n">
-        <v>-7.403699727703664</v>
+        <v>-7.254001327823977</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.005806465873336109</v>
+        <v>0.05407289407853844</v>
       </c>
       <c r="F1911" t="n">
         <v>-1.314969111936795</v>
@@ -45527,10 +45527,10 @@
         <v>2.949069237426784</v>
       </c>
       <c r="D1912" t="n">
-        <v>-7.360151320932974</v>
+        <v>-7.210452921053287</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.004652284739846912</v>
+        <v>0.06453164469172146</v>
       </c>
       <c r="F1912" t="n">
         <v>-1.314969111936795</v>
@@ -45550,10 +45550,10 @@
         <v>2.963531591807927</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.118002927479115</v>
+        <v>-6.968304527599429</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.1159739965025333</v>
+        <v>0.1758533564544078</v>
       </c>
       <c r="F1913" t="n">
         <v>-1.314969111936795</v>
@@ -45573,10 +45573,10 @@
         <v>2.958063712267122</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.054773555710767</v>
+        <v>-6.905075155831081</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.1357978656690677</v>
+        <v>0.1956772256209423</v>
       </c>
       <c r="F1914" t="n">
         <v>-1.314969111936795</v>
@@ -45596,10 +45596,10 @@
         <v>2.955561806277699</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.931482420893636</v>
+        <v>-6.78178402101395</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.1826124136064968</v>
+        <v>0.2424917735583714</v>
       </c>
       <c r="F1915" t="n">
         <v>-1.191677977119665</v>
@@ -45619,10 +45619,10 @@
         <v>2.963262784515024</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.910333221990193</v>
+        <v>-6.760634822110506</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.1987730714051992</v>
+        <v>0.2586524313570742</v>
       </c>
       <c r="F1916" t="n">
         <v>-1.170528778216221</v>
@@ -45642,10 +45642,10 @@
         <v>2.959043492862075</v>
       </c>
       <c r="D1917" t="n">
-        <v>-6.666567780006749</v>
+        <v>-6.516869380127062</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.2920599565456277</v>
+        <v>0.3519393164975022</v>
       </c>
       <c r="F1917" t="n">
         <v>-1.170528778216221</v>
@@ -45665,10 +45665,10 @@
         <v>2.961167806782091</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.519670752288878</v>
+        <v>-6.369972352409192</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.3529430815527919</v>
+        <v>0.4128224415046664</v>
       </c>
       <c r="F1918" t="n">
         <v>-1.122870536237633</v>
@@ -45688,10 +45688,10 @@
         <v>2.953909881765793</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.269820358339803</v>
+        <v>-6.120121958460118</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.4456253141161239</v>
+        <v>0.5055046740679985</v>
       </c>
       <c r="F1919" t="n">
         <v>-1.122870536237633</v>
@@ -45711,10 +45711,10 @@
         <v>2.957509005286441</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.093928265872371</v>
+        <v>-5.944229865992686</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5195812746237456</v>
+        <v>0.5794606345756201</v>
       </c>
       <c r="F1920" t="n">
         <v>-1.122870536237633</v>
@@ -45734,10 +45734,10 @@
         <v>2.970836511340995</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.922481802849908</v>
+        <v>-5.772783402970222</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.6014873658872846</v>
+        <v>0.6613667258391591</v>
       </c>
       <c r="F1921" t="n">
         <v>-0.9514240732151701</v>
@@ -45757,10 +45757,10 @@
         <v>2.969856988957292</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.697448803181085</v>
+        <v>-5.547750403301399</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6905210433711111</v>
+        <v>0.7504004033229852</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.7263910735463472</v>
@@ -45780,10 +45780,10 @@
         <v>2.974551790011609</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.63381306094715</v>
+        <v>-5.484114661067465</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.720670141319002</v>
+        <v>0.7805495012708761</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.6627553313124127</v>
@@ -45803,10 +45803,10 @@
         <v>2.955746048795405</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.540813019741252</v>
+        <v>-5.391114619861566</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.739064416585157</v>
+        <v>0.7989437765370311</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.6627553313124127</v>
@@ -45826,10 +45826,10 @@
         <v>2.957489125420282</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.300382522936392</v>
+        <v>-5.150684123056706</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8369796919319783</v>
+        <v>0.8968590518838528</v>
       </c>
       <c r="F1925" t="n">
         <v>-0.4223248345075524</v>
@@ -45849,10 +45849,10 @@
         <v>2.961418439255103</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.228139954765197</v>
+        <v>-5.125092119699288</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8698060330352764</v>
+        <v>0.9110251670616401</v>
       </c>
       <c r="F1926" t="n">
         <v>-0.4223248345075524</v>
@@ -45872,10 +45872,10 @@
         <v>2.962097023172443</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.112200105140012</v>
+        <v>-5.009152270074103</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9168605568026904</v>
+        <v>0.9580796908290541</v>
       </c>
       <c r="F1927" t="n">
         <v>-0.3455031034914285</v>
@@ -45895,10 +45895,10 @@
         <v>2.959095094392436</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.003395219660285</v>
+        <v>-4.900347384594376</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9573805822145749</v>
+        <v>0.9985997162409386</v>
       </c>
       <c r="F1928" t="n">
         <v>-0.3455031034914285</v>
@@ -45918,10 +45918,10 @@
         <v>2.96067413140305</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.783374421623274</v>
+        <v>-4.680326586557365</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.046967938439993</v>
+        <v>1.088187072466357</v>
       </c>
       <c r="F1929" t="n">
         <v>-0.2042832584234483</v>
@@ -45941,10 +45941,10 @@
         <v>2.976568314204874</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.650506732559997</v>
+        <v>-4.547458897494088</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.116009196867128</v>
+        <v>1.157228330893491</v>
       </c>
       <c r="F1930" t="n">
         <v>-0.2042832584234483</v>
@@ -45964,10 +45964,10 @@
         <v>2.977714158645175</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.490991629040627</v>
+        <v>-4.387943793974718</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.180961082715177</v>
+        <v>1.222180216741541</v>
       </c>
       <c r="F1931" t="n">
         <v>-0.04476815490407837</v>
@@ -45987,10 +45987,10 @@
         <v>2.987802261206615</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.346319483940889</v>
+        <v>-4.24327164887498</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.248918043316512</v>
+        <v>1.290137177342876</v>
       </c>
       <c r="F1932" t="n">
         <v>0.09990399019565904</v>
@@ -46010,10 +46010,10 @@
         <v>2.973839752608041</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.406194311298582</v>
+        <v>-4.303146476232673</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.211005603774861</v>
+        <v>1.252224737801225</v>
       </c>
       <c r="F1933" t="n">
         <v>0.04002916283796693</v>
@@ -46033,10 +46033,10 @@
         <v>2.996240245930607</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.319394813519573</v>
+        <v>-4.216346978453664</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.268125896209031</v>
+        <v>1.309345030235394</v>
       </c>
       <c r="F1934" t="n">
         <v>0.04002916283796693</v>
@@ -46056,10 +46056,10 @@
         <v>2.996312647304019</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.321864519981379</v>
+        <v>-4.21881668491547</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.267210414997721</v>
+        <v>1.308429549024084</v>
       </c>
       <c r="F1935" t="n">
         <v>0.03755945637616076</v>
@@ -46079,10 +46079,10 @@
         <v>3.007319569778721</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.390234706305389</v>
+        <v>-4.287186871239481</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.250869262942819</v>
+        <v>1.292088396969182</v>
       </c>
       <c r="F1936" t="n">
         <v>0.04683515541237571</v>
@@ -46102,10 +46102,10 @@
         <v>2.997756278410613</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.498772887221523</v>
+        <v>-4.395725052155615</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.197890699208256</v>
+        <v>1.23910983323462</v>
       </c>
       <c r="F1937" t="n">
         <v>0.04683515541237571</v>
@@ -46125,10 +46125,10 @@
         <v>2.822465843450999</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.529766046550228</v>
+        <v>-4.42671821148432</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.010203000517161</v>
+        <v>1.051422134543524</v>
       </c>
       <c r="F1938" t="n">
         <v>0.04683515541237571</v>
@@ -46148,10 +46148,10 @@
         <v>2.827033075442787</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.354291786757759</v>
+        <v>-4.251243951691851</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.084959936425936</v>
+        <v>1.1261790704523</v>
       </c>
       <c r="F1939" t="n">
         <v>0.04683515541237571</v>
@@ -46171,10 +46171,10 @@
         <v>2.802775104203994</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.465228039399008</v>
+        <v>-4.3621802043331</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.016327464130644</v>
+        <v>1.057546598157007</v>
       </c>
       <c r="F1940" t="n">
         <v>0.04683515541237571</v>
@@ -46194,10 +46194,10 @@
         <v>2.8059064894239</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.668254616942241</v>
+        <v>-4.565206781876333</v>
       </c>
       <c r="E1941" t="n">
-        <v>0.9382482183332561</v>
+        <v>0.9794673523596193</v>
       </c>
       <c r="F1941" t="n">
         <v>-0.1561914221308577</v>
@@ -46217,10 +46217,10 @@
         <v>2.816078875856032</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.510329018006948</v>
+        <v>-4.40728118294104</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.011590844339506</v>
+        <v>1.052809978365869</v>
       </c>
       <c r="F1942" t="n">
         <v>-0.1561914221308577</v>
@@ -46240,10 +46240,10 @@
         <v>2.811025146429893</v>
       </c>
       <c r="D1943" t="n">
-        <v>-4.424085554980571</v>
+        <v>-4.321037719914663</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.041034500123917</v>
+        <v>1.08225363415028</v>
       </c>
       <c r="F1943" t="n">
         <v>-0.1561914221308577</v>
@@ -46263,10 +46263,10 @@
         <v>2.802800921874418</v>
       </c>
       <c r="D1944" t="n">
-        <v>-4.425268639631632</v>
+        <v>-4.322220804565724</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.032337041708018</v>
+        <v>1.073556175734381</v>
       </c>
       <c r="F1944" t="n">
         <v>-0.1618344705973692</v>
@@ -46286,10 +46286,10 @@
         <v>2.80335279490752</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.302140932637549</v>
+        <v>-4.199093097571641</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.082139997538753</v>
+        <v>1.123359131565116</v>
       </c>
       <c r="F1945" t="n">
         <v>-0.1618344705973692</v>
@@ -46309,10 +46309,10 @@
         <v>2.732625486798885</v>
       </c>
       <c r="D1946" t="n">
-        <v>-4.209330451186689</v>
+        <v>-4.106282616120781</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.048536882010462</v>
+        <v>1.089756016036826</v>
       </c>
       <c r="F1946" t="n">
         <v>-0.06902398914650987</v>
@@ -46332,10 +46332,10 @@
         <v>2.734498962723486</v>
       </c>
       <c r="D1947" t="n">
-        <v>-4.16076739896566</v>
+        <v>-4.057719563899751</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.069835578823475</v>
+        <v>1.111054712849838</v>
       </c>
       <c r="F1947" t="n">
         <v>-0.02046093692547968</v>
@@ -46355,10 +46355,10 @@
         <v>2.729574671235209</v>
       </c>
       <c r="D1948" t="n">
-        <v>-4.048096180729409</v>
+        <v>-3.945048345663501</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.109979774629698</v>
+        <v>1.151198908656061</v>
       </c>
       <c r="F1948" t="n">
         <v>0.09221028131077053</v>
@@ -46378,10 +46378,10 @@
         <v>2.735065967065876</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.935719179546737</v>
+        <v>-3.832671344480829</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.160421870933434</v>
+        <v>1.201641004959798</v>
       </c>
       <c r="F1949" t="n">
         <v>0.09221028131077053</v>
@@ -46401,10 +46401,10 @@
         <v>2.746563168834415</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.133953748433467</v>
+        <v>-4.030905913367559</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.092625245147281</v>
+        <v>1.133844379173645</v>
       </c>
       <c r="F1950" t="n">
         <v>-0.1060242875759601</v>
@@ -46424,10 +46424,10 @@
         <v>2.584918888835069</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.216955029458746</v>
+        <v>-4.113907194392838</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.897780452737823</v>
+        <v>0.9389995867641863</v>
       </c>
       <c r="F1951" t="n">
         <v>-0.1245951721031338</v>
@@ -46447,10 +46447,10 @@
         <v>2.705068549554274</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.344022035765734</v>
+        <v>-4.240974200699826</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9671033109342333</v>
+        <v>1.008322444960597</v>
       </c>
       <c r="F1952" t="n">
         <v>-0.1245951721031338</v>
@@ -46470,10 +46470,10 @@
         <v>2.719581575656597</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.430620618746837</v>
+        <v>-4.327572783680929</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9469769038441151</v>
+        <v>0.9881960378704784</v>
       </c>
       <c r="F1953" t="n">
         <v>-0.1245951721031338</v>
@@ -46493,10 +46493,10 @@
         <v>2.717001016998966</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.392236956188686</v>
+        <v>-4.289189121122778</v>
       </c>
       <c r="E1954" t="n">
-        <v>0.9597498102097444</v>
+        <v>1.000968944236108</v>
       </c>
       <c r="F1954" t="n">
         <v>-0.08621150954498263</v>
@@ -46516,10 +46516,10 @@
         <v>2.713730045844268</v>
       </c>
       <c r="D1955" t="n">
-        <v>-4.21512062615352</v>
+        <v>-4.112072791087612</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.027325371069113</v>
+        <v>1.068544505095476</v>
       </c>
       <c r="F1955" t="n">
         <v>-0.08621150954498263</v>
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741324873263895</v>
+        <v>3.741324873263896</v>
       </c>
       <c r="C1956" t="n">
         <v>2.714413437606181</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.269526293330919</v>
+        <v>-4.082370667111318</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.006246495960066</v>
+        <v>1.081108746447907</v>
       </c>
       <c r="F1956" t="n">
-        <v>-0.1430088562630189</v>
+        <v>-0.090681634760296</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.62860812384837</v>
+        <v>2.660004456750004</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750725801481227</v>
+        <v>3.750725801481228</v>
       </c>
       <c r="C1957" t="n">
         <v>2.708200412912595</v>
       </c>
       <c r="D1957" t="n">
-        <v>-4.090150872092152</v>
+        <v>-3.902995245872551</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.071783639761987</v>
+        <v>1.146645890249828</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.01376790190769978</v>
+        <v>0.06609512341042267</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.716461154057216</v>
+        <v>2.747857486958849</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716988143452223</v>
+        <v>3.716988143452224</v>
       </c>
       <c r="C1958" t="n">
         <v>2.689007868244185</v>
       </c>
       <c r="D1958" t="n">
-        <v>-4.135165085612758</v>
+        <v>-3.948009459393157</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.034585409685334</v>
+        <v>1.109447660173175</v>
       </c>
       <c r="F1958" t="n">
-        <v>-0.01658099340690483</v>
+        <v>0.03574622809581807</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.679059272200043</v>
+        <v>2.710455605101676</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702303297953</v>
+        <v>3.737023032979531</v>
       </c>
       <c r="C1959" t="n">
         <v>2.694699430583131</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.402169595885193</v>
+        <v>-4.215013969665592</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9334751679153062</v>
+        <v>1.008337418403147</v>
       </c>
       <c r="F1959" t="n">
-        <v>-0.2109440314498534</v>
+        <v>-0.1586168099471305</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.568133011713219</v>
+        <v>2.599529344614853</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.693903352479632</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.690956816344109</v>
+        <v>-4.503801190124507</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.8171642016282417</v>
+        <v>0.8920264521160821</v>
       </c>
       <c r="F1960" t="n">
-        <v>-0.3120301515488538</v>
+        <v>-0.2597029300461309</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.50668526155032</v>
+        <v>2.538081594451954</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.70556808628545</v>
+        <v>3.705568086285451</v>
       </c>
       <c r="C1961" t="n">
         <v>2.691503314033949</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.658481230173336</v>
+        <v>-4.471325603953735</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.8277543976508672</v>
+        <v>0.9026166481387077</v>
       </c>
       <c r="F1961" t="n">
-        <v>-0.3120301515488538</v>
+        <v>-0.2597029300461309</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.504285223104637</v>
+        <v>2.535681556006271</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709506867848098</v>
+        <v>3.709506867848099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.688028033242194</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.639443102466039</v>
+        <v>-4.452287476246438</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.831894367942031</v>
+        <v>0.9067566184298714</v>
       </c>
       <c r="F1962" t="n">
-        <v>-0.3702137628800483</v>
+        <v>-0.3178865413773254</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.465899775514165</v>
+        <v>2.497296108415799</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.865609902180875</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.670569733616658</v>
+        <v>-4.483414107397056</v>
       </c>
       <c r="E1963" t="n">
-        <v>0.9970255844204643</v>
+        <v>1.071887834908305</v>
       </c>
       <c r="F1963" t="n">
-        <v>-0.3702137628800483</v>
+        <v>-0.3178865413773254</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.643481644452846</v>
+        <v>2.67487797735448</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.866443231167008</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.722890114217449</v>
+        <v>-4.535734487997848</v>
       </c>
       <c r="E1964" t="n">
-        <v>0.976930761166281</v>
+        <v>1.051793011654122</v>
       </c>
       <c r="F1964" t="n">
-        <v>-0.3352669028711762</v>
+        <v>-0.2829396813684533</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.665283089444303</v>
+        <v>2.696679422345936</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.872451761563934</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.867213020142368</v>
+        <v>-4.680057393922767</v>
       </c>
       <c r="E1965" t="n">
-        <v>0.9252101291932395</v>
+        <v>1.00007237968108</v>
       </c>
       <c r="F1965" t="n">
-        <v>-0.3352669028711762</v>
+        <v>-0.2829396813684533</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.671291619841229</v>
+        <v>2.702687952742862</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.951604409355956</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.719470049907366</v>
+        <v>-4.532314423687764</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.063459965079262</v>
+        <v>1.138322215567103</v>
       </c>
       <c r="F1966" t="n">
-        <v>-0.167459545636293</v>
+        <v>-0.1151323241335701</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.85112868197418</v>
+        <v>2.882525014875814</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.954398030887437</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.821484732438587</v>
+        <v>-4.634329106218986</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.025447713598255</v>
+        <v>1.100309964086095</v>
       </c>
       <c r="F1967" t="n">
-        <v>-0.167459545636293</v>
+        <v>-0.1151323241335701</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.853922303505661</v>
+        <v>2.885318636407295</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.955060379279095</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.684875388344494</v>
+        <v>-4.497719762124893</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.08075379962755</v>
+        <v>1.155616050115391</v>
       </c>
       <c r="F1968" t="n">
-        <v>-0.03085020154220053</v>
+        <v>0.02147701996052237</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.936550258353775</v>
+        <v>2.967946591255409</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.954140856019206</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.827640721167144</v>
+        <v>-4.640485094947543</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.0227281432386</v>
+        <v>1.097590393726441</v>
       </c>
       <c r="F1969" t="n">
-        <v>-0.1736155343648509</v>
+        <v>-0.121288312862128</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.849971535400295</v>
+        <v>2.881367868301929</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>3.020476409816026</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.765342722391022</v>
+        <v>-4.578187096171421</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.11398289654587</v>
+        <v>1.188845147033711</v>
       </c>
       <c r="F1970" t="n">
-        <v>-0.1736155343648509</v>
+        <v>-0.121288312862128</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.916307089197116</v>
+        <v>2.94770342209875</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848725564462185</v>
+        <v>3.848725564462184</v>
       </c>
       <c r="C1971" t="n">
         <v>2.729057282205424</v>
       </c>
       <c r="D1971" t="n">
-        <v>-4.563552524725864</v>
+        <v>-4.376396898506263</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9032798480013315</v>
+        <v>0.978142098489172</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.02440265780430345</v>
+        <v>0.07672987930702635</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.743698876888007</v>
+        <v>2.775095209789641</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.781247022321528</v>
+        <v>3.82524728420147</v>
       </c>
       <c r="C1972" t="n">
         <v>2.732351656133147</v>
       </c>
       <c r="D1972" t="n">
-        <v>-4.522983447524596</v>
+        <v>-4.456782232739026</v>
       </c>
       <c r="E1972" t="n">
-        <v>0.9228018528095616</v>
+        <v>0.9492823387237896</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.06497173500557157</v>
+        <v>0.08414466253478226</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.771334697136491</v>
+        <v>2.782838453654017</v>
       </c>
     </row>
   </sheetData>
